--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.4781</v>
+        <v>7.8466</v>
       </c>
       <c r="C2" t="n">
-        <v>8.608575</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7.060072521561429</v>
+        <v>2.7485</v>
       </c>
       <c r="E2" t="n">
-        <v>87.9868</v>
+        <v>7.8466</v>
       </c>
       <c r="F2" t="n">
-        <v>9.281212618863428</v>
+        <v>4.2936</v>
       </c>
       <c r="G2" t="n">
-        <v>78.70562873304931</v>
+        <v>3.553</v>
       </c>
       <c r="H2" t="n">
-        <v>9.281212618863428</v>
+        <v>4.7138</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6779427528871</v>
+        <v>3.8207</v>
       </c>
       <c r="J2" t="n">
-        <v>78.70562873304931</v>
+        <v>3.553</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -541,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>87.3836</v>
+        <v>7.373699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.7996</v>
+        <v>7.7168</v>
       </c>
       <c r="C3" t="n">
-        <v>7.3497</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.94022053443785</v>
+        <v>2.6961</v>
       </c>
       <c r="E3" t="n">
-        <v>61.568</v>
+        <v>7.7168</v>
       </c>
       <c r="F3" t="n">
-        <v>3.443706382011539</v>
+        <v>1.9903</v>
       </c>
       <c r="G3" t="n">
-        <v>58.1242731365488</v>
+        <v>5.7265</v>
       </c>
       <c r="H3" t="n">
-        <v>3.443706382011539</v>
+        <v>1.9903</v>
       </c>
       <c r="I3" t="n">
-        <v>3.189348017440617</v>
+        <v>1.6132</v>
       </c>
       <c r="J3" t="n">
-        <v>58.1242731365488</v>
+        <v>5.7265</v>
       </c>
       <c r="K3" t="n">
         <v>104</v>
@@ -587,7 +575,7 @@
         <v>154</v>
       </c>
       <c r="M3" t="n">
-        <v>61.3136</v>
+        <v>7.3397</v>
       </c>
       <c r="N3" t="n">
         <v>258</v>
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.8825</v>
+        <v>6.2131</v>
       </c>
       <c r="C4" t="n">
-        <v>5.911875</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.192018326568051</v>
+        <v>2.0886</v>
       </c>
       <c r="E4" t="n">
-        <v>39.7808</v>
+        <v>6.2131</v>
       </c>
       <c r="F4" t="n">
-        <v>2.991046594597169</v>
+        <v>1.7168</v>
       </c>
       <c r="G4" t="n">
-        <v>36.78979265803224</v>
+        <v>4.4963</v>
       </c>
       <c r="H4" t="n">
-        <v>2.991046594597169</v>
+        <v>1.7168</v>
       </c>
       <c r="I4" t="n">
-        <v>2.770122498358522</v>
+        <v>1.3915</v>
       </c>
       <c r="J4" t="n">
-        <v>36.78979265803224</v>
+        <v>4.4963</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -633,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>39.5599</v>
+        <v>5.887799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>258</v>
@@ -642,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8713</v>
+        <v>5.6266</v>
       </c>
       <c r="C5" t="n">
-        <v>3.653475</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.424660408760141</v>
+        <v>1.8517</v>
       </c>
       <c r="E5" t="n">
-        <v>17.755</v>
+        <v>5.6266</v>
       </c>
       <c r="F5" t="n">
-        <v>3.383793185139739</v>
+        <v>4.7492</v>
       </c>
       <c r="G5" t="n">
-        <v>14.37117590095778</v>
+        <v>0.8774</v>
       </c>
       <c r="H5" t="n">
-        <v>3.383793185139739</v>
+        <v>6.5466</v>
       </c>
       <c r="I5" t="n">
-        <v>3.133860117351416</v>
+        <v>5.3062</v>
       </c>
       <c r="J5" t="n">
-        <v>14.37117590095778</v>
+        <v>0.8774</v>
       </c>
       <c r="K5" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L5" t="n">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>17.505</v>
+        <v>6.183599999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>258</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8544</v>
+        <v>4.8696</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6408</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.417213707879266</v>
+        <v>1.5458</v>
       </c>
       <c r="E6" t="n">
-        <v>17.6622</v>
+        <v>4.8696</v>
       </c>
       <c r="F6" t="n">
-        <v>8.386116862984284</v>
+        <v>4.7109</v>
       </c>
       <c r="G6" t="n">
-        <v>9.276046988181196</v>
+        <v>0.1587</v>
       </c>
       <c r="H6" t="n">
-        <v>8.386116862984284</v>
+        <v>6.3926</v>
       </c>
       <c r="I6" t="n">
-        <v>9.406283656625671</v>
+        <v>5.1814</v>
       </c>
       <c r="J6" t="n">
-        <v>9.276046988181196</v>
+        <v>0.1587</v>
       </c>
       <c r="K6" t="n">
         <v>136</v>
@@ -725,7 +713,7 @@
         <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>18.6823</v>
+        <v>5.3401</v>
       </c>
       <c r="N6" t="n">
         <v>179</v>
@@ -734,676 +722,676 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4983</v>
+        <v>4.8401</v>
       </c>
       <c r="C7" t="n">
-        <v>3.373725</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.265660755315439</v>
+        <v>1.5339</v>
       </c>
       <c r="E7" t="n">
-        <v>15.7734</v>
+        <v>4.8401</v>
       </c>
       <c r="F7" t="n">
-        <v>2.586826358130703</v>
+        <v>4.5433</v>
       </c>
       <c r="G7" t="n">
-        <v>13.18659406257802</v>
+        <v>0.2968</v>
       </c>
       <c r="H7" t="n">
-        <v>2.586826358130703</v>
+        <v>5.7181</v>
       </c>
       <c r="I7" t="n">
-        <v>2.418685140548657</v>
+        <v>4.6347</v>
       </c>
       <c r="J7" t="n">
-        <v>13.18659406257802</v>
+        <v>0.2968</v>
       </c>
       <c r="K7" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>15.6053</v>
+        <v>4.9315</v>
       </c>
       <c r="N7" t="n">
-        <v>266</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4285</v>
+        <v>4.2934</v>
       </c>
       <c r="C8" t="n">
-        <v>3.321375</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.237083314874605</v>
+        <v>1.3131</v>
       </c>
       <c r="E8" t="n">
-        <v>15.4173</v>
+        <v>4.2934</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03845579741983421</v>
+        <v>4.3477</v>
       </c>
       <c r="G8" t="n">
-        <v>15.45572708359314</v>
+        <v>-0.0543</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.03845579741983421</v>
+        <v>4.9315</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03561538286211396</v>
+        <v>3.9971</v>
       </c>
       <c r="J8" t="n">
-        <v>15.45572708359314</v>
+        <v>-0.0543</v>
       </c>
       <c r="K8" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L8" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M8" t="n">
-        <v>15.4201</v>
+        <v>3.9428</v>
       </c>
       <c r="N8" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5808</v>
+        <v>3.5378</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6856</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9175630074110456</v>
+        <v>1.0078</v>
       </c>
       <c r="E9" t="n">
-        <v>11.4352</v>
+        <v>3.5378</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.231447861029106</v>
+        <v>3.6941</v>
       </c>
       <c r="G9" t="n">
-        <v>13.66666619864532</v>
+        <v>-0.1563</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.231447861029106</v>
+        <v>3.6941</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.086405902899604</v>
+        <v>2.9942</v>
       </c>
       <c r="J9" t="n">
-        <v>13.66666619864532</v>
+        <v>-0.1563</v>
       </c>
       <c r="K9" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>11.5803</v>
+        <v>2.8379</v>
       </c>
       <c r="N9" t="n">
-        <v>266</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3136</v>
+        <v>3.202</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4852</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8266399761842179</v>
+        <v>0.8722</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3021</v>
+        <v>3.202</v>
       </c>
       <c r="F10" t="n">
-        <v>5.398607337052968</v>
+        <v>1.4454</v>
       </c>
       <c r="G10" t="n">
-        <v>4.903473869272057</v>
+        <v>1.7566</v>
       </c>
       <c r="H10" t="n">
-        <v>5.398607337052968</v>
+        <v>1.4454</v>
       </c>
       <c r="I10" t="n">
-        <v>7.25750924486296</v>
+        <v>1.1715</v>
       </c>
       <c r="J10" t="n">
-        <v>4.903473869272057</v>
+        <v>1.7566</v>
       </c>
       <c r="K10" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>12.161</v>
+        <v>2.9281</v>
       </c>
       <c r="N10" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2571</v>
+        <v>2.9754</v>
       </c>
       <c r="C11" t="n">
-        <v>2.442825</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8079754459123457</v>
+        <v>0.7806</v>
       </c>
       <c r="E11" t="n">
-        <v>10.0695</v>
+        <v>2.9754</v>
       </c>
       <c r="F11" t="n">
-        <v>6.49522126770457</v>
+        <v>3.9578</v>
       </c>
       <c r="G11" t="n">
-        <v>3.574251412444012</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.49522126770457</v>
+        <v>3.9578</v>
       </c>
       <c r="I11" t="n">
-        <v>7.285361586868632</v>
+        <v>3.2079</v>
       </c>
       <c r="J11" t="n">
-        <v>3.574251412444012</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>10.8596</v>
+        <v>2.2255</v>
       </c>
       <c r="N11" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6733</v>
+        <v>2.8003</v>
       </c>
       <c r="C12" t="n">
-        <v>2.004975</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6258832167068592</v>
+        <v>0.7099</v>
       </c>
       <c r="E12" t="n">
-        <v>7.8001</v>
+        <v>2.8003</v>
       </c>
       <c r="F12" t="n">
-        <v>4.015498077846065</v>
+        <v>0.4529</v>
       </c>
       <c r="G12" t="n">
-        <v>3.784632462602251</v>
+        <v>2.3474</v>
       </c>
       <c r="H12" t="n">
-        <v>4.015498077846065</v>
+        <v>0.4529</v>
       </c>
       <c r="I12" t="n">
-        <v>5.398154117021926</v>
+        <v>0.3671</v>
       </c>
       <c r="J12" t="n">
-        <v>3.784632462602251</v>
+        <v>2.3474</v>
       </c>
       <c r="K12" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="M12" t="n">
-        <v>9.1828</v>
+        <v>2.7145</v>
       </c>
       <c r="N12" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0554</v>
+        <v>2.5568</v>
       </c>
       <c r="C13" t="n">
-        <v>1.54155</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4531254339769345</v>
+        <v>0.6115</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6471</v>
+        <v>2.5568</v>
       </c>
       <c r="F13" t="n">
-        <v>3.479850033945679</v>
+        <v>1.891</v>
       </c>
       <c r="G13" t="n">
-        <v>2.167269815048107</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.479850033945679</v>
+        <v>1.891</v>
       </c>
       <c r="I13" t="n">
-        <v>4.678066437386769</v>
+        <v>1.5327</v>
       </c>
       <c r="J13" t="n">
-        <v>2.167269815048107</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>160</v>
       </c>
       <c r="M13" t="n">
-        <v>6.8453</v>
+        <v>2.1985</v>
       </c>
       <c r="N13" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9859</v>
+        <v>2.504</v>
       </c>
       <c r="C14" t="n">
-        <v>1.489425</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4348565811459607</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4194</v>
+        <v>2.504</v>
       </c>
       <c r="F14" t="n">
-        <v>10.0776871141885</v>
+        <v>3.5541</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.65824462273053</v>
+        <v>-1.0501</v>
       </c>
       <c r="H14" t="n">
-        <v>10.0776871141885</v>
+        <v>3.5541</v>
       </c>
       <c r="I14" t="n">
-        <v>9.422647174431967</v>
+        <v>2.8807</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.65824462273053</v>
+        <v>-1.0501</v>
       </c>
       <c r="K14" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L14" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7644</v>
+        <v>1.8306</v>
       </c>
       <c r="N14" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9732</v>
+        <v>2.1297</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4799</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4315523343618948</v>
+        <v>0.439</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3783</v>
+        <v>2.1297</v>
       </c>
       <c r="F15" t="n">
-        <v>5.378262994124296</v>
+        <v>2.5484</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.4187</v>
       </c>
       <c r="H15" t="n">
-        <v>5.378262994124296</v>
+        <v>2.5484</v>
       </c>
       <c r="I15" t="n">
-        <v>5.237814115497478</v>
+        <v>2.0656</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.4187</v>
       </c>
       <c r="K15" t="n">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2378</v>
+        <v>1.6469</v>
       </c>
       <c r="N15" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8765</v>
+        <v>1.9854</v>
       </c>
       <c r="C16" t="n">
-        <v>1.407375</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4066055004307894</v>
+        <v>0.3807</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0674</v>
+        <v>1.9854</v>
       </c>
       <c r="F16" t="n">
-        <v>5.067360646786477</v>
+        <v>1.9854</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.067360646786477</v>
+        <v>1.9854</v>
       </c>
       <c r="I16" t="n">
-        <v>4.601939880035824</v>
+        <v>1.9854</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6019</v>
+        <v>1.9854</v>
       </c>
       <c r="N16" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5423</v>
+        <v>1.4123</v>
       </c>
       <c r="C17" t="n">
-        <v>1.156725</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3236812213063694</v>
+        <v>0.1492</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0339</v>
+        <v>1.4123</v>
       </c>
       <c r="F17" t="n">
-        <v>4.033908742537707</v>
+        <v>2.1496</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.7373</v>
       </c>
       <c r="H17" t="n">
-        <v>4.033908742537707</v>
+        <v>2.1496</v>
       </c>
       <c r="I17" t="n">
-        <v>3.928566560500254</v>
+        <v>1.7423</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.7373</v>
       </c>
       <c r="K17" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9286</v>
+        <v>1.005</v>
       </c>
       <c r="N17" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5084</v>
+        <v>1.4043</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1313</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3155401851090183</v>
+        <v>0.1459</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9325</v>
+        <v>1.4043</v>
       </c>
       <c r="F18" t="n">
-        <v>3.932450286105579</v>
+        <v>1.6701</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.2658</v>
       </c>
       <c r="H18" t="n">
-        <v>3.932450286105579</v>
+        <v>1.6701</v>
       </c>
       <c r="I18" t="n">
-        <v>4.702724053487084</v>
+        <v>1.3536</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.2658</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7027</v>
+        <v>1.0878</v>
       </c>
       <c r="N18" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5055</v>
+        <v>0.9913</v>
       </c>
       <c r="C19" t="n">
-        <v>1.129125</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3148666965019978</v>
+        <v>-0.0209</v>
       </c>
       <c r="E19" t="n">
-        <v>3.9241</v>
+        <v>0.9913</v>
       </c>
       <c r="F19" t="n">
-        <v>4.751146177790744</v>
+        <v>0.9913</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8270893090384939</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.751146177790744</v>
+        <v>0.9913</v>
       </c>
       <c r="I19" t="n">
-        <v>6.387107851380547</v>
+        <v>0.9913</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8270893090384939</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L19" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.56</v>
+        <v>0.9913</v>
       </c>
       <c r="N19" t="n">
-        <v>212</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1213</v>
+        <v>0.9021</v>
       </c>
       <c r="C20" t="n">
-        <v>0.840975</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2261444693612743</v>
+        <v>-0.0569</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8183</v>
+        <v>0.9021</v>
       </c>
       <c r="F20" t="n">
-        <v>2.297216765910893</v>
+        <v>0.9021</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5211307068006605</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.297216765910893</v>
+        <v>0.9021</v>
       </c>
       <c r="I20" t="n">
-        <v>2.576672001351599</v>
+        <v>0.9021</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5211307068006605</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0978</v>
+        <v>0.9021</v>
       </c>
       <c r="N20" t="n">
-        <v>179</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0613</v>
+        <v>0.7738</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7959749999999999</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2128496243376198</v>
+        <v>-0.1088</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6527</v>
+        <v>0.7738</v>
       </c>
       <c r="F21" t="n">
-        <v>2.652659171872988</v>
+        <v>0.7738</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.652659171872988</v>
+        <v>0.7738</v>
       </c>
       <c r="I21" t="n">
-        <v>3.172252205538831</v>
+        <v>0.7738</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1415,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1723</v>
+        <v>0.7738</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1424,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9868</v>
+        <v>0.3435</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7401</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1965212047937233</v>
+        <v>-0.2826</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4492</v>
+        <v>0.3435</v>
       </c>
       <c r="F22" t="n">
-        <v>2.449164653148335</v>
+        <v>0.3435</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.449164653148335</v>
+        <v>0.3435</v>
       </c>
       <c r="I22" t="n">
-        <v>2.928897935723782</v>
+        <v>0.3435</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9289</v>
+        <v>0.3435</v>
       </c>
       <c r="N22" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9392</v>
+        <v>0.3351</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7044</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1862012645245218</v>
+        <v>-0.286</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3206</v>
+        <v>0.3351</v>
       </c>
       <c r="F23" t="n">
-        <v>2.320551392526101</v>
+        <v>0.3351</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.320551392526101</v>
+        <v>0.3351</v>
       </c>
       <c r="I23" t="n">
-        <v>2.117927084793467</v>
+        <v>0.3351</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1179</v>
+        <v>0.3351</v>
       </c>
       <c r="N23" t="n">
-        <v>101</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.889</v>
+        <v>0.2819</v>
       </c>
       <c r="C24" t="n">
-        <v>0.66675</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1754431691676503</v>
+        <v>-0.3075</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1865</v>
+        <v>0.2819</v>
       </c>
       <c r="F24" t="n">
-        <v>2.186477581453626</v>
+        <v>0.2819</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.186477581453626</v>
+        <v>0.2819</v>
       </c>
       <c r="I24" t="n">
-        <v>1.995560238385137</v>
+        <v>0.2819</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9956</v>
+        <v>0.2819</v>
       </c>
       <c r="N24" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
@@ -1566,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8666</v>
+        <v>0.2816</v>
       </c>
       <c r="C25" t="n">
-        <v>0.64995</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1706654852928074</v>
+        <v>-0.3076</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1269</v>
+        <v>0.2816</v>
       </c>
       <c r="F25" t="n">
-        <v>2.126935230884057</v>
+        <v>0.2816</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.126935230884057</v>
+        <v>0.2816</v>
       </c>
       <c r="I25" t="n">
-        <v>2.543551410129387</v>
+        <v>0.2816</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1599,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5436</v>
+        <v>0.2816</v>
       </c>
       <c r="N25" t="n">
         <v>145</v>
@@ -1608,170 +1596,170 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6919</v>
+        <v>0.1067</v>
       </c>
       <c r="C26" t="n">
-        <v>0.518925</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1340496792519018</v>
+        <v>-0.3783</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6706</v>
+        <v>0.1067</v>
       </c>
       <c r="F26" t="n">
-        <v>1.67060718223378</v>
+        <v>0.1067</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.67060718223378</v>
+        <v>0.1067</v>
       </c>
       <c r="I26" t="n">
-        <v>1.626980660877911</v>
+        <v>0.1067</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.627</v>
+        <v>0.1067</v>
       </c>
       <c r="N26" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="C27" t="n">
-        <v>0.506175</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.130553300448164</v>
+        <v>-0.4183</v>
       </c>
       <c r="E27" t="n">
-        <v>1.627</v>
+        <v>0.0076</v>
       </c>
       <c r="F27" t="n">
-        <v>1.627033220893984</v>
+        <v>-0.8562</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.8638</v>
       </c>
       <c r="H27" t="n">
-        <v>1.627033220893984</v>
+        <v>-0.8562</v>
       </c>
       <c r="I27" t="n">
-        <v>1.484965055067773</v>
+        <v>-0.694</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.8638</v>
       </c>
       <c r="K27" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M27" t="n">
-        <v>1.485</v>
+        <v>0.1698000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>101</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6743</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.505725</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1304253850724694</v>
+        <v>-0.4487</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6254</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>1.625439063067229</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.625439063067229</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>1.476147716393697</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4761</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4905</v>
+        <v>-0.1599</v>
       </c>
       <c r="C29" t="n">
-        <v>0.367875</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09328059227710847</v>
+        <v>-0.486</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1625</v>
+        <v>-0.1599</v>
       </c>
       <c r="F29" t="n">
-        <v>1.162518465473668</v>
+        <v>-0.1599</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.162518465473668</v>
+        <v>-0.1599</v>
       </c>
       <c r="I29" t="n">
-        <v>1.055744885837952</v>
+        <v>-0.1599</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1783,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0557</v>
+        <v>-0.1599</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -1792,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4027</v>
+        <v>-0.4112</v>
       </c>
       <c r="C30" t="n">
-        <v>0.302025</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07596304594332892</v>
+        <v>-0.5875</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9467</v>
+        <v>-0.4112</v>
       </c>
       <c r="F30" t="n">
-        <v>0.946696857803033</v>
+        <v>-0.4112</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.946696857803033</v>
+        <v>-0.4112</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8597457982374304</v>
+        <v>-0.4112</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1829,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8597</v>
+        <v>-0.4112</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -1838,461 +1826,461 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3043</v>
+        <v>-0.4386</v>
       </c>
       <c r="C31" t="n">
-        <v>0.228225</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05689525493411795</v>
+        <v>-0.5985</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7091</v>
+        <v>-0.4386</v>
       </c>
       <c r="F31" t="n">
-        <v>0.709062655415573</v>
+        <v>-0.4386</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.709062655415573</v>
+        <v>-0.4386</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6471492109836252</v>
+        <v>-0.4386</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6471</v>
+        <v>-0.4386</v>
       </c>
       <c r="N31" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2522</v>
+        <v>-0.4402</v>
       </c>
       <c r="C32" t="n">
-        <v>0.18915</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04692028719879836</v>
+        <v>-0.5992</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5847</v>
+        <v>-0.4402</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5847486485923251</v>
+        <v>-0.4402</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5847486485923251</v>
+        <v>-0.4402</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5694784224871564</v>
+        <v>-0.4402</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5695</v>
+        <v>-0.4402</v>
       </c>
       <c r="N32" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0339</v>
+        <v>-0.7278</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.025425</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006182293651932662</v>
+        <v>-0.7154</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.077</v>
+        <v>-0.7278</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.336381785893312</v>
+        <v>-0.7278</v>
       </c>
       <c r="G33" t="n">
-        <v>2.259334349187487</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.336381785893312</v>
+        <v>-0.7278</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.140867885365854</v>
+        <v>-0.7278</v>
       </c>
       <c r="J33" t="n">
-        <v>2.259334349187487</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="L33" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8815</v>
+        <v>-0.7278</v>
       </c>
       <c r="N33" t="n">
-        <v>212</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1266</v>
+        <v>-0.9529</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.09494999999999999</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.02329079526562164</v>
+        <v>-0.8063</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2903</v>
+        <v>-0.9529</v>
       </c>
       <c r="F34" t="n">
-        <v>1.779177903975583</v>
+        <v>-0.9529</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.069441708169892</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.779177903975583</v>
+        <v>-0.9529</v>
       </c>
       <c r="I34" t="n">
-        <v>1.9956139788922</v>
+        <v>-0.9529</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.069441708169892</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0738</v>
+        <v>-0.9529</v>
       </c>
       <c r="N34" t="n">
-        <v>179</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>regali</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3106</v>
+        <v>-1.5004</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.23295</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.05809974356595769</v>
+        <v>-1.0275</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7241</v>
+        <v>-1.5004</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7240737122901598</v>
+        <v>-1.5004</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7240737122901598</v>
+        <v>-1.5004</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6608495427360085</v>
+        <v>-1.5004</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-1.5004</v>
       </c>
       <c r="N35" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>regali</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5713</v>
+        <v>-1.5714</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4284750000000001</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1094570227608354</v>
+        <v>-1.0562</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3641</v>
+        <v>-1.5714</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.364118805734357</v>
+        <v>-1.5714</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.364118805734357</v>
+        <v>-1.5714</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.631317334692633</v>
+        <v>-1.5714</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6313</v>
+        <v>-1.5714</v>
       </c>
       <c r="N36" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8226</v>
+        <v>-2.0666</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.61695</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1613301243546152</v>
+        <v>-1.2562</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.0106</v>
+        <v>-2.0666</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.010592386058732</v>
+        <v>-1.9522</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.1144</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.010592386058732</v>
+        <v>-1.9522</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.825925946235485</v>
+        <v>-1.5823</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.1144</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.8259</v>
+        <v>-1.6967</v>
       </c>
       <c r="N37" t="n">
-        <v>100</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6745</v>
+        <v>-2.5916</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.255875</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3558826778224418</v>
+        <v>-1.4683</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.4352</v>
+        <v>-2.5916</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.435222530339076</v>
+        <v>-2.5916</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-4.435222530339076</v>
+        <v>-2.5916</v>
       </c>
       <c r="I38" t="n">
-        <v>-4.319400371488336</v>
+        <v>-2.5916</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-4.3194</v>
+        <v>-2.5916</v>
       </c>
       <c r="N38" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.1953</v>
+        <v>-3.7104</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.646475</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4905486907227226</v>
+        <v>-1.9203</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.1135</v>
+        <v>-3.7104</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.378264291845112</v>
+        <v>-3.7104</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.735246538842913</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.378264291845112</v>
+        <v>-3.7104</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.789228401574723</v>
+        <v>-3.7104</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.735246538842913</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-6.5245</v>
+        <v>-3.7104</v>
       </c>
       <c r="N39" t="n">
-        <v>179</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.1617</v>
+        <v>-4.2774</v>
       </c>
       <c r="C40" t="n">
-        <v>-2.371275</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.7768768150700218</v>
+        <v>-2.1493</v>
       </c>
       <c r="E40" t="n">
-        <v>-9.681900000000001</v>
+        <v>-4.2774</v>
       </c>
       <c r="F40" t="n">
-        <v>4.568446169354082</v>
+        <v>-3.5937</v>
       </c>
       <c r="G40" t="n">
-        <v>-14.25034913406013</v>
+        <v>-0.6837</v>
       </c>
       <c r="H40" t="n">
-        <v>4.568446169354082</v>
+        <v>-3.5937</v>
       </c>
       <c r="I40" t="n">
-        <v>4.231012495467973</v>
+        <v>-2.9128</v>
       </c>
       <c r="J40" t="n">
-        <v>-14.25034913406013</v>
+        <v>-0.6837</v>
       </c>
       <c r="K40" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L40" t="n">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="M40" t="n">
-        <v>-10.0193</v>
+        <v>-3.5965</v>
       </c>
       <c r="N40" t="n">
-        <v>258</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.8299</v>
+        <v>-4.3332</v>
       </c>
       <c r="C41" t="n">
-        <v>-4.372425</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.886303315798474</v>
+        <v>-2.1719</v>
       </c>
       <c r="E41" t="n">
-        <v>-23.5082</v>
+        <v>-4.3332</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.296176818573686</v>
+        <v>-2.4441</v>
       </c>
       <c r="G41" t="n">
-        <v>-19.21206195402759</v>
+        <v>-1.8891</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.296176818573686</v>
+        <v>-2.4441</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.016929470195524</v>
+        <v>-1.981</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.21206195402759</v>
+        <v>-1.8891</v>
       </c>
       <c r="K41" t="n">
         <v>106</v>
@@ -2335,7 +2323,7 @@
         <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-23.229</v>
+        <v>-3.8701</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>1.103145145272958</v>
+        <v>0.9101</v>
       </c>
       <c r="J2" t="n">
-        <v>24.26919319600507</v>
+        <v>20.0222</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.217178621846721</v>
+        <v>0.3068</v>
       </c>
       <c r="J3" t="n">
-        <v>4.777929680627861</v>
+        <v>6.7496</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1012910086068027</v>
+        <v>-0.1128</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.228402189349659</v>
+        <v>-2.4816</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1738929554058843</v>
+        <v>-0.1926</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.825645018929456</v>
+        <v>-4.2372</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.285027888416882</v>
+        <v>-0.2923</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.270613545171405</v>
+        <v>-6.4306</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2288166259745629</v>
+        <v>0.4631</v>
       </c>
       <c r="J7" t="n">
-        <v>5.033965771440383</v>
+        <v>10.1882</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2288166259745629</v>
+        <v>0.4631</v>
       </c>
       <c r="J8" t="n">
-        <v>5.033965771440383</v>
+        <v>10.1882</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1262069214566612</v>
+        <v>0.1878</v>
       </c>
       <c r="J9" t="n">
-        <v>2.776552272046545</v>
+        <v>4.1316</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01942406072340602</v>
+        <v>-0.3719</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4273293359149325</v>
+        <v>-8.181800000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1141156545631458</v>
+        <v>-0.5861</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.510544400389208</v>
+        <v>-12.8942</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2486349234848061</v>
+        <v>0.3715</v>
       </c>
       <c r="J12" t="n">
-        <v>4.724063546211317</v>
+        <v>7.0585</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1286947045176342</v>
+        <v>0.1557</v>
       </c>
       <c r="J13" t="n">
-        <v>2.445199385835049</v>
+        <v>2.9583</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1108375477780814</v>
+        <v>0.1141</v>
       </c>
       <c r="J14" t="n">
-        <v>2.105913407783547</v>
+        <v>2.1679</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.01545689321748484</v>
+        <v>-0.2623</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2936809711322119</v>
+        <v>-4.9837</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.234557051472382</v>
+        <v>-0.6012</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.456583977975258</v>
+        <v>-11.4228</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6885329667357919</v>
+        <v>1.6078</v>
       </c>
       <c r="J17" t="n">
-        <v>13.08212636798005</v>
+        <v>30.5482</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1703844490959082</v>
+        <v>0.6314</v>
       </c>
       <c r="J18" t="n">
-        <v>3.237304532822256</v>
+        <v>11.9966</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1307147350938916</v>
+        <v>0.524</v>
       </c>
       <c r="J19" t="n">
-        <v>2.483579966783941</v>
+        <v>9.956</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01597491009176304</v>
+        <v>0.2619</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3035232917434977</v>
+        <v>4.9761</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1027716452384044</v>
+        <v>-0.0468</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.952661259529683</v>
+        <v>-0.8892</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2441364280869814</v>
+        <v>0.2238</v>
       </c>
       <c r="J22" t="n">
-        <v>4.638592133652646</v>
+        <v>4.2522</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>0.84</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05234185202633558</v>
+        <v>-0.217</v>
       </c>
       <c r="J23" t="n">
-        <v>0.994495188500376</v>
+        <v>-4.123</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.02934891780589279</v>
+        <v>-0.4179</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5576294383119629</v>
+        <v>-7.9401</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.06372320832389243</v>
+        <v>-0.4784</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.210740958153956</v>
+        <v>-9.089600000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1355001020120633</v>
+        <v>-0.5901</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.574501938229203</v>
+        <v>-11.2119</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.88</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8520631200837845</v>
+        <v>1.8661</v>
       </c>
       <c r="J27" t="n">
-        <v>16.1891992815919</v>
+        <v>35.4559</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.47</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3901048770110703</v>
+        <v>1.1042</v>
       </c>
       <c r="J28" t="n">
-        <v>7.411992663210336</v>
+        <v>20.9798</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2131705212733189</v>
+        <v>0.6983</v>
       </c>
       <c r="J29" t="n">
-        <v>4.050239904193059</v>
+        <v>13.2677</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1566686065931995</v>
+        <v>-0.2592</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.976703525270791</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1920429824818219</v>
+        <v>-0.3619</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.648816667154616</v>
+        <v>-6.8761</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9281900049412053</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>27.84570014823616</v>
+        <v>24.813</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2157835894988855</v>
+        <v>0.3426</v>
       </c>
       <c r="J33" t="n">
-        <v>6.473507684966565</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.03077190146449503</v>
+        <v>0.0595</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9231570439348509</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1742180586633857</v>
+        <v>-0.1407</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.226541759901572</v>
+        <v>-4.221</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2112437236888955</v>
+        <v>-0.18</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.337311710666866</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3272166425114836</v>
+        <v>0.7095</v>
       </c>
       <c r="J37" t="n">
-        <v>9.816499275344508</v>
+        <v>21.285</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2206640200479111</v>
+        <v>0.4873</v>
       </c>
       <c r="J38" t="n">
-        <v>6.619920601437334</v>
+        <v>14.619</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1506945983508442</v>
+        <v>0.318</v>
       </c>
       <c r="J39" t="n">
-        <v>4.520837950525325</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.06927867441978018</v>
+        <v>-0.438</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.078360232593405</v>
+        <v>-13.14</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1679183035514915</v>
+        <v>-0.6539</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.037549106544745</v>
+        <v>-19.617</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.17</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2690133387172999</v>
+        <v>0.3728</v>
       </c>
       <c r="J42" t="n">
-        <v>5.649280113063297</v>
+        <v>7.8288</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1389260974732303</v>
+        <v>0.1323</v>
       </c>
       <c r="J43" t="n">
-        <v>2.917448046937837</v>
+        <v>2.7783</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.005821527973389612</v>
+        <v>-0.2789</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.1222520874411819</v>
+        <v>-5.8569</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.04968132617959302</v>
+        <v>-0.3584</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.043307849771453</v>
+        <v>-7.5264</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1500661600771892</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.151389361620973</v>
+        <v>-10.8066</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.87</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8446956473809415</v>
+        <v>1.8626</v>
       </c>
       <c r="J47" t="n">
-        <v>17.73860859499977</v>
+        <v>39.1146</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.79</v>
       </c>
       <c r="I48" t="n">
-        <v>0.758416778356778</v>
+        <v>1.7247</v>
       </c>
       <c r="J48" t="n">
-        <v>15.92675234549234</v>
+        <v>36.2187</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09813547363463414</v>
+        <v>-0.0155</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.060844946327317</v>
+        <v>-0.3255</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2367372057076379</v>
+        <v>-0.4719</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.971481319860396</v>
+        <v>-9.9099</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.325870468957325</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.843279848103825</v>
+        <v>-14.2359</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>2.06</v>
       </c>
       <c r="I52" t="n">
-        <v>1.029920612137293</v>
+        <v>1.978</v>
       </c>
       <c r="J52" t="n">
-        <v>21.62833285488315</v>
+        <v>41.538</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>0.367170426331871</v>
+        <v>1.1043</v>
       </c>
       <c r="J53" t="n">
-        <v>7.71057895296929</v>
+        <v>23.1903</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.005468121221544428</v>
+        <v>0.2865</v>
       </c>
       <c r="J54" t="n">
-        <v>0.114830545652433</v>
+        <v>6.0165</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.186563744142741</v>
+        <v>-0.2842</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.91783862699756</v>
+        <v>-5.9682</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4366017830958206</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.168637445012232</v>
+        <v>-18.0684</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2208544631669664</v>
+        <v>0.4217</v>
       </c>
       <c r="J57" t="n">
-        <v>4.637943726506294</v>
+        <v>8.855700000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1147463473709066</v>
+        <v>0.159</v>
       </c>
       <c r="J58" t="n">
-        <v>2.40967329478904</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08210902593548078</v>
+        <v>0.0206</v>
       </c>
       <c r="J59" t="n">
-        <v>1.724289544645096</v>
+        <v>0.4326</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.09825872077246227</v>
+        <v>-0.5113</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.063433136221708</v>
+        <v>-10.7373</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1892137738142742</v>
+        <v>-0.6902</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.973489250099759</v>
+        <v>-14.4942</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3732490968251518</v>
+        <v>1.0311</v>
       </c>
       <c r="J62" t="n">
-        <v>8.211480130153339</v>
+        <v>22.6842</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2534931512848211</v>
+        <v>0.8091</v>
       </c>
       <c r="J63" t="n">
-        <v>5.576849328266065</v>
+        <v>17.8002</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1507274166218808</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>3.316003165681377</v>
+        <v>12.8964</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.01417169348026832</v>
+        <v>0.0968</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.3117772565659032</v>
+        <v>2.1296</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1993954524236741</v>
+        <v>-0.4945</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.38669995332083</v>
+        <v>-10.879</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2108228755306774</v>
+        <v>0.4557</v>
       </c>
       <c r="J67" t="n">
-        <v>4.638103261674901</v>
+        <v>10.0254</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08408917580904163</v>
+        <v>0.1381</v>
       </c>
       <c r="J68" t="n">
-        <v>1.849961867798916</v>
+        <v>3.0382</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.05628375960258388</v>
+        <v>0.0065</v>
       </c>
       <c r="J69" t="n">
-        <v>1.238242711256845</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0002731169067356765</v>
+        <v>-0.226</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.006008571948184882</v>
+        <v>-4.972</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.08584284490856268</v>
+        <v>-0.4248</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.888542587988379</v>
+        <v>-9.345599999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4699421814302009</v>
+        <v>1.2092</v>
       </c>
       <c r="J72" t="n">
-        <v>14.09826544290603</v>
+        <v>36.276</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2503628813222509</v>
+        <v>0.7759</v>
       </c>
       <c r="J73" t="n">
-        <v>7.510886439667527</v>
+        <v>23.277</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1964671574482704</v>
+        <v>0.6542</v>
       </c>
       <c r="J74" t="n">
-        <v>5.894014723448111</v>
+        <v>19.626</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.05056700972399265</v>
+        <v>-0.203</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.51701029171978</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.287266362951581</v>
+        <v>-0.8097</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.61799088854743</v>
+        <v>-24.291</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1290485384272289</v>
+        <v>0.2837</v>
       </c>
       <c r="J77" t="n">
-        <v>3.871456152816867</v>
+        <v>8.510999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08784142888295848</v>
+        <v>0.0963</v>
       </c>
       <c r="J78" t="n">
-        <v>2.635242866488754</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>0.05613723259866784</v>
+        <v>-0.1461</v>
       </c>
       <c r="J79" t="n">
-        <v>1.684116977960035</v>
+        <v>-4.383</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>0.04560656780494006</v>
+        <v>-0.2053</v>
       </c>
       <c r="J80" t="n">
-        <v>1.368197034148202</v>
+        <v>-6.159</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.02463441952649278</v>
+        <v>-0.4679</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.7390325857947835</v>
+        <v>-14.037</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>2.15</v>
       </c>
       <c r="I82" t="n">
-        <v>1.011999176278022</v>
+        <v>2.0466</v>
       </c>
       <c r="J82" t="n">
-        <v>19.22798434928242</v>
+        <v>38.8854</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.46</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3161409290687995</v>
+        <v>1.0823</v>
       </c>
       <c r="J83" t="n">
-        <v>6.00667765230719</v>
+        <v>20.5637</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1048648200573073</v>
+        <v>0.0414</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.992431581088838</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.182108239190006</v>
+        <v>-0.2597</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.460056544610114</v>
+        <v>-4.9343</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2148063981768576</v>
+        <v>-0.3625</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.081321565360295</v>
+        <v>-6.8875</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1578087860516984</v>
+        <v>0.3535</v>
       </c>
       <c r="J87" t="n">
-        <v>2.99836693498227</v>
+        <v>6.7165</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.119380579093858</v>
+        <v>0.2005</v>
       </c>
       <c r="J88" t="n">
-        <v>2.268231002783303</v>
+        <v>3.8095</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>0.04205646215262659</v>
+        <v>-0.2134</v>
       </c>
       <c r="J89" t="n">
-        <v>0.7990727808999052</v>
+        <v>-4.0546</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.004569667906032387</v>
+        <v>-0.44</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.08682369021461536</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.132168751947291</v>
+        <v>-0.8363</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.511206286998529</v>
+        <v>-15.8897</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.16</v>
       </c>
       <c r="I92" t="n">
-        <v>0.04324189269096766</v>
+        <v>0.3564</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8648378538193533</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.03895351180074648</v>
+        <v>0.3101</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7790702360149295</v>
+        <v>6.202</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>0.004742228091634144</v>
+        <v>-0.2464</v>
       </c>
       <c r="J94" t="n">
-        <v>0.09484456183268289</v>
+        <v>-4.928</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.004728582940702674</v>
+        <v>-0.3597</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.09457165881405348</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0331559838295399</v>
+        <v>-0.6317</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.6631196765907978</v>
+        <v>-12.634</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.93</v>
       </c>
       <c r="I97" t="n">
-        <v>0.120282415639047</v>
+        <v>1.963</v>
       </c>
       <c r="J97" t="n">
-        <v>2.40564831278094</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03556592348955814</v>
+        <v>0.7776</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7113184697911628</v>
+        <v>15.552</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.02147584910270876</v>
+        <v>0.4454</v>
       </c>
       <c r="J99" t="n">
-        <v>0.4295169820541751</v>
+        <v>8.907999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.005001081760535108</v>
+        <v>-0.1902</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.1000216352107022</v>
+        <v>-3.804</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.04197185448066684</v>
+        <v>-0.9167</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.8394370896133369</v>
+        <v>-18.334</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.27</v>
       </c>
       <c r="I102" t="n">
-        <v>0.07967824350903387</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>1.195173652635508</v>
+        <v>9.7155</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>0.64</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.006076627317788894</v>
+        <v>-0.45</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.0911494097668334</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>0.52</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.01989126758885157</v>
+        <v>-0.6574</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.2983690138327736</v>
+        <v>-9.861000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.35</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.04303989267310764</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.6455983900966146</v>
+        <v>-13.239</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.31</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.04847272917304614</v>
+        <v>-0.9319</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.7270909375956921</v>
+        <v>-13.9785</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>2.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1496405302065858</v>
+        <v>2.0593</v>
       </c>
       <c r="J107" t="n">
-        <v>2.244607953098786</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>2.28</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1287704285734882</v>
+        <v>2.0593</v>
       </c>
       <c r="J108" t="n">
-        <v>1.931556428602323</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.43</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0200526854370415</v>
+        <v>0.8475</v>
       </c>
       <c r="J109" t="n">
-        <v>0.3007902815556225</v>
+        <v>12.7125</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.01042148854463226</v>
+        <v>0.3807</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.1563223281694839</v>
+        <v>5.7105</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.07521634898991601</v>
+        <v>-0.9941</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.12824523484874</v>
+        <v>-14.9115</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.72</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1328882419945665</v>
+        <v>1.6709</v>
       </c>
       <c r="J112" t="n">
-        <v>3.189317807869596</v>
+        <v>40.1016</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0607578614895008</v>
+        <v>0.9176</v>
       </c>
       <c r="J113" t="n">
-        <v>1.458188675748019</v>
+        <v>22.0224</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.02513660936282114</v>
+        <v>0.4403</v>
       </c>
       <c r="J114" t="n">
-        <v>0.6032786247077074</v>
+        <v>10.5672</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.95</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.009821653394585447</v>
+        <v>-0.3063</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.2357196814700507</v>
+        <v>-7.3512</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.09019409988542894</v>
+        <v>-1.2936</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.164658397250295</v>
+        <v>-31.0464</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.53</v>
       </c>
       <c r="I117" t="n">
-        <v>0.08368026564311791</v>
+        <v>0.8048</v>
       </c>
       <c r="J117" t="n">
-        <v>2.00832637543483</v>
+        <v>19.3152</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0133939143742708</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>0.3214539449824992</v>
+        <v>-1.9464</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.005205959513736428</v>
+        <v>-0.3493</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.1249430283296743</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.007857193427010883</v>
+        <v>-0.3788</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.1885726422482612</v>
+        <v>-9.091200000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.01051358148313302</v>
+        <v>-0.4075</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.2523259555951924</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>2.89</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2574813548473425</v>
+        <v>2.0593</v>
       </c>
       <c r="J122" t="n">
-        <v>3.862220322710138</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.85</v>
       </c>
       <c r="I123" t="n">
-        <v>0.08833754751362523</v>
+        <v>1.6787</v>
       </c>
       <c r="J123" t="n">
-        <v>1.325063212704378</v>
+        <v>25.1805</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>0.04069477324836569</v>
+        <v>1.1154</v>
       </c>
       <c r="J124" t="n">
-        <v>0.6104215987254853</v>
+        <v>16.731</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.05733086937270629</v>
+        <v>-0.0331</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.8599630405905944</v>
+        <v>-0.4965</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.91</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.08238289121651621</v>
+        <v>-0.5391</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.235743368247743</v>
+        <v>-8.086499999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>0.92</v>
       </c>
       <c r="I127" t="n">
-        <v>0.02724869660379574</v>
+        <v>-0.0111</v>
       </c>
       <c r="J127" t="n">
-        <v>0.4087304490569361</v>
+        <v>-0.1665</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.72</v>
       </c>
       <c r="I128" t="n">
-        <v>0.00175485760774621</v>
+        <v>-0.3357</v>
       </c>
       <c r="J128" t="n">
-        <v>0.02632286411619314</v>
+        <v>-5.0355</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0006187961951668007</v>
+        <v>-0.3677</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.009281942927502011</v>
+        <v>-5.5155</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.009610437371683368</v>
+        <v>-0.534</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.1441565605752505</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.27</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.05156809908140476</v>
+        <v>-0.984</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.7735214862210714</v>
+        <v>-14.76</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1386344168945521</v>
+        <v>1.0402</v>
       </c>
       <c r="J132" t="n">
-        <v>2.356785087207386</v>
+        <v>17.6834</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>0.112205589676271</v>
+        <v>0.8975</v>
       </c>
       <c r="J133" t="n">
-        <v>1.907495024496606</v>
+        <v>15.2575</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.38</v>
       </c>
       <c r="I134" t="n">
-        <v>0.04754386605347991</v>
+        <v>0.5175</v>
       </c>
       <c r="J134" t="n">
-        <v>0.8082457229091585</v>
+        <v>8.797499999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.03492056834571687</v>
+        <v>-0.21</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.5936496618771868</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.07123226289355562</v>
+        <v>-0.4876</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.210948469190446</v>
+        <v>-8.289199999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.01</v>
       </c>
       <c r="I137" t="n">
-        <v>0.03408794681706648</v>
+        <v>0.1388</v>
       </c>
       <c r="J137" t="n">
-        <v>0.5794950958901303</v>
+        <v>2.3596</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.84</v>
       </c>
       <c r="I138" t="n">
-        <v>0.01007476287284636</v>
+        <v>-0.2139</v>
       </c>
       <c r="J138" t="n">
-        <v>0.171270968838388</v>
+        <v>-3.6363</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>0.003939575839628265</v>
+        <v>-0.3015</v>
       </c>
       <c r="J139" t="n">
-        <v>0.06697278927368051</v>
+        <v>-5.1255</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.64</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0147622497562023</v>
+        <v>-0.5474</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.250958245855439</v>
+        <v>-9.3058</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.01896262919706678</v>
+        <v>-0.5884</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.3223646963501352</v>
+        <v>-10.0028</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.0456261364345656</v>
+        <v>0.4848</v>
       </c>
       <c r="J142" t="n">
-        <v>0.8668965922567464</v>
+        <v>9.2112</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>0.93</v>
       </c>
       <c r="I143" t="n">
-        <v>0.01521896631149307</v>
+        <v>-0.0848</v>
       </c>
       <c r="J143" t="n">
-        <v>0.2891603599183684</v>
+        <v>-1.6112</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>0.00674854859878091</v>
+        <v>-0.2782</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1282224233768373</v>
+        <v>-5.2858</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0112351376937304</v>
+        <v>-0.5649</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.2134676161808776</v>
+        <v>-10.7331</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.01820123109636028</v>
+        <v>-0.6554</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.3458233908308452</v>
+        <v>-12.4526</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>2.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2587362024113594</v>
+        <v>2.0593</v>
       </c>
       <c r="J147" t="n">
-        <v>4.915987845815827</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>0.08255930854781567</v>
+        <v>1.1734</v>
       </c>
       <c r="J148" t="n">
-        <v>1.568626862408498</v>
+        <v>22.2946</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.01636965854117793</v>
+        <v>0.5642</v>
       </c>
       <c r="J149" t="n">
-        <v>0.3110235122823807</v>
+        <v>10.7198</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.04117818652528989</v>
+        <v>0.0536</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.7823855439805079</v>
+        <v>1.0184</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.08877253293570909</v>
+        <v>-0.5478</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.686678125778473</v>
+        <v>-10.4082</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.05282809286448704</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>1.479186600205637</v>
+        <v>17.1472</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0250248340263263</v>
+        <v>0.2109</v>
       </c>
       <c r="J153" t="n">
-        <v>0.7006953527371366</v>
+        <v>5.9052</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.01725380669209007</v>
+        <v>0.029</v>
       </c>
       <c r="J154" t="n">
-        <v>0.483106587378522</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.00691027995554569</v>
+        <v>-0.4574</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.1934878387552793</v>
+        <v>-12.8072</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.02200349986571416</v>
+        <v>-0.6511</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.6160979962399965</v>
+        <v>-18.2308</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1546375884254347</v>
+        <v>1.4976</v>
       </c>
       <c r="J157" t="n">
-        <v>4.32985247591217</v>
+        <v>41.9328</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.05303093457006078</v>
+        <v>0.7502</v>
       </c>
       <c r="J158" t="n">
-        <v>1.484866167961702</v>
+        <v>21.0056</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.17</v>
       </c>
       <c r="I159" t="n">
-        <v>0.02654651625507603</v>
+        <v>0.442</v>
       </c>
       <c r="J159" t="n">
-        <v>0.7433024551421287</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.98</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.02556501117409062</v>
+        <v>-0.2201</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.7158203128745373</v>
+        <v>-6.1628</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.05311898106329482</v>
+        <v>-0.5274</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.487331469772255</v>
+        <v>-14.7672</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.02470720026216577</v>
+        <v>0.0639</v>
       </c>
       <c r="J162" t="n">
-        <v>0.5929728062919785</v>
+        <v>1.5336</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>0.02182450921147369</v>
+        <v>-0.0191</v>
       </c>
       <c r="J163" t="n">
-        <v>0.5237882210753685</v>
+        <v>-0.4584</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>0.92</v>
       </c>
       <c r="I164" t="n">
-        <v>0.017200172946993</v>
+        <v>-0.12</v>
       </c>
       <c r="J164" t="n">
-        <v>0.4128041507278319</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>0.009273759743603229</v>
+        <v>-0.3142</v>
       </c>
       <c r="J165" t="n">
-        <v>0.2225702338464775</v>
+        <v>-7.5408</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.006131816266204754</v>
+        <v>-0.5467</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.1471635903889141</v>
+        <v>-13.1208</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.06860434642452991</v>
+        <v>1.0816</v>
       </c>
       <c r="J167" t="n">
-        <v>1.646504314188718</v>
+        <v>25.9584</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.04548463736287417</v>
+        <v>0.7469</v>
       </c>
       <c r="J168" t="n">
-        <v>1.09163129670898</v>
+        <v>17.9256</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.02923706843693205</v>
+        <v>0.4613</v>
       </c>
       <c r="J169" t="n">
-        <v>0.7016896424863693</v>
+        <v>11.0712</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.88</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.008901924532781998</v>
+        <v>-0.503</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.2136461887867679</v>
+        <v>-12.072</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.01030239127363973</v>
+        <v>-0.5299</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.2472573905673535</v>
+        <v>-12.7176</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.03061371791601133</v>
+        <v>0.3516</v>
       </c>
       <c r="J172" t="n">
-        <v>1.224548716640453</v>
+        <v>14.064</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.02874801495261351</v>
+        <v>0.3215</v>
       </c>
       <c r="J173" t="n">
-        <v>1.14992059810454</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.01559420807482969</v>
+        <v>0.034</v>
       </c>
       <c r="J174" t="n">
-        <v>0.6237683229931875</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>0.01424900477899551</v>
+        <v>-0.0453</v>
       </c>
       <c r="J175" t="n">
-        <v>0.5699601911598202</v>
+        <v>-1.812</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.01352917754415693</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.5411671017662774</v>
+        <v>-20.868</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>0.08575545573317926</v>
+        <v>1.4029</v>
       </c>
       <c r="J177" t="n">
-        <v>3.430218229327171</v>
+        <v>56.116</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.15</v>
       </c>
       <c r="I178" t="n">
-        <v>0.02178663107748698</v>
+        <v>0.4188</v>
       </c>
       <c r="J178" t="n">
-        <v>0.8714652430994794</v>
+        <v>16.752</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.11</v>
       </c>
       <c r="I179" t="n">
-        <v>0.01685956618827851</v>
+        <v>0.2932</v>
       </c>
       <c r="J179" t="n">
-        <v>0.6743826475311403</v>
+        <v>11.728</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0003713527634236595</v>
+        <v>-0.1632</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.01485411053694638</v>
+        <v>-6.528</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.009459864870943642</v>
+        <v>-0.3741</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.3783945948377457</v>
+        <v>-14.964</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1163240912774543</v>
+        <v>0.6216</v>
       </c>
       <c r="J182" t="n">
-        <v>2.559130008103994</v>
+        <v>13.6752</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08452807013505437</v>
+        <v>0.4962</v>
       </c>
       <c r="J183" t="n">
-        <v>1.859617542971196</v>
+        <v>10.9164</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.01812491762902659</v>
+        <v>0.13</v>
       </c>
       <c r="J184" t="n">
-        <v>0.398748187838585</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.005375237724503008</v>
+        <v>-0.0499</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.1182552299390662</v>
+        <v>-1.0978</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.07683218154708477</v>
+        <v>-0.4472</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.690307994035865</v>
+        <v>-9.8384</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0601412423211269</v>
+        <v>0.5705</v>
       </c>
       <c r="J187" t="n">
-        <v>1.323107331064792</v>
+        <v>12.551</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.02397839681583269</v>
+        <v>0.15</v>
       </c>
       <c r="J188" t="n">
-        <v>0.5275247299483191</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>0.01305398244828057</v>
+        <v>-0.119</v>
       </c>
       <c r="J189" t="n">
-        <v>0.2871876138621725</v>
+        <v>-2.618</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>0.005980559542229901</v>
+        <v>-0.2335</v>
       </c>
       <c r="J190" t="n">
-        <v>0.1315723099290578</v>
+        <v>-5.137</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.03080675041842507</v>
+        <v>-0.6284</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.6777485092053516</v>
+        <v>-13.8248</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.07149108684726629</v>
+        <v>0.5916</v>
       </c>
       <c r="J192" t="n">
-        <v>1.572803910639859</v>
+        <v>13.0152</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>0.99</v>
       </c>
       <c r="I193" t="n">
-        <v>0.01669172113977658</v>
+        <v>-0.0202</v>
       </c>
       <c r="J193" t="n">
-        <v>0.3672178650750847</v>
+        <v>-0.4444</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>0.01465113561208692</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>0.3223249834659123</v>
+        <v>-1.7534</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>0.001878737394729334</v>
+        <v>-0.2545</v>
       </c>
       <c r="J195" t="n">
-        <v>0.04133222268404536</v>
+        <v>-5.599</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.02670289700880593</v>
+        <v>-0.5161</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.5874637341937305</v>
+        <v>-11.3542</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.06537085585674908</v>
+        <v>0.7461</v>
       </c>
       <c r="J197" t="n">
-        <v>1.43815882884848</v>
+        <v>16.4142</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.04953419262653379</v>
+        <v>0.597</v>
       </c>
       <c r="J198" t="n">
-        <v>1.089752237783743</v>
+        <v>13.134</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>0.003743892885819861</v>
+        <v>-0.1256</v>
       </c>
       <c r="J199" t="n">
-        <v>0.08236564348803693</v>
+        <v>-2.7632</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.98</v>
       </c>
       <c r="I200" t="n">
-        <v>0.001398028648885562</v>
+        <v>-0.1692</v>
       </c>
       <c r="J200" t="n">
-        <v>0.03075663027548237</v>
+        <v>-3.7224</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.96</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.003348273001382848</v>
+        <v>-0.2442</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.07366200603042264</v>
+        <v>-5.3724</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.04536133849534488</v>
+        <v>0.3427</v>
       </c>
       <c r="J202" t="n">
-        <v>0.9525881084022424</v>
+        <v>7.1967</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.04</v>
       </c>
       <c r="I203" t="n">
-        <v>0.02794879237829768</v>
+        <v>0.1534</v>
       </c>
       <c r="J203" t="n">
-        <v>0.5869246399442513</v>
+        <v>3.2214</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.83</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.001485766879506582</v>
+        <v>-0.3116</v>
       </c>
       <c r="J204" t="n">
-        <v>-0.03120110446963821</v>
+        <v>-6.5436</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.009178669567152138</v>
+        <v>-0.3884</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.1927520609101949</v>
+        <v>-8.1564</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.01546426884404554</v>
+        <v>-0.446</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.3247496457249563</v>
+        <v>-9.366</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.54</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1172581508527253</v>
+        <v>1.2985</v>
       </c>
       <c r="J207" t="n">
-        <v>2.462421167907231</v>
+        <v>27.2685</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>0.09378814667056296</v>
+        <v>1.1175</v>
       </c>
       <c r="J208" t="n">
-        <v>1.969551080081822</v>
+        <v>23.4675</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.06225744067858804</v>
+        <v>0.858</v>
       </c>
       <c r="J209" t="n">
-        <v>1.307406254250349</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.03002290556275268</v>
+        <v>0.4868</v>
       </c>
       <c r="J210" t="n">
-        <v>0.6304810168178063</v>
+        <v>10.2228</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.52</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1392948181121663</v>
+        <v>-1.323</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.925191180355491</v>
+        <v>-27.783</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.03738227414006171</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>0.8597923052214194</v>
+        <v>12.7627</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.02483840259022115</v>
+        <v>0.3047</v>
       </c>
       <c r="J213" t="n">
-        <v>0.5712832595750865</v>
+        <v>7.0081</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.01884861589804034</v>
+        <v>0.15</v>
       </c>
       <c r="J214" t="n">
-        <v>0.4335181656549277</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.8</v>
       </c>
       <c r="I215" t="n">
-        <v>0.001967875593870995</v>
+        <v>-0.3863</v>
       </c>
       <c r="J215" t="n">
-        <v>0.04526113865903288</v>
+        <v>-8.8849</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.003723138688409997</v>
+        <v>-0.4962</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.08563218983342992</v>
+        <v>-11.4126</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.9</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1381700984140423</v>
+        <v>1.9507</v>
       </c>
       <c r="J217" t="n">
-        <v>3.177912263522972</v>
+        <v>44.8661</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.1</v>
       </c>
       <c r="I218" t="n">
-        <v>0.01420172462651118</v>
+        <v>0.258</v>
       </c>
       <c r="J218" t="n">
-        <v>0.3266396664097571</v>
+        <v>5.934</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.00134218129505867</v>
+        <v>-0.1076</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.03087016978634941</v>
+        <v>-2.4748</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.01272414477054198</v>
+        <v>-0.377</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.2926553297224655</v>
+        <v>-8.670999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.02270521202511536</v>
+        <v>-0.5448</v>
       </c>
       <c r="J221" t="n">
-        <v>-0.5222198765776532</v>
+        <v>-12.5304</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.03878563780876595</v>
+        <v>0.5354</v>
       </c>
       <c r="J222" t="n">
-        <v>0.6981414805577872</v>
+        <v>9.6372</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.01893252481024361</v>
+        <v>0.0597</v>
       </c>
       <c r="J223" t="n">
-        <v>0.3407854465843849</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>0.01148091120649804</v>
+        <v>-0.2107</v>
       </c>
       <c r="J224" t="n">
-        <v>0.2066564017169647</v>
+        <v>-3.7926</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>0.001776649608524781</v>
+        <v>-0.4535</v>
       </c>
       <c r="J225" t="n">
-        <v>0.03197969295344606</v>
+        <v>-8.163</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.53</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.01211840925765146</v>
+        <v>-0.7128</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.2181313666377262</v>
+        <v>-12.8304</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1262895470756348</v>
+        <v>1.9475</v>
       </c>
       <c r="J227" t="n">
-        <v>2.273211847361427</v>
+        <v>35.055</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.68</v>
       </c>
       <c r="I228" t="n">
-        <v>0.08464537385698066</v>
+        <v>1.4978</v>
       </c>
       <c r="J228" t="n">
-        <v>1.523616729425652</v>
+        <v>26.9604</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>0.05531733248961043</v>
+        <v>1.1492</v>
       </c>
       <c r="J229" t="n">
-        <v>0.9957119848129878</v>
+        <v>20.6856</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.01</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.02151188315991155</v>
+        <v>-0.1119</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.3872138968784078</v>
+        <v>-2.0142</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.08340364630992024</v>
+        <v>-1.1656</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.501265633578564</v>
+        <v>-20.9808</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>0.06495628704498131</v>
+        <v>0.7783</v>
       </c>
       <c r="J232" t="n">
-        <v>1.234169453854645</v>
+        <v>14.7877</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0214111811817976</v>
+        <v>0.1726</v>
       </c>
       <c r="J233" t="n">
-        <v>0.4068124424541543</v>
+        <v>3.2794</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>0.014764509611247</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J234" t="n">
-        <v>0.280525682613693</v>
+        <v>-0.1672</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.02053654456630529</v>
+        <v>-0.6147</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.3901943467598005</v>
+        <v>-11.6793</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.02053654456630529</v>
+        <v>-0.6147</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.3901943467598005</v>
+        <v>-11.6793</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.66</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1053413788135382</v>
+        <v>1.5043</v>
       </c>
       <c r="J237" t="n">
-        <v>2.001486197457226</v>
+        <v>28.5817</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.04167531194674827</v>
+        <v>0.8304</v>
       </c>
       <c r="J238" t="n">
-        <v>0.7918309269882171</v>
+        <v>15.7776</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I239" t="n">
-        <v>0.02390910826220491</v>
+        <v>0.533</v>
       </c>
       <c r="J239" t="n">
-        <v>0.4542730569818932</v>
+        <v>10.127</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>1.11</v>
       </c>
       <c r="I240" t="n">
-        <v>0.00325875314569932</v>
+        <v>0.2402</v>
       </c>
       <c r="J240" t="n">
-        <v>0.06191630976828709</v>
+        <v>4.5638</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.02753998188217632</v>
+        <v>-0.3452</v>
       </c>
       <c r="J241" t="n">
-        <v>-0.52325965576135</v>
+        <v>-6.5588</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.07133939700588915</v>
+        <v>0.8309</v>
       </c>
       <c r="J242" t="n">
-        <v>1.64080613113545</v>
+        <v>19.1107</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.01825298835346947</v>
+        <v>0.057</v>
       </c>
       <c r="J243" t="n">
-        <v>0.4198187321297978</v>
+        <v>1.311</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>0.87</v>
       </c>
       <c r="I244" t="n">
-        <v>0.006153855930345221</v>
+        <v>-0.2684</v>
       </c>
       <c r="J244" t="n">
-        <v>0.1415386863979401</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>0.001125528477829221</v>
+        <v>-0.3467</v>
       </c>
       <c r="J245" t="n">
-        <v>0.02588715499007209</v>
+        <v>-7.9741</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.02116662722505439</v>
+        <v>-0.6414</v>
       </c>
       <c r="J246" t="n">
-        <v>-0.4868324261762509</v>
+        <v>-14.7522</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.65</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1217502164194525</v>
+        <v>1.5464</v>
       </c>
       <c r="J247" t="n">
-        <v>2.800254977647406</v>
+        <v>35.5672</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.25</v>
       </c>
       <c r="I248" t="n">
-        <v>0.04473632447672367</v>
+        <v>0.7134</v>
       </c>
       <c r="J248" t="n">
-        <v>1.028935462964644</v>
+        <v>16.4082</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1.25</v>
       </c>
       <c r="I249" t="n">
-        <v>0.04473632447672367</v>
+        <v>0.7134</v>
       </c>
       <c r="J249" t="n">
-        <v>1.028935462964644</v>
+        <v>16.4082</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.01786837793771517</v>
+        <v>-0.4535</v>
       </c>
       <c r="J250" t="n">
-        <v>-0.4109726925674489</v>
+        <v>-10.4305</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.07579652741671655</v>
+        <v>-1.1518</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.743320130584481</v>
+        <v>-26.4914</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.8</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1037875955162604</v>
+        <v>1.7664</v>
       </c>
       <c r="J252" t="n">
-        <v>2.075751910325208</v>
+        <v>35.328</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.32</v>
       </c>
       <c r="I253" t="n">
-        <v>0.03818719670529251</v>
+        <v>0.8189</v>
       </c>
       <c r="J253" t="n">
-        <v>0.7637439341058503</v>
+        <v>16.378</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.28</v>
       </c>
       <c r="I254" t="n">
-        <v>0.03290986117367851</v>
+        <v>0.7224</v>
       </c>
       <c r="J254" t="n">
-        <v>0.6581972234735701</v>
+        <v>14.448</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.007692220821796495</v>
+        <v>0.1624</v>
       </c>
       <c r="J255" t="n">
-        <v>0.1538444164359299</v>
+        <v>3.248</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.04606970031629852</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.9213940063259705</v>
+        <v>-19.668</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.06378306961559738</v>
+        <v>0.4982</v>
       </c>
       <c r="J257" t="n">
-        <v>1.275661392311948</v>
+        <v>9.964</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.04</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0311051588026581</v>
+        <v>0.1662</v>
       </c>
       <c r="J258" t="n">
-        <v>0.622103176053162</v>
+        <v>3.324</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I259" t="n">
-        <v>0.01409120468289208</v>
+        <v>-0.1017</v>
       </c>
       <c r="J259" t="n">
-        <v>0.2818240936578417</v>
+        <v>-2.034</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.02640152439673956</v>
+        <v>-0.5604</v>
       </c>
       <c r="J260" t="n">
-        <v>-0.5280304879347911</v>
+        <v>-11.208</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.04817472606938344</v>
+        <v>-0.7356</v>
       </c>
       <c r="J261" t="n">
-        <v>-0.9634945213876689</v>
+        <v>-14.712</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>0.08502436825429027</v>
+        <v>1.5715</v>
       </c>
       <c r="J262" t="n">
-        <v>1.615462996831515</v>
+        <v>29.8585</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.65</v>
       </c>
       <c r="I263" t="n">
-        <v>0.07688504032094939</v>
+        <v>1.4609</v>
       </c>
       <c r="J263" t="n">
-        <v>1.460815766098039</v>
+        <v>27.7571</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.01896613688867957</v>
+        <v>0.4774</v>
       </c>
       <c r="J264" t="n">
-        <v>0.3603566008849118</v>
+        <v>9.070600000000001</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1.12</v>
       </c>
       <c r="I265" t="n">
-        <v>0.0062747215357663</v>
+        <v>0.2465</v>
       </c>
       <c r="J265" t="n">
-        <v>0.1192197091795597</v>
+        <v>4.6835</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.03162915546938029</v>
+        <v>-0.6338</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.6009539539182255</v>
+        <v>-12.0422</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.04900360949775591</v>
+        <v>0.342</v>
       </c>
       <c r="J267" t="n">
-        <v>0.9310685804573623</v>
+        <v>6.498</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.96</v>
       </c>
       <c r="I268" t="n">
-        <v>0.02189626443901173</v>
+        <v>-0.0213</v>
       </c>
       <c r="J268" t="n">
-        <v>0.4160290243412229</v>
+        <v>-0.4047</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.007252492206502401</v>
+        <v>-0.4066</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.1377973519235456</v>
+        <v>-7.7254</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.67</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.01952271839583567</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.3709316495208778</v>
+        <v>-9.9123</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.02420461425132913</v>
+        <v>-0.5624</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.4598876707752534</v>
+        <v>-10.6856</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.51</v>
       </c>
       <c r="I272" t="n">
-        <v>0.08102199196743105</v>
+        <v>1.2682</v>
       </c>
       <c r="J272" t="n">
-        <v>1.782483823283483</v>
+        <v>27.9004</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.03640283489515166</v>
+        <v>0.678</v>
       </c>
       <c r="J273" t="n">
-        <v>0.8008623676933364</v>
+        <v>14.916</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.01521396803714536</v>
+        <v>0.2349</v>
       </c>
       <c r="J274" t="n">
-        <v>0.334707296817198</v>
+        <v>5.1678</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0009620926475613668</v>
+        <v>-0.1025</v>
       </c>
       <c r="J275" t="n">
-        <v>0.02116603824635007</v>
+        <v>-2.255</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.01501442154250885</v>
+        <v>-0.4597</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.3303172739351948</v>
+        <v>-10.1134</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>0.06711106133123398</v>
+        <v>0.6533</v>
       </c>
       <c r="J277" t="n">
-        <v>1.476443349287148</v>
+        <v>14.3726</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.04216095707898451</v>
+        <v>0.4056</v>
       </c>
       <c r="J278" t="n">
-        <v>0.9275410557376593</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>1.16</v>
       </c>
       <c r="I279" t="n">
-        <v>0.03572325851878561</v>
+        <v>0.3323</v>
       </c>
       <c r="J279" t="n">
-        <v>0.7859116874132833</v>
+        <v>7.3106</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.03419468813927001</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.7522831390639403</v>
+        <v>-14.1372</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.04436488615153338</v>
+        <v>-0.738</v>
       </c>
       <c r="J281" t="n">
-        <v>-0.9760274953337342</v>
+        <v>-16.236</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.65</v>
       </c>
       <c r="I282" t="n">
-        <v>0.06897002194594747</v>
+        <v>0.9324</v>
       </c>
       <c r="J282" t="n">
-        <v>1.655280526702739</v>
+        <v>22.3776</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>0.01582433491358679</v>
+        <v>-0.0893</v>
       </c>
       <c r="J283" t="n">
-        <v>0.3797840379260828</v>
+        <v>-2.1432</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>0.01288471347139914</v>
+        <v>-0.1721</v>
       </c>
       <c r="J284" t="n">
-        <v>0.3092331233135793</v>
+        <v>-4.1304</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.75</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.001949604540571113</v>
+        <v>-0.4524</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.04679050897370671</v>
+        <v>-10.8576</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.67</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.008609159487617611</v>
+        <v>-0.5579</v>
       </c>
       <c r="J286" t="n">
-        <v>-0.2066198277028227</v>
+        <v>-13.3896</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1193536530359564</v>
+        <v>0.6768</v>
       </c>
       <c r="J287" t="n">
-        <v>2.864487672862954</v>
+        <v>16.2432</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I288" t="n">
-        <v>0.07721079005436576</v>
+        <v>0.4766</v>
       </c>
       <c r="J288" t="n">
-        <v>1.853058961304778</v>
+        <v>11.4384</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.96</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0004899260160435917</v>
+        <v>-0.1337</v>
       </c>
       <c r="J289" t="n">
-        <v>0.0117582243850462</v>
+        <v>-3.2088</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.02543876678386348</v>
+        <v>-0.3066</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.6105304028127235</v>
+        <v>-7.3584</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.06266550800311663</v>
+        <v>-0.5032</v>
       </c>
       <c r="J291" t="n">
-        <v>-1.503972192074799</v>
+        <v>-12.0768</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>2.45</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1511620593325728</v>
+        <v>2.0593</v>
       </c>
       <c r="J292" t="n">
-        <v>1.965106771323447</v>
+        <v>26.7709</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>2.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.09796497444835932</v>
+        <v>1.9832</v>
       </c>
       <c r="J293" t="n">
-        <v>1.273544667828671</v>
+        <v>25.7816</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.74</v>
       </c>
       <c r="I294" t="n">
-        <v>0.04731686521968302</v>
+        <v>1.3818</v>
       </c>
       <c r="J294" t="n">
-        <v>0.6151192478558792</v>
+        <v>17.9634</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>0.003194566409176333</v>
+        <v>0.8554</v>
       </c>
       <c r="J295" t="n">
-        <v>0.04152936331929233</v>
+        <v>11.1202</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>1.3</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.02180641101310355</v>
+        <v>0.5375</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.2834833431703461</v>
+        <v>6.9875</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>0.79</v>
       </c>
       <c r="I297" t="n">
-        <v>0.02294753295334252</v>
+        <v>-0.1377</v>
       </c>
       <c r="J297" t="n">
-        <v>0.2983179283934527</v>
+        <v>-1.7901</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>0.54</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.008062500177900143</v>
+        <v>-0.5252</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.1048125023127019</v>
+        <v>-6.8276</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.01277347294510928</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.1660551482864206</v>
+        <v>-8.157500000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.01572992313251162</v>
+        <v>-0.6831</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.2044890007226511</v>
+        <v>-8.8803</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.2</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.04733469222767892</v>
+        <v>-1.0458</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.6153509989598259</v>
+        <v>-13.5954</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>2.4</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1574778281354205</v>
+        <v>2.0593</v>
       </c>
       <c r="J302" t="n">
-        <v>2.362167422031308</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>2.28</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1423604885973583</v>
+        <v>2.0593</v>
       </c>
       <c r="J303" t="n">
-        <v>2.135407328960375</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.00409012271072004</v>
+        <v>0.5948</v>
       </c>
       <c r="J304" t="n">
-        <v>0.0613518406608006</v>
+        <v>8.922000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>1.15</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.0188047306235619</v>
+        <v>0.2532</v>
       </c>
       <c r="J305" t="n">
-        <v>-0.2820709593534285</v>
+        <v>3.798</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.08871927288136786</v>
+        <v>-1.1094</v>
       </c>
       <c r="J306" t="n">
-        <v>-1.330789093220518</v>
+        <v>-16.641</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>0.9</v>
       </c>
       <c r="I307" t="n">
-        <v>0.01361817471852018</v>
+        <v>-0.1054</v>
       </c>
       <c r="J307" t="n">
-        <v>0.2042726207778026</v>
+        <v>-1.581</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>0.01084225696202085</v>
+        <v>-0.1401</v>
       </c>
       <c r="J308" t="n">
-        <v>0.1626338544303127</v>
+        <v>-2.1015</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>0.005421207899670662</v>
+        <v>-0.2077</v>
       </c>
       <c r="J309" t="n">
-        <v>0.08131811849505993</v>
+        <v>-3.1155</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.66</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.01618892319279535</v>
+        <v>-0.5152</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.2428338478919303</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.03134296423537043</v>
+        <v>-0.6643</v>
       </c>
       <c r="J311" t="n">
-        <v>-0.4701444635305565</v>
+        <v>-9.964499999999999</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>0.09709835088084366</v>
+        <v>1.5949</v>
       </c>
       <c r="J312" t="n">
-        <v>2.136163719378561</v>
+        <v>35.0878</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>1.57</v>
       </c>
       <c r="I313" t="n">
-        <v>0.07790122969931457</v>
+        <v>1.351</v>
       </c>
       <c r="J313" t="n">
-        <v>1.71382705338492</v>
+        <v>29.722</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.006460518565862331</v>
+        <v>0.1692</v>
       </c>
       <c r="J314" t="n">
-        <v>0.1421314084489713</v>
+        <v>3.7224</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.01465387303395201</v>
+        <v>-0.3656</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.3223852067469442</v>
+        <v>-8.043200000000001</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.03576507312878088</v>
+        <v>-0.7342</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.7868316088331795</v>
+        <v>-16.1524</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I317" t="n">
-        <v>0.05975831295468459</v>
+        <v>0.5505</v>
       </c>
       <c r="J317" t="n">
-        <v>1.314682885003061</v>
+        <v>12.111</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>0.01279929141742025</v>
+        <v>-0.0556</v>
       </c>
       <c r="J318" t="n">
-        <v>0.2815844111832454</v>
+        <v>-1.2232</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>0.91</v>
       </c>
       <c r="I319" t="n">
-        <v>0.006253999802995371</v>
+        <v>-0.1914</v>
       </c>
       <c r="J319" t="n">
-        <v>0.1375879956658982</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.79</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.01030451511444238</v>
+        <v>-0.3857</v>
       </c>
       <c r="J320" t="n">
-        <v>-0.2266993325177323</v>
+        <v>-8.4854</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.01316603380934694</v>
+        <v>-0.4145</v>
       </c>
       <c r="J321" t="n">
-        <v>-0.2896527438056328</v>
+        <v>-9.119</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.8466</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.1905</v>
       </c>
       <c r="D2" t="n">
         <v>2.7485</v>
@@ -545,7 +545,7 @@
         <v>7.7168</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.1377</v>
       </c>
       <c r="D3" t="n">
         <v>2.6961</v>
@@ -591,7 +591,7 @@
         <v>6.2131</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.5263</v>
       </c>
       <c r="D4" t="n">
         <v>2.0886</v>
@@ -637,7 +637,7 @@
         <v>5.6266</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.2878</v>
       </c>
       <c r="D5" t="n">
         <v>1.8517</v>
@@ -683,7 +683,7 @@
         <v>4.8696</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="D6" t="n">
         <v>1.5458</v>
@@ -729,7 +729,7 @@
         <v>4.8401</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.968</v>
       </c>
       <c r="D7" t="n">
         <v>1.5339</v>
@@ -775,7 +775,7 @@
         <v>4.2934</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.7457</v>
       </c>
       <c r="D8" t="n">
         <v>1.3131</v>
@@ -821,7 +821,7 @@
         <v>3.5378</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.4385</v>
       </c>
       <c r="D9" t="n">
         <v>1.0078</v>
@@ -867,7 +867,7 @@
         <v>3.202</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.302</v>
       </c>
       <c r="D10" t="n">
         <v>0.8722</v>
@@ -913,7 +913,7 @@
         <v>2.9754</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.2098</v>
       </c>
       <c r="D11" t="n">
         <v>0.7806</v>
@@ -959,7 +959,7 @@
         <v>2.8003</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.1386</v>
       </c>
       <c r="D12" t="n">
         <v>0.7099</v>
@@ -1005,7 +1005,7 @@
         <v>2.5568</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.0396</v>
       </c>
       <c r="D13" t="n">
         <v>0.6115</v>
@@ -1051,7 +1051,7 @@
         <v>2.504</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.0182</v>
       </c>
       <c r="D14" t="n">
         <v>0.5901999999999999</v>
@@ -1097,7 +1097,7 @@
         <v>2.1297</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.866</v>
       </c>
       <c r="D15" t="n">
         <v>0.439</v>
@@ -1143,7 +1143,7 @@
         <v>1.9854</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.8073</v>
       </c>
       <c r="D16" t="n">
         <v>0.3807</v>
@@ -1189,7 +1189,7 @@
         <v>1.4123</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.5743</v>
       </c>
       <c r="D17" t="n">
         <v>0.1492</v>
@@ -1235,7 +1235,7 @@
         <v>1.4043</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="D18" t="n">
         <v>0.1459</v>
@@ -1281,7 +1281,7 @@
         <v>0.9913</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.4031</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0209</v>
@@ -1327,7 +1327,7 @@
         <v>0.9021</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.3668</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0569</v>
@@ -1373,7 +1373,7 @@
         <v>0.7738</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.3146</v>
       </c>
       <c r="D21" t="n">
         <v>-0.1088</v>
@@ -1419,7 +1419,7 @@
         <v>0.3435</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1397</v>
       </c>
       <c r="D22" t="n">
         <v>-0.2826</v>
@@ -1465,7 +1465,7 @@
         <v>0.3351</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1363</v>
       </c>
       <c r="D23" t="n">
         <v>-0.286</v>
@@ -1511,7 +1511,7 @@
         <v>0.2819</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1146</v>
       </c>
       <c r="D24" t="n">
         <v>-0.3075</v>
@@ -1557,7 +1557,7 @@
         <v>0.2816</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1145</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3076</v>
@@ -1603,7 +1603,7 @@
         <v>0.1067</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0434</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3783</v>
@@ -1649,7 +1649,7 @@
         <v>0.0076</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4183</v>
@@ -1695,7 +1695,7 @@
         <v>-0.06759999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0275</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4487</v>
@@ -1741,7 +1741,7 @@
         <v>-0.1599</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.065</v>
       </c>
       <c r="D29" t="n">
         <v>-0.486</v>
@@ -1787,7 +1787,7 @@
         <v>-0.4112</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.1672</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5875</v>
@@ -1833,7 +1833,7 @@
         <v>-0.4386</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1783</v>
       </c>
       <c r="D31" t="n">
         <v>-0.5985</v>
@@ -1879,7 +1879,7 @@
         <v>-0.4402</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.179</v>
       </c>
       <c r="D32" t="n">
         <v>-0.5992</v>
@@ -1925,7 +1925,7 @@
         <v>-0.7278</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.2959</v>
       </c>
       <c r="D33" t="n">
         <v>-0.7154</v>
@@ -1971,7 +1971,7 @@
         <v>-0.9529</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.3875</v>
       </c>
       <c r="D34" t="n">
         <v>-0.8063</v>
@@ -2017,7 +2017,7 @@
         <v>-1.5004</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.6101</v>
       </c>
       <c r="D35" t="n">
         <v>-1.0275</v>
@@ -2063,7 +2063,7 @@
         <v>-1.5714</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.6389</v>
       </c>
       <c r="D36" t="n">
         <v>-1.0562</v>
@@ -2109,7 +2109,7 @@
         <v>-2.0666</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.8403</v>
       </c>
       <c r="D37" t="n">
         <v>-1.2562</v>
@@ -2155,7 +2155,7 @@
         <v>-2.5916</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-1.0538</v>
       </c>
       <c r="D38" t="n">
         <v>-1.4683</v>
@@ -2201,7 +2201,7 @@
         <v>-3.7104</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-1.5087</v>
       </c>
       <c r="D39" t="n">
         <v>-1.9203</v>
@@ -2247,7 +2247,7 @@
         <v>-4.2774</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-1.7392</v>
       </c>
       <c r="D40" t="n">
         <v>-2.1493</v>
@@ -2293,7 +2293,7 @@
         <v>-4.3332</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.7619</v>
       </c>
       <c r="D41" t="n">
         <v>-2.1719</v>

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.1905</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7485</v>
+        <v>2.6822</v>
       </c>
       <c r="E2" t="n">
         <v>7.8466</v>
@@ -548,7 +548,7 @@
         <v>3.1377</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6961</v>
+        <v>2.6305</v>
       </c>
       <c r="E3" t="n">
         <v>7.7168</v>
@@ -594,7 +594,7 @@
         <v>2.5263</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0886</v>
+        <v>2.0314</v>
       </c>
       <c r="E4" t="n">
         <v>6.2131</v>
@@ -640,7 +640,7 @@
         <v>2.2878</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8517</v>
+        <v>1.7977</v>
       </c>
       <c r="E5" t="n">
         <v>5.6266</v>
@@ -686,7 +686,7 @@
         <v>1.98</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5458</v>
+        <v>1.4961</v>
       </c>
       <c r="E6" t="n">
         <v>4.8696</v>
@@ -732,7 +732,7 @@
         <v>1.968</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5339</v>
+        <v>1.4844</v>
       </c>
       <c r="E7" t="n">
         <v>4.8401</v>
@@ -778,7 +778,7 @@
         <v>1.7457</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3131</v>
+        <v>1.2666</v>
       </c>
       <c r="E8" t="n">
         <v>4.2934</v>
@@ -824,7 +824,7 @@
         <v>1.4385</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0078</v>
+        <v>0.9655</v>
       </c>
       <c r="E9" t="n">
         <v>3.5378</v>
@@ -870,7 +870,7 @@
         <v>1.302</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8722</v>
+        <v>0.8318</v>
       </c>
       <c r="E10" t="n">
         <v>3.202</v>
@@ -916,7 +916,7 @@
         <v>1.2098</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7806</v>
+        <v>0.7415</v>
       </c>
       <c r="E11" t="n">
         <v>2.9754</v>
@@ -962,7 +962,7 @@
         <v>1.1386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7099</v>
+        <v>0.6717</v>
       </c>
       <c r="E12" t="n">
         <v>2.8003</v>
@@ -1008,7 +1008,7 @@
         <v>1.0396</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6115</v>
+        <v>0.5747</v>
       </c>
       <c r="E13" t="n">
         <v>2.5568</v>
@@ -1054,7 +1054,7 @@
         <v>1.0182</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5537</v>
       </c>
       <c r="E14" t="n">
         <v>2.504</v>
@@ -1100,7 +1100,7 @@
         <v>0.866</v>
       </c>
       <c r="D15" t="n">
-        <v>0.439</v>
+        <v>0.4046</v>
       </c>
       <c r="E15" t="n">
         <v>2.1297</v>
@@ -1146,7 +1146,7 @@
         <v>0.8073</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3807</v>
+        <v>0.3471</v>
       </c>
       <c r="E16" t="n">
         <v>1.9854</v>
@@ -1192,7 +1192,7 @@
         <v>0.5743</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1492</v>
+        <v>0.1188</v>
       </c>
       <c r="E17" t="n">
         <v>1.4123</v>
@@ -1238,7 +1238,7 @@
         <v>0.571</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1459</v>
+        <v>0.1156</v>
       </c>
       <c r="E18" t="n">
         <v>1.4043</v>
@@ -1284,7 +1284,7 @@
         <v>0.4031</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0209</v>
+        <v>-0.049</v>
       </c>
       <c r="E19" t="n">
         <v>0.9913</v>
@@ -1330,7 +1330,7 @@
         <v>0.3668</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0569</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>0.9021</v>
@@ -1376,7 +1376,7 @@
         <v>0.3146</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1088</v>
+        <v>-0.1356</v>
       </c>
       <c r="E21" t="n">
         <v>0.7738</v>
@@ -1422,7 +1422,7 @@
         <v>0.1397</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2826</v>
+        <v>-0.3071</v>
       </c>
       <c r="E22" t="n">
         <v>0.3435</v>
@@ -1468,7 +1468,7 @@
         <v>0.1363</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.286</v>
+        <v>-0.3104</v>
       </c>
       <c r="E23" t="n">
         <v>0.3351</v>
@@ -1514,7 +1514,7 @@
         <v>0.1146</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3075</v>
+        <v>-0.3316</v>
       </c>
       <c r="E24" t="n">
         <v>0.2819</v>
@@ -1560,7 +1560,7 @@
         <v>0.1145</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3076</v>
+        <v>-0.3317</v>
       </c>
       <c r="E25" t="n">
         <v>0.2816</v>
@@ -1606,7 +1606,7 @@
         <v>0.0434</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3783</v>
+        <v>-0.4014</v>
       </c>
       <c r="E26" t="n">
         <v>0.1067</v>
@@ -1652,7 +1652,7 @@
         <v>0.0031</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4183</v>
+        <v>-0.4409</v>
       </c>
       <c r="E27" t="n">
         <v>0.0076</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0275</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4487</v>
+        <v>-0.4708</v>
       </c>
       <c r="E28" t="n">
         <v>-0.06759999999999999</v>
@@ -1744,7 +1744,7 @@
         <v>-0.065</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.486</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1599</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1672</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5875</v>
+        <v>-0.6077</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4112</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1783</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5985</v>
+        <v>-0.6186</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4386</v>
@@ -1882,7 +1882,7 @@
         <v>-0.179</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5992</v>
+        <v>-0.6193</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4402</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2959</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7154</v>
+        <v>-0.7339</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7278</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3875</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8063</v>
+        <v>-0.8235</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9529</v>
@@ -2020,7 +2020,7 @@
         <v>-0.6101</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0275</v>
+        <v>-1.0417</v>
       </c>
       <c r="E35" t="n">
         <v>-1.5004</v>
@@ -2066,7 +2066,7 @@
         <v>-0.6389</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0562</v>
+        <v>-1.07</v>
       </c>
       <c r="E36" t="n">
         <v>-1.5714</v>
@@ -2112,7 +2112,7 @@
         <v>-0.8403</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2562</v>
+        <v>-1.2672</v>
       </c>
       <c r="E37" t="n">
         <v>-2.0666</v>
@@ -2158,7 +2158,7 @@
         <v>-1.0538</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4683</v>
+        <v>-1.4764</v>
       </c>
       <c r="E38" t="n">
         <v>-2.5916</v>
@@ -2204,7 +2204,7 @@
         <v>-1.5087</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.9203</v>
+        <v>-1.9221</v>
       </c>
       <c r="E39" t="n">
         <v>-3.7104</v>
@@ -2250,7 +2250,7 @@
         <v>-1.7392</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.1493</v>
+        <v>-2.148</v>
       </c>
       <c r="E40" t="n">
         <v>-4.2774</v>
@@ -2296,7 +2296,7 @@
         <v>-1.7619</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1719</v>
+        <v>-2.1703</v>
       </c>
       <c r="E41" t="n">
         <v>-4.3332</v>

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8466</v>
+        <v>7.3643</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1905</v>
+        <v>2.9944</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6822</v>
+        <v>2.6866</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8466</v>
+        <v>7.3643</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2936</v>
+        <v>2.4791</v>
       </c>
       <c r="G2" t="n">
-        <v>3.553</v>
+        <v>4.8852</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7138</v>
+        <v>3.2486</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8207</v>
+        <v>1.6891</v>
       </c>
       <c r="J2" t="n">
-        <v>3.553</v>
+        <v>4.8852</v>
       </c>
       <c r="K2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L2" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>7.373699999999999</v>
+        <v>6.5743</v>
       </c>
       <c r="N2" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7168</v>
+        <v>7.0766</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1377</v>
+        <v>2.8774</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6305</v>
+        <v>2.5567</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7168</v>
+        <v>7.0766</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9903</v>
+        <v>3.8018</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7265</v>
+        <v>3.2748</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9903</v>
+        <v>7.9088</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6132</v>
+        <v>4.1122</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7265</v>
+        <v>3.2748</v>
       </c>
       <c r="K3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L3" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>7.3397</v>
+        <v>7.387</v>
       </c>
       <c r="N3" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2131</v>
+        <v>6.3962</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5263</v>
+        <v>2.6008</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0314</v>
+        <v>2.2496</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2131</v>
+        <v>6.3962</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7168</v>
+        <v>2.3671</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4963</v>
+        <v>4.0291</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7168</v>
+        <v>2.8537</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3915</v>
+        <v>1.4838</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4963</v>
+        <v>4.0291</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>5.887799999999999</v>
+        <v>5.5129</v>
       </c>
       <c r="N4" t="n">
         <v>258</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6266</v>
+        <v>5.3219</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2878</v>
+        <v>2.1639</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7977</v>
+        <v>1.7646</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6266</v>
+        <v>5.3219</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7492</v>
+        <v>4.4518</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8774</v>
+        <v>0.8701</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5466</v>
+        <v>11.0894</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3062</v>
+        <v>5.766</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8774</v>
+        <v>0.8701</v>
       </c>
       <c r="K5" t="n">
         <v>136</v>
@@ -667,7 +667,7 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>6.183599999999999</v>
+        <v>6.6361</v>
       </c>
       <c r="N5" t="n">
         <v>179</v>
@@ -676,185 +676,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8696</v>
+        <v>4.7187</v>
       </c>
       <c r="C6" t="n">
-        <v>1.98</v>
+        <v>1.9187</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4961</v>
+        <v>1.4922</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8696</v>
+        <v>4.7187</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7109</v>
+        <v>4.4518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1587</v>
+        <v>0.2669</v>
       </c>
       <c r="H6" t="n">
-        <v>6.3926</v>
+        <v>11.2379</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1814</v>
+        <v>5.8432</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1587</v>
+        <v>0.2669</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3401</v>
+        <v>6.1101</v>
       </c>
       <c r="N6" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8401</v>
+        <v>4.5832</v>
       </c>
       <c r="C7" t="n">
-        <v>1.968</v>
+        <v>1.8636</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4844</v>
+        <v>1.4311</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8401</v>
+        <v>4.5832</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5433</v>
+        <v>4.4518</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2968</v>
+        <v>0.1314</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7181</v>
+        <v>11.5466</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6347</v>
+        <v>6.0037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2968</v>
+        <v>0.1314</v>
       </c>
       <c r="K7" t="n">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9315</v>
+        <v>6.1351</v>
       </c>
       <c r="N7" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2934</v>
+        <v>4.3008</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7457</v>
+        <v>1.7488</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2666</v>
+        <v>1.3036</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2934</v>
+        <v>4.3008</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3477</v>
+        <v>1.7927</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0543</v>
+        <v>2.5081</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9315</v>
+        <v>1.7927</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9971</v>
+        <v>0.9321</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0543</v>
+        <v>2.5081</v>
       </c>
       <c r="K8" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L8" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9428</v>
+        <v>3.4402</v>
       </c>
       <c r="N8" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5378</v>
+        <v>4.2039</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4385</v>
+        <v>1.7094</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9655</v>
+        <v>1.2598</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5378</v>
+        <v>4.2039</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6941</v>
+        <v>3.9322</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1563</v>
+        <v>0.2717</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6941</v>
+        <v>8.3682</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9942</v>
+        <v>4.3511</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1563</v>
+        <v>0.2717</v>
       </c>
       <c r="K9" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8379</v>
+        <v>4.6228</v>
       </c>
       <c r="N9" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.202</v>
+        <v>3.9664</v>
       </c>
       <c r="C10" t="n">
-        <v>1.302</v>
+        <v>1.6128</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8318</v>
+        <v>1.1526</v>
       </c>
       <c r="E10" t="n">
-        <v>3.202</v>
+        <v>3.9664</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4454</v>
+        <v>2.2818</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7566</v>
+        <v>1.6846</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4454</v>
+        <v>2.5535</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1715</v>
+        <v>1.3277</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7566</v>
+        <v>1.6846</v>
       </c>
       <c r="K10" t="n">
         <v>104</v>
@@ -897,7 +897,7 @@
         <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9281</v>
+        <v>3.0123</v>
       </c>
       <c r="N10" t="n">
         <v>258</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9754</v>
+        <v>3.4527</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2098</v>
+        <v>1.4039</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7415</v>
+        <v>0.9207</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9754</v>
+        <v>3.4527</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9578</v>
+        <v>3.4357</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9578</v>
+        <v>6.619</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2079</v>
+        <v>3.4416</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="K11" t="n">
         <v>163</v>
@@ -943,7 +943,7 @@
         <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2255</v>
+        <v>3.4586</v>
       </c>
       <c r="N11" t="n">
         <v>212</v>
@@ -952,216 +952,216 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8003</v>
+        <v>3.0463</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1386</v>
+        <v>1.2387</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6717</v>
+        <v>0.7372</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8003</v>
+        <v>3.0463</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4529</v>
+        <v>2.4923</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3474</v>
+        <v>0.554</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4529</v>
+        <v>3.2949</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3671</v>
+        <v>1.7132</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3474</v>
+        <v>0.554</v>
       </c>
       <c r="K12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L12" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7145</v>
+        <v>2.2672</v>
       </c>
       <c r="N12" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5568</v>
+        <v>2.7385</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0396</v>
+        <v>1.1135</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5747</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5568</v>
+        <v>2.7385</v>
       </c>
       <c r="F13" t="n">
-        <v>1.891</v>
+        <v>3.408</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6657999999999999</v>
+        <v>-0.6695</v>
       </c>
       <c r="H13" t="n">
-        <v>1.891</v>
+        <v>6.5213</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5327</v>
+        <v>3.3908</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6657999999999999</v>
+        <v>-0.6695</v>
       </c>
       <c r="K13" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="L13" t="n">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1985</v>
+        <v>2.7213</v>
       </c>
       <c r="N13" t="n">
-        <v>266</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.504</v>
+        <v>2.7328</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0182</v>
+        <v>1.1112</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5537</v>
+        <v>0.5957</v>
       </c>
       <c r="E14" t="n">
-        <v>2.504</v>
+        <v>2.7328</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5541</v>
+        <v>3.0213</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0501</v>
+        <v>-0.2885</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5541</v>
+        <v>5.1587</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8807</v>
+        <v>2.6823</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0501</v>
+        <v>-0.2885</v>
       </c>
       <c r="K14" t="n">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="L14" t="n">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8306</v>
+        <v>2.3938</v>
       </c>
       <c r="N14" t="n">
-        <v>258</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1297</v>
+        <v>2.5944</v>
       </c>
       <c r="C15" t="n">
-        <v>0.866</v>
+        <v>1.0549</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4046</v>
+        <v>0.5332</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1297</v>
+        <v>2.5944</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5484</v>
+        <v>3.2848</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4187</v>
+        <v>-0.6904</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5484</v>
+        <v>6.0873</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0656</v>
+        <v>3.1651</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4187</v>
+        <v>-0.6904</v>
       </c>
       <c r="K15" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6469</v>
+        <v>2.4747</v>
       </c>
       <c r="N15" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8073</v>
+        <v>1.0367</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3471</v>
+        <v>0.513</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9854</v>
+        <v>2.5495</v>
       </c>
       <c r="N16" t="n">
         <v>115</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4123</v>
+        <v>2.391</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5743</v>
+        <v>0.9722</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1188</v>
+        <v>0.4414</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4123</v>
+        <v>2.391</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1496</v>
+        <v>2.5154</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7373</v>
+        <v>-0.1244</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1496</v>
+        <v>3.3765</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7423</v>
+        <v>1.7556</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7373</v>
+        <v>-0.1244</v>
       </c>
       <c r="K17" t="n">
         <v>136</v>
@@ -1219,7 +1219,7 @@
         <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.005</v>
+        <v>1.6312</v>
       </c>
       <c r="N17" t="n">
         <v>179</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4043</v>
+        <v>2.2869</v>
       </c>
       <c r="C18" t="n">
-        <v>0.571</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1156</v>
+        <v>0.3944</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4043</v>
+        <v>2.2869</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6701</v>
+        <v>2.7534</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2658</v>
+        <v>-0.4665</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6701</v>
+        <v>4.2148</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3536</v>
+        <v>2.1915</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2658</v>
+        <v>-0.4665</v>
       </c>
       <c r="K18" t="n">
         <v>136</v>
@@ -1265,7 +1265,7 @@
         <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0878</v>
+        <v>1.725</v>
       </c>
       <c r="N18" t="n">
         <v>179</v>
@@ -1274,124 +1274,124 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4031</v>
+        <v>0.8807</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.049</v>
+        <v>0.3398</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9913</v>
+        <v>2.166</v>
       </c>
       <c r="N19" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3668</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0522</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9021</v>
+        <v>1.2977</v>
       </c>
       <c r="N20" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3146</v>
+        <v>0.525</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1356</v>
+        <v>-0.0551</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7738</v>
+        <v>1.2911</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1412,400 +1412,400 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1397</v>
+        <v>0.3788</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3071</v>
+        <v>-0.2175</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3435</v>
+        <v>0.9315</v>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1363</v>
+        <v>0.3152</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3104</v>
+        <v>-0.2881</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3351</v>
+        <v>0.7752</v>
       </c>
       <c r="N23" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1146</v>
+        <v>0.2773</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3316</v>
+        <v>-0.3301</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2819</v>
+        <v>0.6821</v>
       </c>
       <c r="N24" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1145</v>
+        <v>0.239</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3317</v>
+        <v>-0.3727</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2816</v>
+        <v>0.5878</v>
       </c>
       <c r="N25" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1067</v>
+        <v>0.5319</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0434</v>
+        <v>0.2163</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4014</v>
+        <v>-0.3979</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1067</v>
+        <v>0.5319</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1067</v>
+        <v>-0.5308</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.0627</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1067</v>
+        <v>-0.5308</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1067</v>
+        <v>-0.276</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.0627</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1067</v>
+        <v>0.7867</v>
       </c>
       <c r="N26" t="n">
-        <v>101</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0076</v>
+        <v>0.2291</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0031</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4409</v>
+        <v>-0.5346</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0076</v>
+        <v>0.2291</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8562</v>
+        <v>0.2291</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8638</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8562</v>
+        <v>0.2291</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.694</v>
+        <v>0.2291</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8638</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1698000000000001</v>
+        <v>0.2291</v>
       </c>
       <c r="N27" t="n">
-        <v>266</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0275</v>
+        <v>0.0694</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4708</v>
+        <v>-0.5609</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="N28" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.065</v>
+        <v>0.0615</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5697</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1599</v>
+        <v>0.1513</v>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1672</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6077</v>
+        <v>-0.649</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4112</v>
+        <v>-0.0244</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1783</v>
+        <v>-0.0308</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6186</v>
+        <v>-0.6722</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4386</v>
+        <v>-0.0757</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.179</v>
+        <v>-0.0553</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6193</v>
+        <v>-0.6995</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4402</v>
+        <v>-0.1361</v>
       </c>
       <c r="N32" t="n">
         <v>101</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2959</v>
+        <v>-0.0655</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7339</v>
+        <v>-0.7107</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7278</v>
+        <v>-0.1611</v>
       </c>
       <c r="N33" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3875</v>
+        <v>-0.2598</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8235</v>
+        <v>-0.9264</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9529</v>
+        <v>-0.6389</v>
       </c>
       <c r="N34" t="n">
         <v>101</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6101</v>
+        <v>-0.3828</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0417</v>
+        <v>-1.0631</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.5004</v>
+        <v>-0.9415</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6389</v>
+        <v>-0.4241</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.07</v>
+        <v>-1.1089</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5714</v>
+        <v>-1.043</v>
       </c>
       <c r="N36" t="n">
         <v>101</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.0666</v>
+        <v>-1.7039</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.8403</v>
+        <v>-0.6928</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2672</v>
+        <v>-1.4072</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.0666</v>
+        <v>-1.7039</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.9522</v>
+        <v>-1.7684</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1144</v>
+        <v>0.0645</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.9522</v>
+        <v>-1.7684</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5823</v>
+        <v>-0.9195</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1144</v>
+        <v>0.0645</v>
       </c>
       <c r="K37" t="n">
         <v>163</v>
@@ -2139,7 +2139,7 @@
         <v>49</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6967</v>
+        <v>-0.855</v>
       </c>
       <c r="N37" t="n">
         <v>212</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.0538</v>
+        <v>-0.8451</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4764</v>
+        <v>-1.5763</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.5916</v>
+        <v>-2.0783</v>
       </c>
       <c r="N38" t="n">
         <v>145</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.5087</v>
+        <v>-1.3635</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.9221</v>
+        <v>-2.1519</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.7104</v>
+        <v>-3.3533</v>
       </c>
       <c r="N39" t="n">
         <v>115</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.2774</v>
+        <v>-4.5919</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.7392</v>
+        <v>-1.8671</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.148</v>
+        <v>-2.711</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.2774</v>
+        <v>-4.5919</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.5937</v>
+        <v>-3.2078</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6837</v>
+        <v>-1.3841</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.5937</v>
+        <v>-3.2078</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.9128</v>
+        <v>-1.6679</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6837</v>
+        <v>-1.3841</v>
       </c>
       <c r="K40" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="L40" t="n">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.5965</v>
+        <v>-3.052</v>
       </c>
       <c r="N40" t="n">
-        <v>179</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.3332</v>
+        <v>-5.2987</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.7619</v>
+        <v>-2.1545</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1703</v>
+        <v>-3.0301</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.3332</v>
+        <v>-5.2987</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4441</v>
+        <v>-4.836</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.8891</v>
+        <v>-0.4627</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4441</v>
+        <v>-4.836</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.981</v>
+        <v>-2.5145</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.8891</v>
+        <v>-0.4627</v>
       </c>
       <c r="K41" t="n">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="L41" t="n">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.8701</v>
+        <v>-2.9772</v>
       </c>
       <c r="N41" t="n">
-        <v>266</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9101</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>20.0222</v>
+        <v>18.1742</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3068</v>
+        <v>0.2638</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7496</v>
+        <v>5.8036</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1128</v>
+        <v>-0.0487</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.4816</v>
+        <v>-1.0714</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1926</v>
+        <v>-0.1018</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.2372</v>
+        <v>-2.2396</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2923</v>
+        <v>-0.1703</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.4306</v>
+        <v>-3.7466</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4631</v>
+        <v>0.4153</v>
       </c>
       <c r="J7" t="n">
-        <v>10.1882</v>
+        <v>9.1366</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4631</v>
+        <v>0.4153</v>
       </c>
       <c r="J8" t="n">
-        <v>10.1882</v>
+        <v>9.1366</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1878</v>
+        <v>0.1548</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1316</v>
+        <v>3.4056</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3719</v>
+        <v>-0.2304</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.181800000000001</v>
+        <v>-5.0688</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5861</v>
+        <v>-0.3844</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.8942</v>
+        <v>-8.456799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3715</v>
+        <v>0.4177</v>
       </c>
       <c r="J12" t="n">
-        <v>7.0585</v>
+        <v>7.9363</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1557</v>
+        <v>0.1505</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9583</v>
+        <v>2.8595</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1141</v>
+        <v>0.1019</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1679</v>
+        <v>1.9361</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2623</v>
+        <v>-0.1614</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.9837</v>
+        <v>-3.0666</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6012</v>
+        <v>-0.3964</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.4228</v>
+        <v>-7.5316</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6078</v>
+        <v>1.3969</v>
       </c>
       <c r="J17" t="n">
-        <v>30.5482</v>
+        <v>26.5411</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6314</v>
+        <v>0.6891</v>
       </c>
       <c r="J18" t="n">
-        <v>11.9966</v>
+        <v>13.0929</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.524</v>
+        <v>0.5965</v>
       </c>
       <c r="J19" t="n">
-        <v>9.956</v>
+        <v>11.3335</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2619</v>
+        <v>0.3422</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9761</v>
+        <v>6.5018</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0468</v>
+        <v>0.0307</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8892</v>
+        <v>0.5833</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2238</v>
+        <v>0.2146</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2522</v>
+        <v>4.0774</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.84</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.217</v>
+        <v>-0.174</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.123</v>
+        <v>-3.306</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4179</v>
+        <v>-0.2798</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.9401</v>
+        <v>-5.3162</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4784</v>
+        <v>-0.3177</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.089600000000001</v>
+        <v>-6.0363</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5901</v>
+        <v>-0.393</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.2119</v>
+        <v>-7.467</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.88</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8661</v>
+        <v>1.5734</v>
       </c>
       <c r="J27" t="n">
-        <v>35.4559</v>
+        <v>29.8946</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.47</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1042</v>
+        <v>1.0797</v>
       </c>
       <c r="J28" t="n">
-        <v>20.9798</v>
+        <v>20.5143</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6983</v>
+        <v>0.7711</v>
       </c>
       <c r="J29" t="n">
-        <v>13.2677</v>
+        <v>14.6509</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2592</v>
+        <v>-0.1726</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.9248</v>
+        <v>-3.2794</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3619</v>
+        <v>-0.2781</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.8761</v>
+        <v>-5.2839</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7429</v>
       </c>
       <c r="J32" t="n">
-        <v>24.813</v>
+        <v>22.287</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3426</v>
+        <v>0.2979</v>
       </c>
       <c r="J33" t="n">
-        <v>10.278</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0595</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>1.785</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1407</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.221</v>
+        <v>-1.971</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.18</v>
+        <v>-0.092</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.4</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7095</v>
+        <v>0.6714</v>
       </c>
       <c r="J37" t="n">
-        <v>21.285</v>
+        <v>20.142</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4873</v>
+        <v>0.4431</v>
       </c>
       <c r="J38" t="n">
-        <v>14.619</v>
+        <v>13.293</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.318</v>
+        <v>0.2807</v>
       </c>
       <c r="J39" t="n">
-        <v>9.539999999999999</v>
+        <v>8.420999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.438</v>
+        <v>-0.2755</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.14</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6539</v>
+        <v>-0.4351</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.617</v>
+        <v>-13.053</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.17</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3728</v>
+        <v>0.4156</v>
       </c>
       <c r="J42" t="n">
-        <v>7.8288</v>
+        <v>8.727600000000001</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1323</v>
+        <v>0.114</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7783</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2789</v>
+        <v>-0.1772</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.8569</v>
+        <v>-3.7212</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3584</v>
+        <v>-0.2279</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.5264</v>
+        <v>-4.7859</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3347</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.8066</v>
+        <v>-7.0287</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.87</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8626</v>
+        <v>1.5707</v>
       </c>
       <c r="J47" t="n">
-        <v>39.1146</v>
+        <v>32.9847</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.79</v>
       </c>
       <c r="I48" t="n">
-        <v>1.7247</v>
+        <v>1.4759</v>
       </c>
       <c r="J48" t="n">
-        <v>36.2187</v>
+        <v>30.9939</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0155</v>
+        <v>0.0636</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3255</v>
+        <v>1.3356</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4719</v>
+        <v>-0.3948</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.9099</v>
+        <v>-8.290800000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6165</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.2359</v>
+        <v>-12.9465</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>2.06</v>
       </c>
       <c r="I52" t="n">
-        <v>1.978</v>
+        <v>1.5231</v>
       </c>
       <c r="J52" t="n">
-        <v>41.538</v>
+        <v>31.9851</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1043</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>23.1903</v>
+        <v>16.8189</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2865</v>
+        <v>0.354</v>
       </c>
       <c r="J54" t="n">
-        <v>6.0165</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2842</v>
+        <v>-0.2001</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.9682</v>
+        <v>-4.2021</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.0684</v>
+        <v>-17.178</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4217</v>
+        <v>0.4198</v>
       </c>
       <c r="J57" t="n">
-        <v>8.855700000000001</v>
+        <v>8.815799999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.159</v>
+        <v>0.1437</v>
       </c>
       <c r="J58" t="n">
-        <v>3.339</v>
+        <v>3.0177</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0206</v>
+        <v>-0.0091</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4326</v>
+        <v>-0.1911</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5113</v>
+        <v>-0.3329</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.7373</v>
+        <v>-6.9909</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6902</v>
+        <v>-0.4633</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.4942</v>
+        <v>-9.7293</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0311</v>
+        <v>0.7446</v>
       </c>
       <c r="J62" t="n">
-        <v>22.6842</v>
+        <v>16.3812</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8091</v>
+        <v>0.6099</v>
       </c>
       <c r="J63" t="n">
-        <v>17.8002</v>
+        <v>13.4178</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.4843</v>
       </c>
       <c r="J64" t="n">
-        <v>12.8964</v>
+        <v>10.6546</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0968</v>
+        <v>0.1597</v>
       </c>
       <c r="J65" t="n">
-        <v>2.1296</v>
+        <v>3.5134</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4945</v>
+        <v>-0.4246</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.879</v>
+        <v>-9.341200000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4557</v>
+        <v>0.4503</v>
       </c>
       <c r="J67" t="n">
-        <v>10.0254</v>
+        <v>9.906599999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1381</v>
+        <v>0.1405</v>
       </c>
       <c r="J68" t="n">
-        <v>3.0382</v>
+        <v>3.091</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0065</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>0.143</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.226</v>
+        <v>-0.1336</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.972</v>
+        <v>-2.9392</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4248</v>
+        <v>-0.2681</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.345599999999999</v>
+        <v>-5.8982</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2092</v>
+        <v>0.8559</v>
       </c>
       <c r="J72" t="n">
-        <v>36.276</v>
+        <v>25.677</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7759</v>
+        <v>0.5868</v>
       </c>
       <c r="J73" t="n">
-        <v>23.277</v>
+        <v>17.604</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6542</v>
+        <v>0.5163</v>
       </c>
       <c r="J74" t="n">
-        <v>19.626</v>
+        <v>15.489</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.203</v>
+        <v>-0.1309</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.09</v>
+        <v>-3.927</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8097</v>
+        <v>-0.7639</v>
       </c>
       <c r="J76" t="n">
-        <v>-24.291</v>
+        <v>-22.917</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2837</v>
+        <v>0.3044</v>
       </c>
       <c r="J77" t="n">
-        <v>8.510999999999999</v>
+        <v>9.132</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0963</v>
+        <v>0.0785</v>
       </c>
       <c r="J78" t="n">
-        <v>2.889</v>
+        <v>2.355</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1461</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.383</v>
+        <v>-2.829</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2053</v>
+        <v>-0.1278</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.159</v>
+        <v>-3.834</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4679</v>
+        <v>-0.3005</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.037</v>
+        <v>-9.015000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.15</v>
       </c>
       <c r="I82" t="n">
-        <v>2.0466</v>
+        <v>1.6102</v>
       </c>
       <c r="J82" t="n">
-        <v>38.8854</v>
+        <v>30.5938</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.46</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0823</v>
+        <v>0.7932</v>
       </c>
       <c r="J83" t="n">
-        <v>20.5637</v>
+        <v>15.0708</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0414</v>
+        <v>0.1241</v>
       </c>
       <c r="J84" t="n">
-        <v>0.7866</v>
+        <v>2.3579</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2597</v>
+        <v>-0.173</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.9343</v>
+        <v>-3.287</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3625</v>
+        <v>-0.2786</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.8875</v>
+        <v>-5.2934</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3535</v>
+        <v>0.365</v>
       </c>
       <c r="J87" t="n">
-        <v>6.7165</v>
+        <v>6.935</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2005</v>
+        <v>0.1884</v>
       </c>
       <c r="J88" t="n">
-        <v>3.8095</v>
+        <v>3.5796</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2134</v>
+        <v>-0.1607</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.0546</v>
+        <v>-3.0533</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.44</v>
+        <v>-0.2874</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.359999999999999</v>
+        <v>-5.4606</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8363</v>
+        <v>-0.5752</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.8897</v>
+        <v>-10.9288</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.16</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3564</v>
+        <v>0.3944</v>
       </c>
       <c r="J92" t="n">
-        <v>7.128</v>
+        <v>7.888</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3101</v>
+        <v>0.3347</v>
       </c>
       <c r="J93" t="n">
-        <v>6.202</v>
+        <v>6.694</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2464</v>
+        <v>-0.1569</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.928</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3597</v>
+        <v>-0.2284</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.194</v>
+        <v>-4.568</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6317</v>
+        <v>-0.4194</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.634</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.93</v>
       </c>
       <c r="I97" t="n">
-        <v>1.963</v>
+        <v>1.6628</v>
       </c>
       <c r="J97" t="n">
-        <v>39.26</v>
+        <v>33.256</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7776</v>
+        <v>0.7872</v>
       </c>
       <c r="J98" t="n">
-        <v>15.552</v>
+        <v>15.744</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4454</v>
+        <v>0.508</v>
       </c>
       <c r="J99" t="n">
-        <v>8.907999999999999</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1902</v>
+        <v>-0.1095</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.804</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9167</v>
+        <v>-0.8811</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.334</v>
+        <v>-17.622</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.27</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.8414</v>
       </c>
       <c r="J102" t="n">
-        <v>9.7155</v>
+        <v>12.621</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.64</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.45</v>
+        <v>-0.341</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.75</v>
+        <v>-5.115</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.52</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.6574</v>
+        <v>-0.4496</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.861000000000001</v>
+        <v>-6.744</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.35</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.6109</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.239</v>
+        <v>-9.163500000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.31</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9319</v>
+        <v>-0.6491</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.9785</v>
+        <v>-9.736499999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.46</v>
       </c>
       <c r="I107" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J107" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.28</v>
       </c>
       <c r="I108" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J108" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.43</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8475</v>
+        <v>0.988</v>
       </c>
       <c r="J109" t="n">
-        <v>12.7125</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3807</v>
+        <v>0.501</v>
       </c>
       <c r="J110" t="n">
-        <v>5.7105</v>
+        <v>7.515</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9941</v>
+        <v>-0.9718</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.9115</v>
+        <v>-14.577</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.72</v>
       </c>
       <c r="I112" t="n">
-        <v>1.6709</v>
+        <v>1.4386</v>
       </c>
       <c r="J112" t="n">
-        <v>40.1016</v>
+        <v>34.5264</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9176</v>
+        <v>0.906</v>
       </c>
       <c r="J113" t="n">
-        <v>22.0224</v>
+        <v>21.744</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4403</v>
+        <v>0.4474</v>
       </c>
       <c r="J114" t="n">
-        <v>10.5672</v>
+        <v>10.7376</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.95</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3063</v>
+        <v>-0.2344</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.3512</v>
+        <v>-5.6256</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.2936</v>
+        <v>-1.3104</v>
       </c>
       <c r="J116" t="n">
-        <v>-31.0464</v>
+        <v>-31.4496</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.53</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8048</v>
+        <v>0.9998</v>
       </c>
       <c r="J117" t="n">
-        <v>19.3152</v>
+        <v>23.9952</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0484</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.9464</v>
+        <v>-1.1616</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3493</v>
+        <v>-0.2165</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.3832</v>
+        <v>-5.196</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3788</v>
+        <v>-0.2367</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.091200000000001</v>
+        <v>-5.6808</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4075</v>
+        <v>-0.2566</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.779999999999999</v>
+        <v>-6.1584</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.89</v>
       </c>
       <c r="I122" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J122" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.85</v>
       </c>
       <c r="I123" t="n">
-        <v>1.6787</v>
+        <v>1.4708</v>
       </c>
       <c r="J123" t="n">
-        <v>25.1805</v>
+        <v>22.062</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>1.1154</v>
+        <v>1.1624</v>
       </c>
       <c r="J124" t="n">
-        <v>16.731</v>
+        <v>17.436</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0331</v>
+        <v>0.0576</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.4965</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.91</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5391</v>
+        <v>-0.4639</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.086499999999999</v>
+        <v>-6.9585</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.92</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0111</v>
+        <v>-0.0437</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.1665</v>
+        <v>-0.6555</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.72</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3357</v>
+        <v>-0.2694</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.0355</v>
+        <v>-4.041</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3677</v>
+        <v>-0.2891</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.5155</v>
+        <v>-4.3365</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.534</v>
+        <v>-0.3708</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.01</v>
+        <v>-5.562</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.27</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.984</v>
+        <v>-0.6907</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.76</v>
+        <v>-10.3605</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0402</v>
+        <v>0.9555</v>
       </c>
       <c r="J132" t="n">
-        <v>17.6834</v>
+        <v>16.2435</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8975</v>
+        <v>0.8181</v>
       </c>
       <c r="J133" t="n">
-        <v>15.2575</v>
+        <v>13.9077</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.38</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5175</v>
+        <v>0.4728</v>
       </c>
       <c r="J134" t="n">
-        <v>8.797499999999999</v>
+        <v>8.037599999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.21</v>
+        <v>-0.1082</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.57</v>
+        <v>-1.8394</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4876</v>
+        <v>-0.3096</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.289199999999999</v>
+        <v>-5.2632</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.01</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1388</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>2.3596</v>
+        <v>1.3957</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.84</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2139</v>
+        <v>-0.1731</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.6363</v>
+        <v>-2.9427</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3015</v>
+        <v>-0.2231</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.1255</v>
+        <v>-3.7927</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.64</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5474</v>
+        <v>-0.364</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.3058</v>
+        <v>-6.188</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5884</v>
+        <v>-0.3921</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.0028</v>
+        <v>-6.6657</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4848</v>
+        <v>0.5646</v>
       </c>
       <c r="J142" t="n">
-        <v>9.2112</v>
+        <v>10.7274</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.93</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0848</v>
+        <v>-0.0828</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.6112</v>
+        <v>-1.5732</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2782</v>
+        <v>-0.1902</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.2858</v>
+        <v>-3.6138</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5649</v>
+        <v>-0.3729</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.7331</v>
+        <v>-7.0851</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6554</v>
+        <v>-0.4381</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.4526</v>
+        <v>-8.3239</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.19</v>
       </c>
       <c r="I147" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J147" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1734</v>
+        <v>1.1306</v>
       </c>
       <c r="J148" t="n">
-        <v>22.2946</v>
+        <v>21.4814</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5642</v>
+        <v>0.6674</v>
       </c>
       <c r="J149" t="n">
-        <v>10.7198</v>
+        <v>12.6806</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0536</v>
+        <v>0.1412</v>
       </c>
       <c r="J150" t="n">
-        <v>1.0184</v>
+        <v>2.6828</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5478</v>
+        <v>-0.4736</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.4082</v>
+        <v>-8.9984</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.7409</v>
       </c>
       <c r="J152" t="n">
-        <v>17.1472</v>
+        <v>20.7452</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2109</v>
+        <v>0.2169</v>
       </c>
       <c r="J153" t="n">
-        <v>5.9052</v>
+        <v>6.0732</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.029</v>
+        <v>0.0074</v>
       </c>
       <c r="J154" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.2072</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4574</v>
+        <v>-0.2925</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.8072</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6511</v>
+        <v>-0.4335</v>
       </c>
       <c r="J156" t="n">
-        <v>-18.2308</v>
+        <v>-12.138</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4976</v>
+        <v>1.3212</v>
       </c>
       <c r="J157" t="n">
-        <v>41.9328</v>
+        <v>36.9936</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7502</v>
+        <v>0.75</v>
       </c>
       <c r="J158" t="n">
-        <v>21.0056</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.17</v>
       </c>
       <c r="I159" t="n">
-        <v>0.442</v>
+        <v>0.4895</v>
       </c>
       <c r="J159" t="n">
-        <v>12.376</v>
+        <v>13.706</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.98</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2201</v>
+        <v>-0.1422</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.1628</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5274</v>
+        <v>-0.458</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.7672</v>
+        <v>-12.824</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0639</v>
+        <v>0.0287</v>
       </c>
       <c r="J162" t="n">
-        <v>1.5336</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0191</v>
+        <v>-0.0366</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.4584</v>
+        <v>-0.8784</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.92</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.12</v>
+        <v>-0.0997</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.88</v>
+        <v>-2.3928</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3142</v>
+        <v>-0.2037</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.5408</v>
+        <v>-4.8888</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5467</v>
+        <v>-0.3587</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.1208</v>
+        <v>-8.6088</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0816</v>
+        <v>1.0447</v>
       </c>
       <c r="J167" t="n">
-        <v>25.9584</v>
+        <v>25.0728</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7469</v>
+        <v>0.726</v>
       </c>
       <c r="J168" t="n">
-        <v>17.9256</v>
+        <v>17.424</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4613</v>
+        <v>0.4521</v>
       </c>
       <c r="J169" t="n">
-        <v>11.0712</v>
+        <v>10.8504</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.88</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.503</v>
+        <v>-0.4382</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.072</v>
+        <v>-10.5168</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5299</v>
+        <v>-0.4661</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.7176</v>
+        <v>-11.1864</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3516</v>
+        <v>0.3992</v>
       </c>
       <c r="J172" t="n">
-        <v>14.064</v>
+        <v>15.968</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3215</v>
+        <v>0.3617</v>
       </c>
       <c r="J173" t="n">
-        <v>12.86</v>
+        <v>14.468</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.034</v>
+        <v>0.0368</v>
       </c>
       <c r="J174" t="n">
-        <v>1.36</v>
+        <v>1.472</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0453</v>
+        <v>-0.0211</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.812</v>
+        <v>-0.844</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3371</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.868</v>
+        <v>-13.484</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4029</v>
+        <v>1.257</v>
       </c>
       <c r="J177" t="n">
-        <v>56.116</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.15</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4188</v>
+        <v>0.4456</v>
       </c>
       <c r="J178" t="n">
-        <v>16.752</v>
+        <v>17.824</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.11</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2932</v>
+        <v>0.3411</v>
       </c>
       <c r="J179" t="n">
-        <v>11.728</v>
+        <v>13.644</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1632</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.528</v>
+        <v>-3.652</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3741</v>
+        <v>-0.3016</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.964</v>
+        <v>-12.064</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6216</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>13.6752</v>
+        <v>11.9196</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4962</v>
+        <v>0.4251</v>
       </c>
       <c r="J183" t="n">
-        <v>10.9164</v>
+        <v>9.3522</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.13</v>
+        <v>0.1331</v>
       </c>
       <c r="J184" t="n">
-        <v>2.86</v>
+        <v>2.9282</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0499</v>
+        <v>-0.0102</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.0978</v>
+        <v>-0.2244</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4472</v>
+        <v>-0.2811</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.8384</v>
+        <v>-6.1842</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5705</v>
+        <v>0.5229</v>
       </c>
       <c r="J187" t="n">
-        <v>12.551</v>
+        <v>11.5038</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.15</v>
+        <v>0.1124</v>
       </c>
       <c r="J188" t="n">
-        <v>3.3</v>
+        <v>2.4728</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.119</v>
+        <v>-0.0728</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.618</v>
+        <v>-1.6016</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2335</v>
+        <v>-0.1415</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.137</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6284</v>
+        <v>-0.4164</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.8248</v>
+        <v>-9.1608</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5916</v>
+        <v>0.7126</v>
       </c>
       <c r="J192" t="n">
-        <v>13.0152</v>
+        <v>15.6772</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.99</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0202</v>
+        <v>-0.0192</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.4444</v>
+        <v>-0.4224</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0482</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.7534</v>
+        <v>-1.0604</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2545</v>
+        <v>-0.1536</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.599</v>
+        <v>-3.3792</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5161</v>
+        <v>-0.3337</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.3542</v>
+        <v>-7.3414</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7461</v>
+        <v>0.7164</v>
       </c>
       <c r="J197" t="n">
-        <v>16.4142</v>
+        <v>15.7608</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.597</v>
+        <v>0.5662</v>
       </c>
       <c r="J198" t="n">
-        <v>13.134</v>
+        <v>12.4564</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1256</v>
+        <v>-0.0709</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.7632</v>
+        <v>-1.5598</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.98</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1692</v>
+        <v>-0.1119</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.7224</v>
+        <v>-2.4618</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.96</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2442</v>
+        <v>-0.1838</v>
       </c>
       <c r="J201" t="n">
-        <v>-5.3724</v>
+        <v>-4.0436</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3427</v>
+        <v>0.3763</v>
       </c>
       <c r="J202" t="n">
-        <v>7.1967</v>
+        <v>7.9023</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.04</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1534</v>
+        <v>0.1392</v>
       </c>
       <c r="J203" t="n">
-        <v>3.2214</v>
+        <v>2.9232</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.83</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3116</v>
+        <v>-0.1977</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.5436</v>
+        <v>-4.1517</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3884</v>
+        <v>-0.2477</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.1564</v>
+        <v>-5.2017</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.446</v>
+        <v>-0.2868</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.366</v>
+        <v>-6.0228</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.54</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2985</v>
+        <v>1.1909</v>
       </c>
       <c r="J207" t="n">
-        <v>27.2685</v>
+        <v>25.0089</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1175</v>
+        <v>1.0757</v>
       </c>
       <c r="J208" t="n">
-        <v>23.4675</v>
+        <v>22.5897</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.858</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>18.018</v>
+        <v>18.0684</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4868</v>
+        <v>0.5357</v>
       </c>
       <c r="J210" t="n">
-        <v>10.2228</v>
+        <v>11.2497</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.52</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.323</v>
+        <v>-1.3457</v>
       </c>
       <c r="J211" t="n">
-        <v>-27.783</v>
+        <v>-28.2597</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.6643</v>
       </c>
       <c r="J212" t="n">
-        <v>12.7627</v>
+        <v>15.2789</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3047</v>
+        <v>0.3416</v>
       </c>
       <c r="J213" t="n">
-        <v>7.0081</v>
+        <v>7.8568</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.15</v>
+        <v>0.1593</v>
       </c>
       <c r="J214" t="n">
-        <v>3.45</v>
+        <v>3.6639</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3863</v>
+        <v>-0.2404</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.8849</v>
+        <v>-5.5292</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4962</v>
+        <v>-0.3186</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.4126</v>
+        <v>-7.3278</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.9</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9507</v>
+        <v>1.6518</v>
       </c>
       <c r="J217" t="n">
-        <v>44.8661</v>
+        <v>37.9914</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.1</v>
       </c>
       <c r="I218" t="n">
-        <v>0.258</v>
+        <v>0.3117</v>
       </c>
       <c r="J218" t="n">
-        <v>5.934</v>
+        <v>7.1691</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1076</v>
+        <v>-0.0384</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.4748</v>
+        <v>-0.8832</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.377</v>
+        <v>-0.3037</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.670999999999999</v>
+        <v>-6.9851</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5448</v>
+        <v>-0.4783</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.5304</v>
+        <v>-11.0009</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5354</v>
+        <v>0.634</v>
       </c>
       <c r="J222" t="n">
-        <v>9.6372</v>
+        <v>11.412</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0597</v>
+        <v>0.0255</v>
       </c>
       <c r="J223" t="n">
-        <v>1.0746</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2107</v>
+        <v>-0.1439</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.7926</v>
+        <v>-2.5902</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4535</v>
+        <v>-0.2933</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.163</v>
+        <v>-5.2794</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.53</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7128</v>
+        <v>-0.4804</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.8304</v>
+        <v>-8.6472</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I227" t="n">
-        <v>1.9475</v>
+        <v>1.6449</v>
       </c>
       <c r="J227" t="n">
-        <v>35.055</v>
+        <v>29.6082</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.68</v>
       </c>
       <c r="I228" t="n">
-        <v>1.4978</v>
+        <v>1.329</v>
       </c>
       <c r="J228" t="n">
-        <v>26.9604</v>
+        <v>23.922</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1492</v>
+        <v>1.1114</v>
       </c>
       <c r="J229" t="n">
-        <v>20.6856</v>
+        <v>20.0052</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.01</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1119</v>
+        <v>-0.0292</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.0142</v>
+        <v>-0.5256</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.1656</v>
+        <v>-1.1651</v>
       </c>
       <c r="J231" t="n">
-        <v>-20.9808</v>
+        <v>-20.9718</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7783</v>
+        <v>0.9697</v>
       </c>
       <c r="J232" t="n">
-        <v>14.7877</v>
+        <v>18.4243</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1726</v>
+        <v>0.1718</v>
       </c>
       <c r="J233" t="n">
-        <v>3.2794</v>
+        <v>3.2642</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.1672</v>
+        <v>-0.3306</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6147</v>
+        <v>-0.4063</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.6793</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6147</v>
+        <v>-0.4063</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.6793</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.66</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5043</v>
+        <v>1.3278</v>
       </c>
       <c r="J237" t="n">
-        <v>28.5817</v>
+        <v>25.2282</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8304</v>
+        <v>0.8476</v>
       </c>
       <c r="J238" t="n">
-        <v>15.7776</v>
+        <v>16.1044</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I239" t="n">
-        <v>0.533</v>
+        <v>0.5991</v>
       </c>
       <c r="J239" t="n">
-        <v>10.127</v>
+        <v>11.3829</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.11</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2402</v>
+        <v>0.3179</v>
       </c>
       <c r="J240" t="n">
-        <v>4.5638</v>
+        <v>6.0401</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3452</v>
+        <v>-0.2637</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.5588</v>
+        <v>-5.0103</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8309</v>
+        <v>1.0275</v>
       </c>
       <c r="J242" t="n">
-        <v>19.1107</v>
+        <v>23.6325</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.057</v>
+        <v>0.0427</v>
       </c>
       <c r="J243" t="n">
-        <v>1.311</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.87</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2684</v>
+        <v>-0.1634</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.1732</v>
+        <v>-3.7582</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3467</v>
+        <v>-0.2153</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.9741</v>
+        <v>-4.9519</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6414</v>
+        <v>-0.4261</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.7522</v>
+        <v>-9.8003</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.65</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5464</v>
+        <v>1.3533</v>
       </c>
       <c r="J247" t="n">
-        <v>35.5672</v>
+        <v>31.1259</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.25</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7134</v>
+        <v>0.6966</v>
       </c>
       <c r="J248" t="n">
-        <v>16.4082</v>
+        <v>16.0218</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.25</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7134</v>
+        <v>0.6966</v>
       </c>
       <c r="J249" t="n">
-        <v>16.4082</v>
+        <v>16.0218</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4535</v>
+        <v>-0.3854</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.4305</v>
+        <v>-8.8642</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.1518</v>
+        <v>-1.1469</v>
       </c>
       <c r="J251" t="n">
-        <v>-26.4914</v>
+        <v>-26.3787</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.8</v>
       </c>
       <c r="I252" t="n">
-        <v>1.7664</v>
+        <v>1.5037</v>
       </c>
       <c r="J252" t="n">
-        <v>35.328</v>
+        <v>30.074</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.32</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8189</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J253" t="n">
-        <v>16.378</v>
+        <v>16.602</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.28</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7224</v>
+        <v>0.7393</v>
       </c>
       <c r="J254" t="n">
-        <v>14.448</v>
+        <v>14.786</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1624</v>
+        <v>0.2367</v>
       </c>
       <c r="J255" t="n">
-        <v>3.248</v>
+        <v>4.734</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9559</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.668</v>
+        <v>-19.118</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4982</v>
+        <v>0.5827</v>
       </c>
       <c r="J257" t="n">
-        <v>9.964</v>
+        <v>11.654</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.04</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1662</v>
+        <v>0.1499</v>
       </c>
       <c r="J258" t="n">
-        <v>3.324</v>
+        <v>2.998</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1017</v>
+        <v>-0.0882</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.034</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5604</v>
+        <v>-0.3683</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.208</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7356</v>
+        <v>-0.4977</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.712</v>
+        <v>-9.954000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5715</v>
+        <v>1.3746</v>
       </c>
       <c r="J262" t="n">
-        <v>29.8585</v>
+        <v>26.1174</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.65</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4609</v>
+        <v>1.3024</v>
       </c>
       <c r="J263" t="n">
-        <v>27.7571</v>
+        <v>24.7456</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4774</v>
+        <v>0.5643</v>
       </c>
       <c r="J264" t="n">
-        <v>9.070600000000001</v>
+        <v>10.7217</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.12</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2465</v>
+        <v>0.3329</v>
       </c>
       <c r="J265" t="n">
-        <v>4.6835</v>
+        <v>6.3251</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6338</v>
+        <v>-0.5679</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.0422</v>
+        <v>-10.7901</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.342</v>
+        <v>0.3708</v>
       </c>
       <c r="J267" t="n">
-        <v>6.498</v>
+        <v>7.0452</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.96</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0213</v>
+        <v>-0.0427</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.4047</v>
+        <v>-0.8113</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4066</v>
+        <v>-0.2668</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.7254</v>
+        <v>-5.0692</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.67</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3432</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.9123</v>
+        <v>-6.5208</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5624</v>
+        <v>-0.3715</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.6856</v>
+        <v>-7.0585</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.51</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2682</v>
+        <v>1.1681</v>
       </c>
       <c r="J272" t="n">
-        <v>27.9004</v>
+        <v>25.6982</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.678</v>
+        <v>0.667</v>
       </c>
       <c r="J273" t="n">
-        <v>14.916</v>
+        <v>14.674</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J274" t="n">
-        <v>5.1678</v>
+        <v>6.2942</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1025</v>
+        <v>-0.0353</v>
       </c>
       <c r="J275" t="n">
-        <v>-2.255</v>
+        <v>-0.7766</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4597</v>
+        <v>-0.3902</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.1134</v>
+        <v>-8.5844</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6533</v>
+        <v>0.7978</v>
       </c>
       <c r="J277" t="n">
-        <v>14.3726</v>
+        <v>17.5516</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4056</v>
+        <v>0.4645</v>
       </c>
       <c r="J278" t="n">
-        <v>8.9232</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.16</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3323</v>
+        <v>0.3708</v>
       </c>
       <c r="J279" t="n">
-        <v>7.3106</v>
+        <v>8.1576</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.4269</v>
       </c>
       <c r="J280" t="n">
-        <v>-14.1372</v>
+        <v>-9.3918</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.738</v>
+        <v>-0.4994</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.236</v>
+        <v>-10.9868</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.65</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9324</v>
+        <v>0.9162</v>
       </c>
       <c r="J282" t="n">
-        <v>22.3776</v>
+        <v>21.9888</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0893</v>
+        <v>-0.0495</v>
       </c>
       <c r="J283" t="n">
-        <v>-2.1432</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1721</v>
+        <v>-0.0994</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.1304</v>
+        <v>-2.3856</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.75</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4524</v>
+        <v>-0.2876</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.8576</v>
+        <v>-6.9024</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.67</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5579</v>
+        <v>-0.3638</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.3896</v>
+        <v>-8.731199999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6768</v>
+        <v>0.5924</v>
       </c>
       <c r="J287" t="n">
-        <v>16.2432</v>
+        <v>14.2176</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4766</v>
+        <v>0.4019</v>
       </c>
       <c r="J288" t="n">
-        <v>11.4384</v>
+        <v>9.6456</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.96</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1337</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.2088</v>
+        <v>-1.644</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3066</v>
+        <v>-0.1833</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.3584</v>
+        <v>-4.3992</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5032</v>
+        <v>-0.3229</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.0768</v>
+        <v>-7.7496</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.45</v>
       </c>
       <c r="I292" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J292" t="n">
-        <v>26.7709</v>
+        <v>23.8394</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>2.09</v>
       </c>
       <c r="I293" t="n">
-        <v>1.9832</v>
+        <v>1.7056</v>
       </c>
       <c r="J293" t="n">
-        <v>25.7816</v>
+        <v>22.1728</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.74</v>
       </c>
       <c r="I294" t="n">
-        <v>1.3818</v>
+        <v>1.339</v>
       </c>
       <c r="J294" t="n">
-        <v>17.9634</v>
+        <v>17.407</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8554</v>
+        <v>1.0106</v>
       </c>
       <c r="J295" t="n">
-        <v>11.1202</v>
+        <v>13.1378</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.3</v>
       </c>
       <c r="I296" t="n">
-        <v>0.5375</v>
+        <v>0.68</v>
       </c>
       <c r="J296" t="n">
-        <v>6.9875</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.79</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1377</v>
+        <v>-0.1337</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.7901</v>
+        <v>-1.7381</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.54</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.5252</v>
+        <v>-0.4091</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.8276</v>
+        <v>-5.3183</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.454</v>
       </c>
       <c r="J299" t="n">
-        <v>-8.157500000000001</v>
+        <v>-5.902</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6831</v>
+        <v>-0.481</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.8803</v>
+        <v>-6.253</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.2</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0458</v>
+        <v>-0.7392</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.5954</v>
+        <v>-9.6096</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.4</v>
       </c>
       <c r="I302" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J302" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>2.28</v>
       </c>
       <c r="I303" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J303" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5948</v>
+        <v>0.7251</v>
       </c>
       <c r="J304" t="n">
-        <v>8.922000000000001</v>
+        <v>10.8765</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.15</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2532</v>
+        <v>0.361</v>
       </c>
       <c r="J305" t="n">
-        <v>3.798</v>
+        <v>5.415</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.1094</v>
+        <v>-1.1033</v>
       </c>
       <c r="J306" t="n">
-        <v>-16.641</v>
+        <v>-16.5495</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.9</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1054</v>
+        <v>-0.1045</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.581</v>
+        <v>-1.5675</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1401</v>
+        <v>-0.1274</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.1015</v>
+        <v>-1.911</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2077</v>
+        <v>-0.1711</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.1155</v>
+        <v>-2.5665</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.66</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5152</v>
+        <v>-0.3434</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.728</v>
+        <v>-5.151</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6643</v>
+        <v>-0.4463</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.964499999999999</v>
+        <v>-6.6945</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5949</v>
+        <v>1.387</v>
       </c>
       <c r="J312" t="n">
-        <v>35.0878</v>
+        <v>30.514</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.57</v>
       </c>
       <c r="I313" t="n">
-        <v>1.351</v>
+        <v>1.2257</v>
       </c>
       <c r="J313" t="n">
-        <v>29.722</v>
+        <v>26.9654</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1692</v>
+        <v>0.2405</v>
       </c>
       <c r="J314" t="n">
-        <v>3.7224</v>
+        <v>5.291</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3656</v>
+        <v>-0.2872</v>
       </c>
       <c r="J315" t="n">
-        <v>-8.043200000000001</v>
+        <v>-6.3184</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7342</v>
+        <v>-0.6793</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.1524</v>
+        <v>-14.9446</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5505</v>
+        <v>0.6555</v>
       </c>
       <c r="J317" t="n">
-        <v>12.111</v>
+        <v>14.421</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0556</v>
+        <v>-0.0464</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.2232</v>
+        <v>-1.0208</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.91</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1914</v>
+        <v>-0.1177</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.2108</v>
+        <v>-2.5894</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.79</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3857</v>
+        <v>-0.243</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.4854</v>
+        <v>-5.346</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4145</v>
+        <v>-0.2628</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.119</v>
+        <v>-5.7816</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.3643</v>
+        <v>7.7024</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9944</v>
+        <v>3.1319</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6866</v>
+        <v>2.8821</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3643</v>
+        <v>7.7024</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4791</v>
+        <v>2.4321</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8852</v>
+        <v>5.2703</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2486</v>
+        <v>3.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6891</v>
+        <v>1.6903</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8852</v>
+        <v>5.2703</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5743</v>
+        <v>6.960599999999999</v>
       </c>
       <c r="N2" t="n">
         <v>258</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0766</v>
+        <v>7.1339</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8774</v>
+        <v>2.9007</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5567</v>
+        <v>2.6233</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0766</v>
+        <v>7.1339</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8018</v>
+        <v>3.7197</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2748</v>
+        <v>3.4141</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9088</v>
+        <v>7.3786</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1122</v>
+        <v>3.9844</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2748</v>
+        <v>3.4141</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>7.387</v>
+        <v>7.3985</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3962</v>
+        <v>6.5537</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6008</v>
+        <v>2.6648</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2496</v>
+        <v>2.3592</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3962</v>
+        <v>6.5537</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3671</v>
+        <v>2.2895</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0291</v>
+        <v>4.2642</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8537</v>
+        <v>2.6599</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4838</v>
+        <v>1.4363</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0291</v>
+        <v>4.2642</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5129</v>
+        <v>5.7005</v>
       </c>
       <c r="N4" t="n">
         <v>258</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3219</v>
+        <v>5.5351</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1639</v>
+        <v>2.2506</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7646</v>
+        <v>1.8955</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3219</v>
+        <v>5.5351</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8701</v>
+        <v>0.9544</v>
       </c>
       <c r="H5" t="n">
-        <v>11.0894</v>
+        <v>10.9685</v>
       </c>
       <c r="I5" t="n">
-        <v>5.766</v>
+        <v>5.9229</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8701</v>
+        <v>0.9544</v>
       </c>
       <c r="K5" t="n">
         <v>136</v>
@@ -667,7 +667,7 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>6.6361</v>
+        <v>6.8773</v>
       </c>
       <c r="N5" t="n">
         <v>179</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7187</v>
+        <v>4.8466</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9187</v>
+        <v>1.9707</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4922</v>
+        <v>1.5821</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7187</v>
+        <v>4.8466</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2669</v>
+        <v>0.2659</v>
       </c>
       <c r="H6" t="n">
-        <v>11.2379</v>
+        <v>10.5355</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8432</v>
+        <v>5.6891</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2669</v>
+        <v>0.2659</v>
       </c>
       <c r="K6" t="n">
         <v>163</v>
@@ -713,7 +713,7 @@
         <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1101</v>
+        <v>5.955</v>
       </c>
       <c r="N6" t="n">
         <v>212</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5832</v>
+        <v>4.713</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8636</v>
+        <v>1.9164</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4311</v>
+        <v>1.5213</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5832</v>
+        <v>4.713</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1314</v>
+        <v>0.1323</v>
       </c>
       <c r="H7" t="n">
-        <v>11.5466</v>
+        <v>11.4554</v>
       </c>
       <c r="I7" t="n">
-        <v>6.0037</v>
+        <v>6.1858</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1314</v>
+        <v>0.1323</v>
       </c>
       <c r="K7" t="n">
         <v>136</v>
@@ -759,7 +759,7 @@
         <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>6.1351</v>
+        <v>6.3181</v>
       </c>
       <c r="N7" t="n">
         <v>179</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3008</v>
+        <v>4.4943</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7488</v>
+        <v>1.8274</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3036</v>
+        <v>1.4217</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3008</v>
+        <v>4.4943</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7927</v>
+        <v>1.8989</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5081</v>
+        <v>2.5954</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7927</v>
+        <v>1.8989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9321</v>
+        <v>1.0254</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5081</v>
+        <v>2.5954</v>
       </c>
       <c r="K8" t="n">
         <v>104</v>
@@ -805,7 +805,7 @@
         <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4402</v>
+        <v>3.6208</v>
       </c>
       <c r="N8" t="n">
         <v>258</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2039</v>
+        <v>4.2283</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7094</v>
+        <v>1.7193</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2598</v>
+        <v>1.3006</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2039</v>
+        <v>4.2283</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9322</v>
+        <v>3.9156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2717</v>
+        <v>0.3127</v>
       </c>
       <c r="H9" t="n">
-        <v>8.3682</v>
+        <v>8.024900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3511</v>
+        <v>4.3334</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2717</v>
+        <v>0.3127</v>
       </c>
       <c r="K9" t="n">
         <v>106</v>
@@ -851,7 +851,7 @@
         <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6228</v>
+        <v>4.646100000000001</v>
       </c>
       <c r="N9" t="n">
         <v>266</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9664</v>
+        <v>4.1261</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6128</v>
+        <v>1.6777</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1526</v>
+        <v>1.2541</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9664</v>
+        <v>4.1261</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2818</v>
+        <v>2.2171</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6846</v>
+        <v>1.909</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5535</v>
+        <v>2.4208</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3277</v>
+        <v>1.3072</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6846</v>
+        <v>1.909</v>
       </c>
       <c r="K10" t="n">
         <v>104</v>
@@ -897,7 +897,7 @@
         <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0123</v>
+        <v>3.2162</v>
       </c>
       <c r="N10" t="n">
         <v>258</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4527</v>
+        <v>3.3809</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4039</v>
+        <v>1.3747</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9207</v>
+        <v>0.9149</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4527</v>
+        <v>3.3809</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4357</v>
+        <v>3.381</v>
       </c>
       <c r="G11" t="n">
-        <v>0.017</v>
+        <v>-0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.619</v>
+        <v>6.2608</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4416</v>
+        <v>3.3808</v>
       </c>
       <c r="J11" t="n">
-        <v>0.017</v>
+        <v>-0.0001</v>
       </c>
       <c r="K11" t="n">
         <v>163</v>
@@ -943,7 +943,7 @@
         <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4586</v>
+        <v>3.3807</v>
       </c>
       <c r="N11" t="n">
         <v>212</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0463</v>
+        <v>3.051</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2387</v>
+        <v>1.2406</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7372</v>
+        <v>0.7647</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0463</v>
+        <v>3.051</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4923</v>
+        <v>2.41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.554</v>
+        <v>0.641</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2949</v>
+        <v>3.0573</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7132</v>
+        <v>1.6509</v>
       </c>
       <c r="J12" t="n">
-        <v>0.554</v>
+        <v>0.641</v>
       </c>
       <c r="K12" t="n">
         <v>106</v>
@@ -989,7 +989,7 @@
         <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2672</v>
+        <v>2.2919</v>
       </c>
       <c r="N12" t="n">
         <v>266</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7385</v>
+        <v>2.7386</v>
       </c>
       <c r="C13" t="n">
         <v>1.1135</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7385</v>
+        <v>2.7386</v>
       </c>
       <c r="F13" t="n">
-        <v>3.408</v>
+        <v>3.4234</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6695</v>
+        <v>-0.6848</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5213</v>
+        <v>6.401</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3908</v>
+        <v>3.4565</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6695</v>
+        <v>-0.6848</v>
       </c>
       <c r="K13" t="n">
         <v>163</v>
@@ -1035,7 +1035,7 @@
         <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7213</v>
+        <v>2.7717</v>
       </c>
       <c r="N13" t="n">
         <v>212</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7328</v>
+        <v>2.7171</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1112</v>
+        <v>1.1048</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5957</v>
+        <v>0.6127</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7328</v>
+        <v>2.7171</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0213</v>
+        <v>3.0371</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2885</v>
+        <v>-0.32</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1587</v>
+        <v>5.1262</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6823</v>
+        <v>2.7681</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2885</v>
+        <v>-0.32</v>
       </c>
       <c r="K14" t="n">
         <v>163</v>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3938</v>
+        <v>2.4481</v>
       </c>
       <c r="N14" t="n">
         <v>212</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5944</v>
+        <v>2.6649</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0549</v>
+        <v>1.0836</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5332</v>
+        <v>0.5889</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5944</v>
+        <v>2.6649</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2848</v>
+        <v>3.1988</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6904</v>
+        <v>-0.5339</v>
       </c>
       <c r="H15" t="n">
-        <v>6.0873</v>
+        <v>5.6599</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1651</v>
+        <v>3.0563</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6904</v>
+        <v>-0.5339</v>
       </c>
       <c r="K15" t="n">
         <v>104</v>
@@ -1127,7 +1127,7 @@
         <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4747</v>
+        <v>2.5224</v>
       </c>
       <c r="N15" t="n">
         <v>258</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5495</v>
+        <v>2.3857</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0367</v>
+        <v>0.9701</v>
       </c>
       <c r="D16" t="n">
-        <v>0.513</v>
+        <v>0.4618</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5495</v>
+        <v>2.3857</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5495</v>
+        <v>2.3857</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5495</v>
+        <v>2.4967</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5495</v>
+        <v>2.4967</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5495</v>
+        <v>2.4967</v>
       </c>
       <c r="N16" t="n">
         <v>115</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.391</v>
+        <v>2.3583</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9722</v>
+        <v>0.9589</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4414</v>
+        <v>0.4493</v>
       </c>
       <c r="E17" t="n">
-        <v>2.391</v>
+        <v>2.3583</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5154</v>
+        <v>2.4949</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1244</v>
+        <v>-0.1366</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3765</v>
+        <v>3.3373</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7556</v>
+        <v>1.8021</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1244</v>
+        <v>-0.1366</v>
       </c>
       <c r="K17" t="n">
         <v>136</v>
@@ -1219,7 +1219,7 @@
         <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6312</v>
+        <v>1.6655</v>
       </c>
       <c r="N17" t="n">
         <v>179</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2869</v>
+        <v>2.2031</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8958</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3944</v>
+        <v>0.3787</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2869</v>
+        <v>2.2031</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7534</v>
+        <v>2.6963</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4665</v>
+        <v>-0.4932</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2148</v>
+        <v>4.0019</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1915</v>
+        <v>2.161</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4665</v>
+        <v>-0.4932</v>
       </c>
       <c r="K18" t="n">
         <v>136</v>
@@ -1265,7 +1265,7 @@
         <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>1.725</v>
+        <v>1.6678</v>
       </c>
       <c r="N18" t="n">
         <v>179</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8807</v>
+        <v>0.8364</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3398</v>
+        <v>0.3122</v>
       </c>
       <c r="E19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="F19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="I19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.166</v>
+        <v>2.057</v>
       </c>
       <c r="N19" t="n">
         <v>115</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.4892</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0522</v>
+        <v>-0.0765</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2977</v>
+        <v>1.2031</v>
       </c>
       <c r="N20" t="n">
         <v>145</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="C21" t="n">
-        <v>0.525</v>
+        <v>0.4807</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0551</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2911</v>
+        <v>1.1823</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3788</v>
+        <v>0.3465</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2175</v>
+        <v>-0.2363</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9315</v>
+        <v>0.8521</v>
       </c>
       <c r="N22" t="n">
         <v>145</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3152</v>
+        <v>0.2888</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2881</v>
+        <v>-0.3009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7752</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6821</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2773</v>
+        <v>0.2736</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3301</v>
+        <v>-0.3179</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6821</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6821</v>
+        <v>-0.4637</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.1366</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6821</v>
+        <v>-0.4637</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6821</v>
+        <v>-0.2504</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.1366</v>
       </c>
       <c r="K24" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6821</v>
+        <v>0.8862000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>145</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="C25" t="n">
-        <v>0.239</v>
+        <v>0.2309</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3727</v>
+        <v>-0.3657</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5878</v>
+        <v>0.5679</v>
       </c>
       <c r="N25" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5319</v>
+        <v>0.5185</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2163</v>
+        <v>0.2108</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3979</v>
+        <v>-0.3882</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5319</v>
+        <v>0.5185</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5308</v>
+        <v>0.5185</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0627</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5308</v>
+        <v>0.5185</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.276</v>
+        <v>0.5185</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0627</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7867</v>
+        <v>0.5185</v>
       </c>
       <c r="N26" t="n">
-        <v>266</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0712</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5346</v>
+        <v>-0.5444</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2291</v>
+        <v>0.1752</v>
       </c>
       <c r="N27" t="n">
         <v>101</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0694</v>
+        <v>0.0455</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5609</v>
+        <v>-0.5733</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1708</v>
+        <v>0.1118</v>
       </c>
       <c r="N28" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0615</v>
+        <v>0.0414</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5697</v>
+        <v>-0.5779</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1513</v>
+        <v>0.1018</v>
       </c>
       <c r="N29" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0213</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.649</v>
+        <v>-0.6481</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0244</v>
+        <v>-0.0525</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0308</v>
+        <v>-0.0475</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6722</v>
+        <v>-0.6774</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0757</v>
+        <v>-0.1169</v>
       </c>
       <c r="N31" t="n">
         <v>115</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0553</v>
+        <v>-0.0697</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6995</v>
+        <v>-0.7022</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1361</v>
+        <v>-0.1713</v>
       </c>
       <c r="N32" t="n">
         <v>101</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0655</v>
+        <v>-0.095</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7107</v>
+        <v>-0.7306</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1611</v>
+        <v>-0.2337</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2598</v>
+        <v>-0.2825</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9264</v>
+        <v>-0.9405</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6389</v>
+        <v>-0.6948</v>
       </c>
       <c r="N34" t="n">
         <v>101</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3828</v>
+        <v>-0.4018</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0631</v>
+        <v>-1.074</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9415</v>
+        <v>-0.9881</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4241</v>
+        <v>-0.4474</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1089</v>
+        <v>-1.125</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.043</v>
+        <v>-1.1002</v>
       </c>
       <c r="N36" t="n">
         <v>101</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7039</v>
+        <v>-1.38</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6928</v>
+        <v>-0.5611</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.4072</v>
+        <v>-1.2524</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7039</v>
+        <v>-1.38</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7684</v>
+        <v>-1.4384</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0645</v>
+        <v>0.0584</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.7684</v>
+        <v>-1.4384</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9195</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0645</v>
+        <v>0.0584</v>
       </c>
       <c r="K37" t="n">
         <v>163</v>
@@ -2139,7 +2139,7 @@
         <v>49</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.855</v>
+        <v>-0.7182999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>212</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8451</v>
+        <v>-0.8534</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5763</v>
+        <v>-1.5796</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.0783</v>
+        <v>-2.0987</v>
       </c>
       <c r="N38" t="n">
         <v>145</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.3635</v>
+        <v>-1.3244</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.1519</v>
+        <v>-2.1069</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.3533</v>
+        <v>-3.2571</v>
       </c>
       <c r="N39" t="n">
         <v>115</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.5919</v>
+        <v>-4.1624</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.8671</v>
+        <v>-1.6925</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.711</v>
+        <v>-2.519</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.5919</v>
+        <v>-4.1624</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.2078</v>
+        <v>-2.8213</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3841</v>
+        <v>-1.3411</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.2078</v>
+        <v>-2.8213</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6679</v>
+        <v>-1.5235</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.3841</v>
+        <v>-1.3411</v>
       </c>
       <c r="K40" t="n">
         <v>106</v>
@@ -2277,7 +2277,7 @@
         <v>160</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.052</v>
+        <v>-2.8646</v>
       </c>
       <c r="N40" t="n">
         <v>266</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.2987</v>
+        <v>-4.8162</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.1545</v>
+        <v>-1.9583</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.0301</v>
+        <v>-2.8166</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.2987</v>
+        <v>-4.8162</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.836</v>
+        <v>-4.3451</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4627</v>
+        <v>-0.4711</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.836</v>
+        <v>-4.3451</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.5145</v>
+        <v>-2.3463</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4627</v>
+        <v>-0.4711</v>
       </c>
       <c r="K41" t="n">
         <v>136</v>
@@ -2323,7 +2323,7 @@
         <v>43</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9772</v>
+        <v>-2.8174</v>
       </c>
       <c r="N41" t="n">
         <v>179</v>
@@ -2429,10 +2429,10 @@
         <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8094</v>
       </c>
       <c r="J2" t="n">
-        <v>18.1742</v>
+        <v>17.8068</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2638</v>
+        <v>0.2799</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8036</v>
+        <v>6.1578</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0487</v>
+        <v>-0.0525</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0714</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1018</v>
+        <v>-0.1096</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2396</v>
+        <v>-2.4112</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1703</v>
+        <v>-0.1803</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.7466</v>
+        <v>-3.9666</v>
       </c>
     </row>
     <row r="7">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1548</v>
+        <v>0.1649</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4056</v>
+        <v>3.6278</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2304</v>
+        <v>-0.2435</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.0688</v>
+        <v>-5.357</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3844</v>
+        <v>-0.394</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.456799999999999</v>
+        <v>-8.667999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4177</v>
+        <v>0.4111</v>
       </c>
       <c r="J12" t="n">
-        <v>7.9363</v>
+        <v>7.8109</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1505</v>
+        <v>0.1559</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8595</v>
+        <v>2.9621</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1019</v>
+        <v>0.1073</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9361</v>
+        <v>2.0387</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1614</v>
+        <v>-0.1759</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.0666</v>
+        <v>-3.3421</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3964</v>
+        <v>-0.4066</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.5316</v>
+        <v>-7.7254</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3969</v>
+        <v>1.5052</v>
       </c>
       <c r="J17" t="n">
-        <v>26.5411</v>
+        <v>28.5988</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6891</v>
+        <v>0.6632</v>
       </c>
       <c r="J18" t="n">
-        <v>13.0929</v>
+        <v>12.6008</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5965</v>
+        <v>0.5804</v>
       </c>
       <c r="J19" t="n">
-        <v>11.3335</v>
+        <v>11.0276</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3422</v>
+        <v>0.3503</v>
       </c>
       <c r="J20" t="n">
-        <v>6.5018</v>
+        <v>6.6557</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0307</v>
+        <v>0.056</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5833</v>
+        <v>1.064</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2146</v>
+        <v>0.2029</v>
       </c>
       <c r="J22" t="n">
-        <v>4.0774</v>
+        <v>3.8551</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.84</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.174</v>
+        <v>-0.1932</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.306</v>
+        <v>-3.6708</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2798</v>
+        <v>-0.2982</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3162</v>
+        <v>-5.6658</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3177</v>
+        <v>-0.3349</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.0363</v>
+        <v>-6.3631</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.393</v>
+        <v>-0.4072</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.467</v>
+        <v>-7.7368</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.88</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5734</v>
+        <v>1.7071</v>
       </c>
       <c r="J27" t="n">
-        <v>29.8946</v>
+        <v>32.4349</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.47</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0797</v>
+        <v>1.0561</v>
       </c>
       <c r="J28" t="n">
-        <v>20.5143</v>
+        <v>20.0659</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7711</v>
+        <v>0.7376</v>
       </c>
       <c r="J29" t="n">
-        <v>14.6509</v>
+        <v>14.0144</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1726</v>
+        <v>-0.1544</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.2794</v>
+        <v>-2.9336</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2781</v>
+        <v>-0.2567</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.2839</v>
+        <v>-4.8773</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7429</v>
+        <v>0.7341</v>
       </c>
       <c r="J32" t="n">
-        <v>22.287</v>
+        <v>22.023</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2979</v>
+        <v>0.314</v>
       </c>
       <c r="J33" t="n">
-        <v>8.936999999999999</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>2.463</v>
+        <v>2.913</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.971</v>
+        <v>-2.109</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.092</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.76</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6714</v>
+        <v>0.6541</v>
       </c>
       <c r="J37" t="n">
-        <v>20.142</v>
+        <v>19.623</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4431</v>
+        <v>0.4436</v>
       </c>
       <c r="J38" t="n">
-        <v>13.293</v>
+        <v>13.308</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2807</v>
+        <v>0.2899</v>
       </c>
       <c r="J39" t="n">
-        <v>8.420999999999999</v>
+        <v>8.696999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2755</v>
+        <v>-0.287</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.265000000000001</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4351</v>
+        <v>-0.4419</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.053</v>
+        <v>-13.257</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.17</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4156</v>
+        <v>0.4058</v>
       </c>
       <c r="J42" t="n">
-        <v>8.727600000000001</v>
+        <v>8.521800000000001</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
       <c r="J43" t="n">
-        <v>2.394</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1772</v>
+        <v>-0.1932</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.7212</v>
+        <v>-4.0572</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2279</v>
+        <v>-0.2437</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.7859</v>
+        <v>-5.1177</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3347</v>
+        <v>-0.3482</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.0287</v>
+        <v>-7.3122</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.87</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5707</v>
+        <v>1.7027</v>
       </c>
       <c r="J47" t="n">
-        <v>32.9847</v>
+        <v>35.7567</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.79</v>
       </c>
       <c r="I48" t="n">
-        <v>1.4759</v>
+        <v>1.6011</v>
       </c>
       <c r="J48" t="n">
-        <v>30.9939</v>
+        <v>33.6231</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0636</v>
+        <v>0.0896</v>
       </c>
       <c r="J49" t="n">
-        <v>1.3356</v>
+        <v>1.8816</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3948</v>
+        <v>-0.3676</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.290800000000001</v>
+        <v>-7.7196</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6165</v>
+        <v>-0.5693</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.9465</v>
+        <v>-11.9553</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>2.06</v>
       </c>
       <c r="I52" t="n">
-        <v>1.5231</v>
+        <v>1.6502</v>
       </c>
       <c r="J52" t="n">
-        <v>31.9851</v>
+        <v>34.6542</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8881</v>
       </c>
       <c r="J53" t="n">
-        <v>16.8189</v>
+        <v>18.6501</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.354</v>
+        <v>0.3742</v>
       </c>
       <c r="J54" t="n">
-        <v>7.434</v>
+        <v>7.8582</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2001</v>
+        <v>-0.1842</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.2021</v>
+        <v>-3.8682</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.7488</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.178</v>
+        <v>-15.7248</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4198</v>
+        <v>0.4566</v>
       </c>
       <c r="J57" t="n">
-        <v>8.815799999999999</v>
+        <v>9.5886</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1437</v>
+        <v>0.1446</v>
       </c>
       <c r="J58" t="n">
-        <v>3.0177</v>
+        <v>3.0366</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0091</v>
+        <v>-0.0165</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.1911</v>
+        <v>-0.3465</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3329</v>
+        <v>-0.3468</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.9909</v>
+        <v>-7.2828</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4633</v>
+        <v>-0.4715</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.7293</v>
+        <v>-9.9015</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7446</v>
+        <v>0.8227</v>
       </c>
       <c r="J62" t="n">
-        <v>16.3812</v>
+        <v>18.0994</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6099</v>
+        <v>0.6756</v>
       </c>
       <c r="J63" t="n">
-        <v>13.4178</v>
+        <v>14.8632</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4843</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>10.6546</v>
+        <v>11.7876</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1597</v>
+        <v>0.1746</v>
       </c>
       <c r="J65" t="n">
-        <v>3.5134</v>
+        <v>3.8412</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4246</v>
+        <v>-0.4012</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.341200000000001</v>
+        <v>-8.8264</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4503</v>
+        <v>0.4978</v>
       </c>
       <c r="J67" t="n">
-        <v>9.906599999999999</v>
+        <v>10.9516</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1405</v>
+        <v>0.1488</v>
       </c>
       <c r="J68" t="n">
-        <v>3.091</v>
+        <v>3.2736</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0132</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1336</v>
+        <v>-0.1464</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.9392</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2681</v>
+        <v>-0.2812</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.8982</v>
+        <v>-6.1864</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8559</v>
+        <v>0.9415</v>
       </c>
       <c r="J72" t="n">
-        <v>25.677</v>
+        <v>28.245</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5868</v>
+        <v>0.649</v>
       </c>
       <c r="J73" t="n">
-        <v>17.604</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5163</v>
+        <v>0.5708</v>
       </c>
       <c r="J74" t="n">
-        <v>15.489</v>
+        <v>17.124</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1309</v>
+        <v>-0.1252</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.927</v>
+        <v>-3.756</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7639</v>
+        <v>-0.7063</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.917</v>
+        <v>-21.189</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3044</v>
+        <v>0.304</v>
       </c>
       <c r="J77" t="n">
-        <v>9.132</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0785</v>
+        <v>0.0823</v>
       </c>
       <c r="J78" t="n">
-        <v>2.355</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.1071</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.829</v>
+        <v>-3.213</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1278</v>
+        <v>-0.1419</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.834</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3005</v>
+        <v>-0.3142</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.015000000000001</v>
+        <v>-9.426</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.15</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6102</v>
+        <v>1.7427</v>
       </c>
       <c r="J82" t="n">
-        <v>30.5938</v>
+        <v>33.1113</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.46</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7932</v>
+        <v>0.8814</v>
       </c>
       <c r="J83" t="n">
-        <v>15.0708</v>
+        <v>16.7466</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1241</v>
+        <v>0.1498</v>
       </c>
       <c r="J84" t="n">
-        <v>2.3579</v>
+        <v>2.8462</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.173</v>
+        <v>-0.1547</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.287</v>
+        <v>-2.9393</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2786</v>
+        <v>-0.257</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.2934</v>
+        <v>-4.883</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.365</v>
+        <v>0.3726</v>
       </c>
       <c r="J87" t="n">
-        <v>6.935</v>
+        <v>7.0794</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1884</v>
+        <v>0.1836</v>
       </c>
       <c r="J88" t="n">
-        <v>3.5796</v>
+        <v>3.4884</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1607</v>
+        <v>-0.1781</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.0533</v>
+        <v>-3.3839</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2874</v>
+        <v>-0.3041</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.4606</v>
+        <v>-5.7779</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5752</v>
+        <v>-0.5777</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.9288</v>
+        <v>-10.9763</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.16</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3944</v>
+        <v>0.3864</v>
       </c>
       <c r="J92" t="n">
-        <v>7.888</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3347</v>
+        <v>0.3304</v>
       </c>
       <c r="J93" t="n">
-        <v>6.694</v>
+        <v>6.608</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1569</v>
+        <v>-0.1725</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.138</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2284</v>
+        <v>-0.2441</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.568</v>
+        <v>-4.882</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4194</v>
+        <v>-0.4295</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.388</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.93</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6628</v>
+        <v>1.6556</v>
       </c>
       <c r="J97" t="n">
-        <v>33.256</v>
+        <v>33.112</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7872</v>
+        <v>0.7486</v>
       </c>
       <c r="J98" t="n">
-        <v>15.744</v>
+        <v>14.972</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.508</v>
+        <v>0.4989</v>
       </c>
       <c r="J99" t="n">
-        <v>10.16</v>
+        <v>9.978</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1095</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.19</v>
+        <v>-1.952</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8811</v>
+        <v>-0.8061</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.622</v>
+        <v>-16.122</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.27</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8414</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>12.621</v>
+        <v>11.3325</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.64</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.341</v>
+        <v>-0.3619</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.115</v>
+        <v>-5.4285</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.52</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4496</v>
+        <v>-0.4652</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.744</v>
+        <v>-6.978</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.35</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6109</v>
+        <v>-0.6148</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.163500000000001</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.31</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6491</v>
+        <v>-0.6499</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.736499999999999</v>
+        <v>-9.7485</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J107" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.28</v>
       </c>
       <c r="I108" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J108" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.43</v>
       </c>
       <c r="I109" t="n">
-        <v>0.988</v>
+        <v>0.9452</v>
       </c>
       <c r="J109" t="n">
-        <v>14.82</v>
+        <v>14.178</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I110" t="n">
-        <v>0.501</v>
+        <v>0.5091</v>
       </c>
       <c r="J110" t="n">
-        <v>7.515</v>
+        <v>7.6365</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9718</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.577</v>
+        <v>-13.1175</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.72</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4386</v>
+        <v>1.4163</v>
       </c>
       <c r="J112" t="n">
-        <v>34.5264</v>
+        <v>33.9912</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.906</v>
+        <v>0.8479</v>
       </c>
       <c r="J113" t="n">
-        <v>21.744</v>
+        <v>20.3496</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4474</v>
+        <v>0.4405</v>
       </c>
       <c r="J114" t="n">
-        <v>10.7376</v>
+        <v>10.572</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.95</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2344</v>
+        <v>-0.2261</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.6256</v>
+        <v>-5.4264</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.3104</v>
+        <v>-1.1794</v>
       </c>
       <c r="J116" t="n">
-        <v>-31.4496</v>
+        <v>-28.3056</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.53</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9998</v>
+        <v>0.9482</v>
       </c>
       <c r="J117" t="n">
-        <v>23.9952</v>
+        <v>22.7568</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0484</v>
+        <v>-0.0569</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.1616</v>
+        <v>-1.3656</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2165</v>
+        <v>-0.2306</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.196</v>
+        <v>-5.5344</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2367</v>
+        <v>-0.2506</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.6808</v>
+        <v>-6.0144</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2566</v>
+        <v>-0.2702</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.1584</v>
+        <v>-6.4848</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.89</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J122" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.85</v>
       </c>
       <c r="I123" t="n">
-        <v>1.4708</v>
+        <v>1.4706</v>
       </c>
       <c r="J123" t="n">
-        <v>22.062</v>
+        <v>22.059</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>1.1624</v>
+        <v>1.1401</v>
       </c>
       <c r="J124" t="n">
-        <v>17.436</v>
+        <v>17.1015</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0576</v>
+        <v>0.103</v>
       </c>
       <c r="J125" t="n">
-        <v>0.864</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.91</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4639</v>
+        <v>-0.4164</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.9585</v>
+        <v>-6.246</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.92</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0437</v>
+        <v>-0.0707</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.6555</v>
+        <v>-1.0605</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.72</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2694</v>
+        <v>-0.2922</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.041</v>
+        <v>-4.383</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2891</v>
+        <v>-0.3111</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.3365</v>
+        <v>-4.6665</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3708</v>
+        <v>-0.3899</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.562</v>
+        <v>-5.8485</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.27</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6907</v>
+        <v>-0.6875</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.3605</v>
+        <v>-10.3125</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9555</v>
+        <v>0.9377</v>
       </c>
       <c r="J132" t="n">
-        <v>16.2435</v>
+        <v>15.9409</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8181</v>
+        <v>0.8095</v>
       </c>
       <c r="J133" t="n">
-        <v>13.9077</v>
+        <v>13.7615</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.38</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4728</v>
+        <v>0.4868</v>
       </c>
       <c r="J134" t="n">
-        <v>8.037599999999999</v>
+        <v>8.275600000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1082</v>
+        <v>-0.1113</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.8394</v>
+        <v>-1.8921</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3096</v>
+        <v>-0.3158</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.2632</v>
+        <v>-5.3686</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.01</v>
       </c>
       <c r="I137" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0737</v>
       </c>
       <c r="J137" t="n">
-        <v>1.3957</v>
+        <v>1.2529</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.84</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1731</v>
+        <v>-0.1925</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.9427</v>
+        <v>-3.2725</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2231</v>
+        <v>-0.2423</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7927</v>
+        <v>-4.1191</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.64</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.364</v>
+        <v>-0.3796</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.188</v>
+        <v>-6.4532</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3921</v>
+        <v>-0.4065</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.6657</v>
+        <v>-6.9105</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5646</v>
+        <v>0.5367</v>
       </c>
       <c r="J142" t="n">
-        <v>10.7274</v>
+        <v>10.1973</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.93</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0828</v>
+        <v>-0.0984</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.5732</v>
+        <v>-1.8696</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1902</v>
+        <v>-0.2079</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.6138</v>
+        <v>-3.9501</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3729</v>
+        <v>-0.3866</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.0851</v>
+        <v>-7.3454</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4381</v>
+        <v>-0.4488</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.3239</v>
+        <v>-8.527200000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.19</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8338</v>
+        <v>1.9161</v>
       </c>
       <c r="J147" t="n">
-        <v>34.8422</v>
+        <v>36.4059</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1306</v>
+        <v>1.0996</v>
       </c>
       <c r="J148" t="n">
-        <v>21.4814</v>
+        <v>20.8924</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6674</v>
+        <v>0.6483</v>
       </c>
       <c r="J149" t="n">
-        <v>12.6806</v>
+        <v>12.3177</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1412</v>
+        <v>0.1697</v>
       </c>
       <c r="J150" t="n">
-        <v>2.6828</v>
+        <v>3.2243</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4736</v>
+        <v>-0.4356</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.9984</v>
+        <v>-8.276400000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7409</v>
+        <v>0.7059</v>
       </c>
       <c r="J152" t="n">
-        <v>20.7452</v>
+        <v>19.7652</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2169</v>
+        <v>0.2211</v>
       </c>
       <c r="J153" t="n">
-        <v>6.0732</v>
+        <v>6.1908</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0074</v>
+        <v>0.0052</v>
       </c>
       <c r="J154" t="n">
-        <v>0.2072</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2925</v>
+        <v>-0.3062</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.19</v>
+        <v>-8.573600000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4335</v>
+        <v>-0.4421</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.138</v>
+        <v>-12.3788</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3212</v>
+        <v>1.2953</v>
       </c>
       <c r="J157" t="n">
-        <v>36.9936</v>
+        <v>36.2684</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.75</v>
+        <v>0.7141</v>
       </c>
       <c r="J158" t="n">
-        <v>21</v>
+        <v>19.9948</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.17</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4895</v>
+        <v>0.4808</v>
       </c>
       <c r="J159" t="n">
-        <v>13.706</v>
+        <v>13.4624</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.98</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1422</v>
+        <v>-0.1331</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.9816</v>
+        <v>-3.7268</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.458</v>
+        <v>-0.4306</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.824</v>
+        <v>-12.0568</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0287</v>
+        <v>0.0207</v>
       </c>
       <c r="J162" t="n">
-        <v>0.6888</v>
+        <v>0.4968</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0366</v>
+        <v>-0.048</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.8784</v>
+        <v>-1.152</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.92</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0997</v>
+        <v>-0.1145</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.3928</v>
+        <v>-2.748</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2037</v>
+        <v>-0.2206</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.8888</v>
+        <v>-5.2944</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3587</v>
+        <v>-0.3721</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.6088</v>
+        <v>-8.930400000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0447</v>
+        <v>0.989</v>
       </c>
       <c r="J167" t="n">
-        <v>25.0728</v>
+        <v>23.736</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.726</v>
+        <v>0.6886</v>
       </c>
       <c r="J168" t="n">
-        <v>17.424</v>
+        <v>16.5264</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4521</v>
+        <v>0.4437</v>
       </c>
       <c r="J169" t="n">
-        <v>10.8504</v>
+        <v>10.6488</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.88</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4382</v>
+        <v>-0.4167</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.5168</v>
+        <v>-10.0008</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4661</v>
+        <v>-0.4421</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.1864</v>
+        <v>-10.6104</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3992</v>
+        <v>0.3975</v>
       </c>
       <c r="J172" t="n">
-        <v>15.968</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3617</v>
+        <v>0.3624</v>
       </c>
       <c r="J173" t="n">
-        <v>14.468</v>
+        <v>14.496</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0368</v>
+        <v>0.0427</v>
       </c>
       <c r="J174" t="n">
-        <v>1.472</v>
+        <v>1.708</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0211</v>
+        <v>-0.0257</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.844</v>
+        <v>-1.028</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3371</v>
+        <v>-0.3484</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.484</v>
+        <v>-13.936</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.257</v>
+        <v>1.2252</v>
       </c>
       <c r="J177" t="n">
-        <v>50.28</v>
+        <v>49.008</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.15</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4456</v>
+        <v>0.4394</v>
       </c>
       <c r="J178" t="n">
-        <v>17.824</v>
+        <v>17.576</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.11</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3411</v>
+        <v>0.3433</v>
       </c>
       <c r="J179" t="n">
-        <v>13.644</v>
+        <v>13.732</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.652</v>
+        <v>-3.392</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3016</v>
+        <v>-0.2885</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.064</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5454</v>
       </c>
       <c r="J182" t="n">
-        <v>11.9196</v>
+        <v>11.9988</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4251</v>
+        <v>0.4352</v>
       </c>
       <c r="J183" t="n">
-        <v>9.3522</v>
+        <v>9.574400000000001</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1331</v>
+        <v>0.1483</v>
       </c>
       <c r="J184" t="n">
-        <v>2.9282</v>
+        <v>3.2626</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0102</v>
+        <v>-0.0078</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.2244</v>
+        <v>-0.1716</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2811</v>
+        <v>-0.2914</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.1842</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5229</v>
+        <v>0.513</v>
       </c>
       <c r="J187" t="n">
-        <v>11.5038</v>
+        <v>11.286</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1124</v>
+        <v>0.1201</v>
       </c>
       <c r="J188" t="n">
-        <v>2.4728</v>
+        <v>2.6422</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0728</v>
+        <v>-0.0837</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.6016</v>
+        <v>-1.8414</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.113</v>
+        <v>-3.4166</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4164</v>
+        <v>-0.4256</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.1608</v>
+        <v>-9.363200000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7126</v>
+        <v>0.6822</v>
       </c>
       <c r="J192" t="n">
-        <v>15.6772</v>
+        <v>15.0084</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.99</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0192</v>
+        <v>-0.0243</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.4224</v>
+        <v>-0.5346</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0482</v>
+        <v>-0.0568</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.0604</v>
+        <v>-1.2496</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1536</v>
+        <v>-0.1674</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.3792</v>
+        <v>-3.6828</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3337</v>
+        <v>-0.3457</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.3414</v>
+        <v>-7.6054</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7164</v>
+        <v>0.6774</v>
       </c>
       <c r="J197" t="n">
-        <v>15.7608</v>
+        <v>14.9028</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5662</v>
+        <v>0.5441</v>
       </c>
       <c r="J198" t="n">
-        <v>12.4564</v>
+        <v>11.9702</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0709</v>
+        <v>-0.0707</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.5598</v>
+        <v>-1.5554</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.98</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1119</v>
+        <v>-0.112</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.4618</v>
+        <v>-2.464</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.96</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1838</v>
+        <v>-0.1822</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.0436</v>
+        <v>-4.0084</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3763</v>
+        <v>0.3692</v>
       </c>
       <c r="J202" t="n">
-        <v>7.9023</v>
+        <v>7.7532</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.04</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1392</v>
+        <v>0.1413</v>
       </c>
       <c r="J203" t="n">
-        <v>2.9232</v>
+        <v>2.9673</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.83</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1977</v>
+        <v>-0.2137</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.1517</v>
+        <v>-4.4877</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.2017</v>
+        <v>-5.5293</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2868</v>
+        <v>-0.3017</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.0228</v>
+        <v>-6.3357</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.54</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1909</v>
+        <v>1.1575</v>
       </c>
       <c r="J207" t="n">
-        <v>25.0089</v>
+        <v>24.3075</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0757</v>
+        <v>1.0314</v>
       </c>
       <c r="J208" t="n">
-        <v>22.5897</v>
+        <v>21.6594</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8119</v>
       </c>
       <c r="J209" t="n">
-        <v>18.0684</v>
+        <v>17.0499</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5357</v>
+        <v>0.5233</v>
       </c>
       <c r="J210" t="n">
-        <v>11.2497</v>
+        <v>10.9893</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.52</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.3457</v>
+        <v>-1.2077</v>
       </c>
       <c r="J211" t="n">
-        <v>-28.2597</v>
+        <v>-25.3617</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6643</v>
+        <v>0.6409</v>
       </c>
       <c r="J212" t="n">
-        <v>15.2789</v>
+        <v>14.7407</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3416</v>
+        <v>0.3437</v>
       </c>
       <c r="J213" t="n">
-        <v>7.8568</v>
+        <v>7.9051</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1593</v>
+        <v>0.1684</v>
       </c>
       <c r="J214" t="n">
-        <v>3.6639</v>
+        <v>3.8732</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2404</v>
+        <v>-0.2535</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.5292</v>
+        <v>-5.8305</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3186</v>
+        <v>-0.3302</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.3278</v>
+        <v>-7.5946</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.9</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6518</v>
+        <v>1.6405</v>
       </c>
       <c r="J217" t="n">
-        <v>37.9914</v>
+        <v>37.7315</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.1</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3117</v>
+        <v>0.3166</v>
       </c>
       <c r="J218" t="n">
-        <v>7.1691</v>
+        <v>7.2818</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0384</v>
+        <v>-0.0265</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.8832</v>
+        <v>-0.6095</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3037</v>
+        <v>-0.2899</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.9851</v>
+        <v>-6.6677</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4783</v>
+        <v>-0.4506</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.0009</v>
+        <v>-10.3638</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.634</v>
+        <v>0.6038</v>
       </c>
       <c r="J222" t="n">
-        <v>11.412</v>
+        <v>10.8684</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0255</v>
+        <v>0.0184</v>
       </c>
       <c r="J223" t="n">
-        <v>0.459</v>
+        <v>0.3312</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1439</v>
+        <v>-0.1599</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.5902</v>
+        <v>-2.8782</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2933</v>
+        <v>-0.3086</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.2794</v>
+        <v>-5.5548</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.53</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4804</v>
+        <v>-0.4879</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.6472</v>
+        <v>-8.7822</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I227" t="n">
-        <v>1.6449</v>
+        <v>1.6432</v>
       </c>
       <c r="J227" t="n">
-        <v>29.6082</v>
+        <v>29.5776</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.68</v>
       </c>
       <c r="I228" t="n">
-        <v>1.329</v>
+        <v>1.3108</v>
       </c>
       <c r="J228" t="n">
-        <v>23.922</v>
+        <v>23.5944</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1114</v>
+        <v>1.0778</v>
       </c>
       <c r="J229" t="n">
-        <v>20.0052</v>
+        <v>19.4004</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.01</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.0292</v>
+        <v>0.0014</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.5256</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.1651</v>
+        <v>-1.0491</v>
       </c>
       <c r="J231" t="n">
-        <v>-20.9718</v>
+        <v>-18.8838</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9697</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="J232" t="n">
-        <v>18.4243</v>
+        <v>17.3812</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1718</v>
+        <v>0.1774</v>
       </c>
       <c r="J233" t="n">
-        <v>3.2642</v>
+        <v>3.3706</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0174</v>
+        <v>-0.0229</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.3306</v>
+        <v>-0.4351</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4063</v>
+        <v>-0.416</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.7197</v>
+        <v>-7.904</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4063</v>
+        <v>-0.416</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.7197</v>
+        <v>-7.904</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.66</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3278</v>
+        <v>1.3055</v>
       </c>
       <c r="J237" t="n">
-        <v>25.2282</v>
+        <v>24.8045</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8476</v>
+        <v>0.803</v>
       </c>
       <c r="J238" t="n">
-        <v>16.1044</v>
+        <v>15.257</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>11.3829</v>
+        <v>11.0618</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.11</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3179</v>
+        <v>0.3273</v>
       </c>
       <c r="J240" t="n">
-        <v>6.0401</v>
+        <v>6.2187</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2637</v>
+        <v>-0.2466</v>
       </c>
       <c r="J241" t="n">
-        <v>-5.0103</v>
+        <v>-4.6854</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0275</v>
+        <v>0.9787</v>
       </c>
       <c r="J242" t="n">
-        <v>23.6325</v>
+        <v>22.5101</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0427</v>
+        <v>0.0469</v>
       </c>
       <c r="J243" t="n">
-        <v>0.9821</v>
+        <v>1.0787</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.87</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1634</v>
+        <v>-0.1775</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.7582</v>
+        <v>-4.0825</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2153</v>
+        <v>-0.2296</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.9519</v>
+        <v>-5.2808</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4261</v>
+        <v>-0.4347</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.8003</v>
+        <v>-9.998100000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.65</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3533</v>
+        <v>1.326</v>
       </c>
       <c r="J247" t="n">
-        <v>31.1259</v>
+        <v>30.498</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.25</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6966</v>
+        <v>0.6636</v>
       </c>
       <c r="J248" t="n">
-        <v>16.0218</v>
+        <v>15.2628</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.25</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6966</v>
+        <v>0.6636</v>
       </c>
       <c r="J249" t="n">
-        <v>16.0218</v>
+        <v>15.2628</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3854</v>
+        <v>-0.3674</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.8642</v>
+        <v>-8.450200000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.1469</v>
+        <v>-1.0398</v>
       </c>
       <c r="J251" t="n">
-        <v>-26.3787</v>
+        <v>-23.9154</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.8</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5037</v>
+        <v>1.4899</v>
       </c>
       <c r="J252" t="n">
-        <v>30.074</v>
+        <v>29.798</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.32</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>16.602</v>
+        <v>15.736</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.28</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7393</v>
+        <v>0.7068</v>
       </c>
       <c r="J254" t="n">
-        <v>14.786</v>
+        <v>14.136</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2367</v>
+        <v>0.251</v>
       </c>
       <c r="J255" t="n">
-        <v>4.734</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9559</v>
+        <v>-0.8711</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.118</v>
+        <v>-17.422</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5827</v>
+        <v>0.5566</v>
       </c>
       <c r="J257" t="n">
-        <v>11.654</v>
+        <v>11.132</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.04</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1499</v>
+        <v>0.1491</v>
       </c>
       <c r="J258" t="n">
-        <v>2.998</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0882</v>
+        <v>-0.1025</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.764</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3683</v>
+        <v>-0.3814</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.366</v>
+        <v>-7.628</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4977</v>
+        <v>-0.5044</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.954000000000001</v>
+        <v>-10.088</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3746</v>
+        <v>1.3574</v>
       </c>
       <c r="J262" t="n">
-        <v>26.1174</v>
+        <v>25.7906</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.65</v>
       </c>
       <c r="I263" t="n">
-        <v>1.3024</v>
+        <v>1.2808</v>
       </c>
       <c r="J263" t="n">
-        <v>24.7456</v>
+        <v>24.3352</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5643</v>
+        <v>0.5532</v>
       </c>
       <c r="J264" t="n">
-        <v>10.7217</v>
+        <v>10.5108</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.12</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3329</v>
+        <v>0.3439</v>
       </c>
       <c r="J265" t="n">
-        <v>6.3251</v>
+        <v>6.5341</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5679</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.7901</v>
+        <v>-9.9693</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3708</v>
+        <v>0.357</v>
       </c>
       <c r="J267" t="n">
-        <v>7.0452</v>
+        <v>6.783</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.96</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0427</v>
+        <v>-0.0568</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.8113</v>
+        <v>-1.0792</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2668</v>
+        <v>-0.2842</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.0692</v>
+        <v>-5.3998</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.67</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3432</v>
+        <v>-0.3583</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.5208</v>
+        <v>-6.8077</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3715</v>
+        <v>-0.3855</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.0585</v>
+        <v>-7.3245</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.51</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1681</v>
+        <v>1.1302</v>
       </c>
       <c r="J272" t="n">
-        <v>25.6982</v>
+        <v>24.8644</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.667</v>
+        <v>0.6385</v>
       </c>
       <c r="J273" t="n">
-        <v>14.674</v>
+        <v>14.047</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J274" t="n">
-        <v>6.2942</v>
+        <v>6.4284</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0353</v>
+        <v>-0.0243</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.7766</v>
+        <v>-0.5346</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3902</v>
+        <v>-0.3708</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.5844</v>
+        <v>-8.1576</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7978</v>
+        <v>0.7587</v>
       </c>
       <c r="J277" t="n">
-        <v>17.5516</v>
+        <v>16.6914</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4645</v>
+        <v>0.4562</v>
       </c>
       <c r="J278" t="n">
-        <v>10.219</v>
+        <v>10.0364</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.16</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3708</v>
+        <v>0.369</v>
       </c>
       <c r="J279" t="n">
-        <v>8.1576</v>
+        <v>8.118</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4269</v>
+        <v>-0.4354</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.3918</v>
+        <v>-9.578799999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4994</v>
+        <v>-0.5044</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.9868</v>
+        <v>-11.0968</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.65</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9162</v>
+        <v>0.8721</v>
       </c>
       <c r="J282" t="n">
-        <v>21.9888</v>
+        <v>20.9304</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0495</v>
+        <v>-0.0578</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.188</v>
+        <v>-1.3872</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0994</v>
+        <v>-0.111</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.3856</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.75</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2876</v>
+        <v>-0.3004</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.9024</v>
+        <v>-7.2096</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.67</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3638</v>
+        <v>-0.3745</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.731199999999999</v>
+        <v>-8.988</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5924</v>
+        <v>0.5901</v>
       </c>
       <c r="J287" t="n">
-        <v>14.2176</v>
+        <v>14.1624</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4019</v>
+        <v>0.4105</v>
       </c>
       <c r="J288" t="n">
-        <v>9.6456</v>
+        <v>9.852</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.96</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0765</v>
       </c>
       <c r="J289" t="n">
-        <v>-1.644</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1833</v>
+        <v>-0.1955</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.3992</v>
+        <v>-4.692</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3229</v>
+        <v>-0.3337</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.7496</v>
+        <v>-8.008800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.45</v>
       </c>
       <c r="I292" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J292" t="n">
-        <v>23.8394</v>
+        <v>25.1836</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>2.09</v>
       </c>
       <c r="I293" t="n">
-        <v>1.7056</v>
+        <v>1.7218</v>
       </c>
       <c r="J293" t="n">
-        <v>22.1728</v>
+        <v>22.3834</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.74</v>
       </c>
       <c r="I294" t="n">
-        <v>1.339</v>
+        <v>1.3329</v>
       </c>
       <c r="J294" t="n">
-        <v>17.407</v>
+        <v>17.3277</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>1.0106</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="J295" t="n">
-        <v>13.1378</v>
+        <v>12.6659</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.3</v>
       </c>
       <c r="I296" t="n">
-        <v>0.68</v>
+        <v>0.6742</v>
       </c>
       <c r="J296" t="n">
-        <v>8.84</v>
+        <v>8.7646</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.79</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1337</v>
+        <v>-0.1721</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.7381</v>
+        <v>-2.2373</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.54</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.4091</v>
+        <v>-0.4309</v>
       </c>
       <c r="J298" t="n">
-        <v>-5.3183</v>
+        <v>-5.6017</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.454</v>
+        <v>-0.4731</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.902</v>
+        <v>-6.1503</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.481</v>
+        <v>-0.4984</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.253</v>
+        <v>-6.4792</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.2</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7392</v>
+        <v>-0.7339</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.6096</v>
+        <v>-9.540699999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.4</v>
       </c>
       <c r="I302" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J302" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>2.28</v>
       </c>
       <c r="I303" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J303" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7251</v>
+        <v>0.7059</v>
       </c>
       <c r="J304" t="n">
-        <v>10.8765</v>
+        <v>10.5885</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.15</v>
       </c>
       <c r="I305" t="n">
-        <v>0.361</v>
+        <v>0.3806</v>
       </c>
       <c r="J305" t="n">
-        <v>5.415</v>
+        <v>5.709</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.1033</v>
+        <v>-0.9908</v>
       </c>
       <c r="J306" t="n">
-        <v>-16.5495</v>
+        <v>-14.862</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.9</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1045</v>
+        <v>-0.124</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.5675</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1274</v>
+        <v>-0.1472</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.911</v>
+        <v>-2.208</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1711</v>
+        <v>-0.1909</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.5665</v>
+        <v>-2.8635</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.66</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3434</v>
+        <v>-0.3602</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.151</v>
+        <v>-5.403</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4463</v>
+        <v>-0.4582</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.6945</v>
+        <v>-6.873</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.387</v>
+        <v>1.3664</v>
       </c>
       <c r="J312" t="n">
-        <v>30.514</v>
+        <v>30.0608</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.57</v>
       </c>
       <c r="I313" t="n">
-        <v>1.2257</v>
+        <v>1.1952</v>
       </c>
       <c r="J313" t="n">
-        <v>26.9654</v>
+        <v>26.2944</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2405</v>
+        <v>0.2537</v>
       </c>
       <c r="J314" t="n">
-        <v>5.291</v>
+        <v>5.5814</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2872</v>
+        <v>-0.2709</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.3184</v>
+        <v>-5.9598</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6793</v>
+        <v>-0.6283</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.9446</v>
+        <v>-13.8226</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6555</v>
+        <v>0.6286</v>
       </c>
       <c r="J317" t="n">
-        <v>14.421</v>
+        <v>13.8292</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0464</v>
+        <v>-0.0554</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.0208</v>
+        <v>-1.2188</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.91</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1177</v>
+        <v>-0.1313</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.5894</v>
+        <v>-2.8886</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.79</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.243</v>
+        <v>-0.2576</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.346</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2628</v>
+        <v>-0.2771</v>
       </c>
       <c r="J321" t="n">
-        <v>-5.7816</v>
+        <v>-6.0962</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7024</v>
+        <v>7.8895</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1319</v>
+        <v>3.208</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8821</v>
+        <v>2.9102</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7024</v>
+        <v>7.8895</v>
       </c>
       <c r="F2" t="n">
         <v>2.4321</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2703</v>
+        <v>5.2713</v>
       </c>
       <c r="H2" t="n">
         <v>3.1302</v>
@@ -520,7 +520,7 @@
         <v>1.6903</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2703</v>
+        <v>5.2713</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>6.960599999999999</v>
+        <v>6.9616</v>
       </c>
       <c r="N2" t="n">
         <v>258</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1339</v>
+        <v>7.4904</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9007</v>
+        <v>3.0457</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6233</v>
+        <v>2.732</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1339</v>
+        <v>7.4904</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7197</v>
+        <v>3.72</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4141</v>
+        <v>3.423</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3786</v>
+        <v>7.3794</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9844</v>
+        <v>3.9848</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4141</v>
+        <v>3.423</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>7.3985</v>
+        <v>7.4078</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5537</v>
+        <v>6.588</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6648</v>
+        <v>2.6788</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3592</v>
+        <v>2.3289</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5537</v>
+        <v>6.588</v>
       </c>
       <c r="F4" t="n">
         <v>2.2895</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2642</v>
+        <v>4.265</v>
       </c>
       <c r="H4" t="n">
         <v>2.6599</v>
@@ -612,7 +612,7 @@
         <v>1.4363</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2642</v>
+        <v>4.265</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7005</v>
+        <v>5.7013</v>
       </c>
       <c r="N4" t="n">
         <v>258</v>
@@ -634,40 +634,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5351</v>
+        <v>6.3683</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2506</v>
+        <v>2.5894</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8955</v>
+        <v>2.2308</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5351</v>
+        <v>6.3683</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5807</v>
+        <v>3.0638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9544</v>
+        <v>2.8642</v>
       </c>
       <c r="H5" t="n">
-        <v>10.9685</v>
+        <v>3.9807</v>
       </c>
       <c r="I5" t="n">
-        <v>5.9229</v>
+        <v>4.0833</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9544</v>
+        <v>2.8642</v>
       </c>
       <c r="K5" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8773</v>
+        <v>6.9475</v>
       </c>
       <c r="N5" t="n">
         <v>179</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8466</v>
+        <v>5.9239</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9707</v>
+        <v>2.4087</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5821</v>
+        <v>2.0323</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8466</v>
+        <v>5.9239</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5807</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2659</v>
+        <v>3.1619</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5355</v>
+        <v>2.528</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6891</v>
+        <v>2.5931</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2659</v>
+        <v>3.1619</v>
       </c>
       <c r="K6" t="n">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>5.955</v>
+        <v>5.755000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.713</v>
+        <v>5.5089</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9164</v>
+        <v>2.24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5213</v>
+        <v>1.8469</v>
       </c>
       <c r="E7" t="n">
-        <v>4.713</v>
+        <v>5.5089</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5807</v>
+        <v>2.4929</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1323</v>
+        <v>2.7555</v>
       </c>
       <c r="H7" t="n">
-        <v>11.4554</v>
+        <v>2.7313</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1858</v>
+        <v>2.8017</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1323</v>
+        <v>2.7555</v>
       </c>
       <c r="K7" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>6.3181</v>
+        <v>5.5572</v>
       </c>
       <c r="N7" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4943</v>
+        <v>4.4539</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8274</v>
+        <v>1.811</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4217</v>
+        <v>1.3756</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4943</v>
+        <v>4.4539</v>
       </c>
       <c r="F8" t="n">
         <v>1.8989</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5954</v>
+        <v>2.5958</v>
       </c>
       <c r="H8" t="n">
         <v>1.8989</v>
@@ -796,7 +796,7 @@
         <v>1.0254</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5954</v>
+        <v>2.5958</v>
       </c>
       <c r="K8" t="n">
         <v>104</v>
@@ -805,7 +805,7 @@
         <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6208</v>
+        <v>3.6212</v>
       </c>
       <c r="N8" t="n">
         <v>258</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2283</v>
+        <v>4.3197</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7193</v>
+        <v>1.7564</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3006</v>
+        <v>1.3157</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2283</v>
+        <v>4.3197</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9156</v>
+        <v>3.916</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3127</v>
+        <v>0.3125</v>
       </c>
       <c r="H9" t="n">
-        <v>8.024900000000001</v>
+        <v>8.026</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3334</v>
+        <v>4.334</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3127</v>
+        <v>0.3125</v>
       </c>
       <c r="K9" t="n">
         <v>106</v>
@@ -851,7 +851,7 @@
         <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>4.646100000000001</v>
+        <v>4.6465</v>
       </c>
       <c r="N9" t="n">
         <v>266</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1261</v>
+        <v>4.1435</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6777</v>
+        <v>1.6848</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2541</v>
+        <v>1.237</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1261</v>
+        <v>4.1435</v>
       </c>
       <c r="F10" t="n">
         <v>2.2171</v>
       </c>
       <c r="G10" t="n">
-        <v>1.909</v>
+        <v>1.8994</v>
       </c>
       <c r="H10" t="n">
         <v>2.4208</v>
@@ -888,7 +888,7 @@
         <v>1.3072</v>
       </c>
       <c r="J10" t="n">
-        <v>1.909</v>
+        <v>1.8994</v>
       </c>
       <c r="K10" t="n">
         <v>104</v>
@@ -897,7 +897,7 @@
         <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2162</v>
+        <v>3.2066</v>
       </c>
       <c r="N10" t="n">
         <v>258</v>
@@ -910,40 +910,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3809</v>
+        <v>3.184</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3747</v>
+        <v>1.2947</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9149</v>
+        <v>0.8084</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3809</v>
+        <v>3.184</v>
       </c>
       <c r="F11" t="n">
-        <v>3.381</v>
+        <v>2.3436</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001</v>
+        <v>0.7973</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2608</v>
+        <v>2.4044</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3808</v>
+        <v>2.4664</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0001</v>
+        <v>0.7973</v>
       </c>
       <c r="K11" t="n">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3807</v>
+        <v>3.2637</v>
       </c>
       <c r="N11" t="n">
         <v>212</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.051</v>
+        <v>3.0018</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2406</v>
+        <v>1.2206</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7647</v>
+        <v>0.727</v>
       </c>
       <c r="E12" t="n">
-        <v>3.051</v>
+        <v>3.0018</v>
       </c>
       <c r="F12" t="n">
-        <v>2.41</v>
+        <v>2.4102</v>
       </c>
       <c r="G12" t="n">
-        <v>0.641</v>
+        <v>0.6407</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0573</v>
+        <v>3.058</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6509</v>
+        <v>1.6513</v>
       </c>
       <c r="J12" t="n">
-        <v>0.641</v>
+        <v>0.6407</v>
       </c>
       <c r="K12" t="n">
         <v>106</v>
@@ -989,7 +989,7 @@
         <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2919</v>
+        <v>2.292</v>
       </c>
       <c r="N12" t="n">
         <v>266</v>
@@ -998,44 +998,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7386</v>
+        <v>2.8781</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1135</v>
+        <v>1.1703</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6718</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7386</v>
+        <v>2.8781</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4234</v>
+        <v>0.3803</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6848</v>
+        <v>2.4021</v>
       </c>
       <c r="H13" t="n">
-        <v>6.401</v>
+        <v>0.3803</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4565</v>
+        <v>0.3901</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6848</v>
+        <v>2.4021</v>
       </c>
       <c r="K13" t="n">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7717</v>
+        <v>2.7922</v>
       </c>
       <c r="N13" t="n">
         <v>212</v>
@@ -1044,228 +1044,228 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7171</v>
+        <v>2.5447</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1048</v>
+        <v>1.0347</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6127</v>
+        <v>0.5228</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7171</v>
+        <v>2.5447</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0371</v>
+        <v>3.1988</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.32</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1262</v>
+        <v>5.6599</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7681</v>
+        <v>3.0563</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.32</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4481</v>
+        <v>2.5014</v>
       </c>
       <c r="N14" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6649</v>
+        <v>2.5242</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0836</v>
+        <v>1.0264</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5889</v>
+        <v>0.5137</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6649</v>
+        <v>2.5242</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1988</v>
+        <v>2.5317</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5339</v>
+        <v>-0.3195</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6599</v>
+        <v>2.8162</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0563</v>
+        <v>2.8162</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5339</v>
+        <v>-0.3195</v>
       </c>
       <c r="K15" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="L15" t="n">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5224</v>
+        <v>2.4967</v>
       </c>
       <c r="N15" t="n">
-        <v>258</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3857</v>
+        <v>2.2041</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9701</v>
+        <v>0.8962</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4618</v>
+        <v>0.3707</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3857</v>
+        <v>2.2041</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3857</v>
+        <v>2.5922</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.3608</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4967</v>
+        <v>2.9486</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4967</v>
+        <v>3.0246</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.3608</v>
       </c>
       <c r="K16" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4967</v>
+        <v>2.6638</v>
       </c>
       <c r="N16" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3583</v>
+        <v>2.1601</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9589</v>
+        <v>0.8783</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4493</v>
+        <v>0.351</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3583</v>
+        <v>2.1601</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4949</v>
+        <v>0.9151</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1366</v>
+        <v>1.0593</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3373</v>
+        <v>0.9151</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8021</v>
+        <v>0.9151</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1366</v>
+        <v>1.0593</v>
       </c>
       <c r="K17" t="n">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6655</v>
+        <v>1.9744</v>
       </c>
       <c r="N17" t="n">
-        <v>179</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2031</v>
+        <v>1.5117</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8958</v>
+        <v>0.6147</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3787</v>
+        <v>0.0614</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2031</v>
+        <v>1.5117</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6963</v>
+        <v>2.123</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4932</v>
+        <v>-0.5279</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0019</v>
+        <v>2.123</v>
       </c>
       <c r="I18" t="n">
-        <v>2.161</v>
+        <v>2.1777</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4932</v>
+        <v>-0.5279</v>
       </c>
       <c r="K18" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6678</v>
+        <v>1.6498</v>
       </c>
       <c r="N18" t="n">
         <v>179</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.057</v>
+        <v>1.4808</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8364</v>
+        <v>0.6021</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3122</v>
+        <v>0.0476</v>
       </c>
       <c r="E19" t="n">
-        <v>2.057</v>
+        <v>1.4808</v>
       </c>
       <c r="F19" t="n">
-        <v>2.057</v>
+        <v>0.8806</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.6653</v>
       </c>
       <c r="H19" t="n">
-        <v>2.057</v>
+        <v>0.8806</v>
       </c>
       <c r="I19" t="n">
-        <v>2.057</v>
+        <v>0.9033</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.6653</v>
       </c>
       <c r="K19" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>2.057</v>
+        <v>1.5686</v>
       </c>
       <c r="N19" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20">
@@ -1324,40 +1324,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2031</v>
+        <v>1.2922</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4892</v>
+        <v>0.5254</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0765</v>
+        <v>-0.0366</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2031</v>
+        <v>1.2922</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2031</v>
+        <v>1.7434</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.5417</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2031</v>
+        <v>1.7434</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2031</v>
+        <v>1.7434</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.5417</v>
       </c>
       <c r="K20" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2031</v>
+        <v>1.2017</v>
       </c>
       <c r="N20" t="n">
         <v>145</v>
@@ -1370,40 +1370,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1823</v>
+        <v>1.1662</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4807</v>
+        <v>0.4742</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0929</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1823</v>
+        <v>1.1662</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1823</v>
+        <v>0.9298</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1823</v>
+        <v>0.9298</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1823</v>
+        <v>0.9298</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="K21" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1823</v>
+        <v>1.0588</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1416,40 +1416,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8521</v>
+        <v>0.7741</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3465</v>
+        <v>0.3148</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2363</v>
+        <v>-0.268</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8521</v>
+        <v>0.7741</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8521</v>
+        <v>0.979</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.1276</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8521</v>
+        <v>0.979</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8521</v>
+        <v>0.979</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.1276</v>
       </c>
       <c r="K22" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8521</v>
+        <v>0.8513999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>145</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6835</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2888</v>
+        <v>0.2779</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3009</v>
+        <v>-0.3085</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6835</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6957</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6957</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6957</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6957</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6331</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2736</v>
+        <v>0.2574</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3179</v>
+        <v>-0.331</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6331</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4637</v>
+        <v>1.2502</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1366</v>
+        <v>-0.6601</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4637</v>
+        <v>1.2502</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2504</v>
+        <v>1.2502</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1366</v>
+        <v>-0.6601</v>
       </c>
       <c r="K24" t="n">
         <v>106</v>
       </c>
       <c r="L24" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8862000000000001</v>
+        <v>0.5901</v>
       </c>
       <c r="N24" t="n">
-        <v>266</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5679</v>
+        <v>0.5978</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2309</v>
+        <v>0.2431</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3657</v>
+        <v>-0.3468</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5679</v>
+        <v>0.5978</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5679</v>
+        <v>-0.463</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5679</v>
+        <v>-0.463</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5679</v>
+        <v>-0.25</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="K25" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5679</v>
+        <v>0.8864000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>145</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26">
@@ -1600,40 +1600,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5185</v>
+        <v>0.4728</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2108</v>
+        <v>0.1922</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3882</v>
+        <v>-0.4026</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5185</v>
+        <v>0.4728</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5185</v>
+        <v>1.3058</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.7873</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5185</v>
+        <v>1.3058</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5185</v>
+        <v>1.3058</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.7873</v>
       </c>
       <c r="K26" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5185</v>
+        <v>0.5185000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>115</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1752</v>
+        <v>0.4219</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0712</v>
+        <v>0.1715</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5444</v>
+        <v>-0.4254</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1752</v>
+        <v>0.4219</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1752</v>
+        <v>0.1118</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1752</v>
+        <v>0.1118</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1752</v>
+        <v>0.1118</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1752</v>
+        <v>0.1118</v>
       </c>
       <c r="N27" t="n">
         <v>101</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1118</v>
+        <v>0.2453</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0455</v>
+        <v>0.0997</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5733</v>
+        <v>-0.5043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1118</v>
+        <v>0.2453</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1118</v>
+        <v>0.1023</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1118</v>
+        <v>0.1023</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1118</v>
+        <v>0.1023</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1118</v>
+        <v>0.1023</v>
       </c>
       <c r="N28" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1018</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0414</v>
+        <v>-0.0273</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5779</v>
+        <v>-0.6438</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1018</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1018</v>
+        <v>-0.1713</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1018</v>
+        <v>-0.1713</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1018</v>
+        <v>-0.1713</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1018</v>
+        <v>-0.1713</v>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0525</v>
+        <v>-0.1495</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0213</v>
+        <v>-0.0608</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6481</v>
+        <v>-0.6806</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0525</v>
+        <v>-0.1495</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0525</v>
+        <v>0.1752</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0525</v>
+        <v>0.1752</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0525</v>
+        <v>0.1752</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0525</v>
+        <v>0.1752</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
@@ -1830,37 +1830,37 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1169</v>
+        <v>-0.2523</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0475</v>
+        <v>-0.1026</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6774</v>
+        <v>-0.7265</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1169</v>
+        <v>-0.2523</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1169</v>
+        <v>0.4891</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.606</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1169</v>
+        <v>0.4891</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1169</v>
+        <v>0.4891</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.606</v>
       </c>
       <c r="K31" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M31" t="n">
         <v>-0.1169</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1713</v>
+        <v>-0.2683</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0697</v>
+        <v>-0.1091</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7022</v>
+        <v>-0.7337</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1713</v>
+        <v>-0.2683</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1713</v>
+        <v>-0.0525</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1713</v>
+        <v>-0.0525</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1713</v>
+        <v>-0.0525</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1713</v>
+        <v>-0.0525</v>
       </c>
       <c r="N32" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2776</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.095</v>
+        <v>-0.1129</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7306</v>
+        <v>-0.7378</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2776</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2332</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2332</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2332</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2337</v>
+        <v>-0.2332</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6948</v>
+        <v>-0.6881</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2825</v>
+        <v>-0.2798</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9405</v>
+        <v>-0.9212</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6948</v>
+        <v>-0.6881</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6948</v>
+        <v>0.3174</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.9324</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6948</v>
+        <v>0.3174</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6948</v>
+        <v>0.3256</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.9324</v>
       </c>
       <c r="K34" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6948</v>
+        <v>-0.6068</v>
       </c>
       <c r="N34" t="n">
-        <v>101</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9881</v>
+        <v>-0.9922</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4018</v>
+        <v>-0.4034</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.074</v>
+        <v>-1.057</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9881</v>
+        <v>-0.9922</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9881</v>
+        <v>-0.6948</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9881</v>
+        <v>-0.6948</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9881</v>
+        <v>-0.6948</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9881</v>
+        <v>-0.6948</v>
       </c>
       <c r="N35" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>regali</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1002</v>
+        <v>-1.2349</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4474</v>
+        <v>-0.5021</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.125</v>
+        <v>-1.1654</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1002</v>
+        <v>-1.2349</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1002</v>
+        <v>-0.9879</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1002</v>
+        <v>-0.9879</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1002</v>
+        <v>-0.9879</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1002</v>
+        <v>-0.9879</v>
       </c>
       <c r="N36" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>regali</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.38</v>
+        <v>-1.2733</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5611</v>
+        <v>-0.5177</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2524</v>
+        <v>-1.1826</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.38</v>
+        <v>-1.2733</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4384</v>
+        <v>-1.1002</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0584</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4384</v>
+        <v>-1.1002</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-1.1002</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0584</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7182999999999999</v>
+        <v>-1.1002</v>
       </c>
       <c r="N37" t="n">
-        <v>212</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38">
@@ -2152,40 +2152,40 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0987</v>
+        <v>-2.1874</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8534</v>
+        <v>-0.8894</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5796</v>
+        <v>-1.5909</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0987</v>
+        <v>-2.1874</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.0987</v>
+        <v>-1.5564</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.0987</v>
+        <v>-1.5564</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.0987</v>
+        <v>-1.5564</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.0987</v>
+        <v>-2.0992</v>
       </c>
       <c r="N38" t="n">
         <v>145</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.2571</v>
+        <v>-3.1756</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.3244</v>
+        <v>-1.2912</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.1069</v>
+        <v>-2.0323</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.2571</v>
+        <v>-3.1756</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.2571</v>
+        <v>-2.423</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.463</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.2571</v>
+        <v>-2.423</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.2571</v>
+        <v>-2.4854</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.463</v>
       </c>
       <c r="K39" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.2571</v>
+        <v>-2.9484</v>
       </c>
       <c r="N39" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.1624</v>
+        <v>-3.7372</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.6925</v>
+        <v>-1.5196</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.519</v>
+        <v>-2.2831</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.1624</v>
+        <v>-3.7372</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.8213</v>
+        <v>-2.3624</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3411</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.8213</v>
+        <v>-2.3624</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5235</v>
+        <v>-2.3624</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.3411</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="L40" t="n">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.8646</v>
+        <v>-3.2571</v>
       </c>
       <c r="N40" t="n">
-        <v>266</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.8162</v>
+        <v>-4.4376</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.9583</v>
+        <v>-1.8044</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.8166</v>
+        <v>-2.596</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.8162</v>
+        <v>-4.4376</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.3451</v>
+        <v>-2.8578</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4711</v>
+        <v>-1.3419</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.3451</v>
+        <v>-2.8578</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3463</v>
+        <v>-1.5432</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4711</v>
+        <v>-1.3419</v>
       </c>
       <c r="K41" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="L41" t="n">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8174</v>
+        <v>-2.8851</v>
       </c>
       <c r="N41" t="n">
-        <v>179</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2598,7 +2598,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2629,16 +2629,16 @@
         <v>1.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4153</v>
+        <v>0.4157</v>
       </c>
       <c r="J7" t="n">
-        <v>9.1366</v>
+        <v>9.1454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2669,10 +2669,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4153</v>
+        <v>0.4157</v>
       </c>
       <c r="J8" t="n">
-        <v>9.1366</v>
+        <v>9.1454</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1649</v>
+        <v>0.1651</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6278</v>
+        <v>3.6322</v>
       </c>
     </row>
     <row r="10">
@@ -2746,13 +2746,13 @@
         <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2435</v>
+        <v>-0.2533</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.357</v>
+        <v>-5.5726</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.394</v>
+        <v>-0.3939</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.667999999999999</v>
+        <v>-8.665800000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3029,10 +3029,10 @@
         <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5052</v>
+        <v>1.5058</v>
       </c>
       <c r="J17" t="n">
-        <v>28.5988</v>
+        <v>28.6102</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6632</v>
+        <v>0.6634</v>
       </c>
       <c r="J18" t="n">
-        <v>12.6008</v>
+        <v>12.6046</v>
       </c>
     </row>
     <row r="19">
@@ -3106,13 +3106,13 @@
         <v>19</v>
       </c>
       <c r="H19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5804</v>
+        <v>0.5592</v>
       </c>
       <c r="J19" t="n">
-        <v>11.0276</v>
+        <v>10.6248</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3503</v>
+        <v>0.3506</v>
       </c>
       <c r="J20" t="n">
-        <v>6.6557</v>
+        <v>6.6614</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>0.056</v>
+        <v>0.0564</v>
       </c>
       <c r="J21" t="n">
-        <v>1.064</v>
+        <v>1.0716</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2029</v>
+        <v>0.2021</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8551</v>
+        <v>3.8399</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.84</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1932</v>
+        <v>-0.1935</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6708</v>
+        <v>-3.6765</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2982</v>
+        <v>-0.2984</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6658</v>
+        <v>-5.6696</v>
       </c>
     </row>
     <row r="25">
@@ -3346,13 +3346,13 @@
         <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3349</v>
+        <v>-0.326</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.3631</v>
+        <v>-6.194</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4072</v>
+        <v>-0.4074</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.7368</v>
+        <v>-7.7406</v>
       </c>
     </row>
     <row r="27">
@@ -5429,10 +5429,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.304</v>
+        <v>0.3035</v>
       </c>
       <c r="J77" t="n">
-        <v>9.119999999999999</v>
+        <v>9.105</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0823</v>
+        <v>0.0819</v>
       </c>
       <c r="J78" t="n">
-        <v>2.469</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1071</v>
+        <v>-0.1072</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.213</v>
+        <v>-3.216</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1419</v>
+        <v>-0.1421</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.257</v>
+        <v>-4.263</v>
       </c>
     </row>
     <row r="81">
@@ -5586,13 +5586,13 @@
         <v>30</v>
       </c>
       <c r="H81" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3142</v>
+        <v>-0.305</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.426</v>
+        <v>-9.15</v>
       </c>
     </row>
     <row r="82">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6229,10 +6229,10 @@
         <v>1.93</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6556</v>
+        <v>1.5083</v>
       </c>
       <c r="J97" t="n">
-        <v>33.112</v>
+        <v>30.166</v>
       </c>
     </row>
     <row r="98">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7486</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>14.972</v>
+        <v>13.356</v>
       </c>
     </row>
     <row r="99">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4989</v>
+        <v>0.4832</v>
       </c>
       <c r="J99" t="n">
-        <v>9.978</v>
+        <v>9.664</v>
       </c>
     </row>
     <row r="100">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6429,10 +6429,10 @@
         <v>1.27</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>11.3325</v>
+        <v>10.0935</v>
       </c>
     </row>
     <row r="103">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6629,10 +6629,10 @@
         <v>2.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9372</v>
+        <v>2.0074</v>
       </c>
       <c r="J107" t="n">
-        <v>29.058</v>
+        <v>30.111</v>
       </c>
     </row>
     <row r="108">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6669,10 +6669,10 @@
         <v>2.28</v>
       </c>
       <c r="I108" t="n">
-        <v>1.9372</v>
+        <v>1.8123</v>
       </c>
       <c r="J108" t="n">
-        <v>29.058</v>
+        <v>27.1845</v>
       </c>
     </row>
     <row r="109">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6709,10 +6709,10 @@
         <v>1.43</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9452</v>
+        <v>0.8142</v>
       </c>
       <c r="J109" t="n">
-        <v>14.178</v>
+        <v>12.213</v>
       </c>
     </row>
     <row r="110">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5091</v>
+        <v>0.4907</v>
       </c>
       <c r="J110" t="n">
-        <v>7.6365</v>
+        <v>7.3605</v>
       </c>
     </row>
     <row r="111">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6829,10 +6829,10 @@
         <v>1.72</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4163</v>
+        <v>1.2677</v>
       </c>
       <c r="J112" t="n">
-        <v>33.9912</v>
+        <v>30.4248</v>
       </c>
     </row>
     <row r="113">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8479</v>
+        <v>0.7405</v>
       </c>
       <c r="J113" t="n">
-        <v>20.3496</v>
+        <v>17.772</v>
       </c>
     </row>
     <row r="114">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6906,13 +6906,13 @@
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4405</v>
+        <v>0.456</v>
       </c>
       <c r="J114" t="n">
-        <v>10.572</v>
+        <v>10.944</v>
       </c>
     </row>
     <row r="115">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6946,13 +6946,13 @@
         <v>24</v>
       </c>
       <c r="H115" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2261</v>
+        <v>-0.1949</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.4264</v>
+        <v>-4.6776</v>
       </c>
     </row>
     <row r="116">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6989,10 +6989,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.1794</v>
+        <v>-1.18</v>
       </c>
       <c r="J116" t="n">
-        <v>-28.3056</v>
+        <v>-28.32</v>
       </c>
     </row>
     <row r="117">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7029,10 +7029,10 @@
         <v>1.53</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9482</v>
+        <v>0.8165</v>
       </c>
       <c r="J117" t="n">
-        <v>22.7568</v>
+        <v>19.596</v>
       </c>
     </row>
     <row r="118">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7229,10 +7229,10 @@
         <v>2.89</v>
       </c>
       <c r="I122" t="n">
-        <v>1.9372</v>
+        <v>2.4491</v>
       </c>
       <c r="J122" t="n">
-        <v>29.058</v>
+        <v>36.7365</v>
       </c>
     </row>
     <row r="123">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -7269,10 +7269,10 @@
         <v>1.85</v>
       </c>
       <c r="I123" t="n">
-        <v>1.4706</v>
+        <v>1.3233</v>
       </c>
       <c r="J123" t="n">
-        <v>22.059</v>
+        <v>19.8495</v>
       </c>
     </row>
     <row r="124">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>1.1401</v>
+        <v>0.9928</v>
       </c>
       <c r="J124" t="n">
-        <v>17.1015</v>
+        <v>14.892</v>
       </c>
     </row>
     <row r="125">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2252</v>
+        <v>1.2246</v>
       </c>
       <c r="J177" t="n">
-        <v>49.008</v>
+        <v>48.984</v>
       </c>
     </row>
     <row r="178">
@@ -9466,13 +9466,13 @@
         <v>40</v>
       </c>
       <c r="H178" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4394</v>
+        <v>0.4617</v>
       </c>
       <c r="J178" t="n">
-        <v>17.576</v>
+        <v>18.468</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.11</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3433</v>
+        <v>0.343</v>
       </c>
       <c r="J179" t="n">
-        <v>13.732</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0848</v>
+        <v>-0.0852</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.392</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2885</v>
+        <v>-0.2888</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.54</v>
+        <v>-11.552</v>
       </c>
     </row>
     <row r="182">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="J232" t="n">
-        <v>17.3812</v>
+        <v>17.366</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1774</v>
+        <v>0.177</v>
       </c>
       <c r="J233" t="n">
-        <v>3.3706</v>
+        <v>3.363</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0229</v>
+        <v>-0.023</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.4351</v>
+        <v>-0.437</v>
       </c>
     </row>
     <row r="235">
@@ -11746,13 +11746,13 @@
         <v>19</v>
       </c>
       <c r="H235" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.416</v>
+        <v>-0.4074</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.904</v>
+        <v>-7.7406</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.416</v>
+        <v>-0.4162</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.904</v>
+        <v>-7.9078</v>
       </c>
     </row>
     <row r="237">
@@ -12229,10 +12229,10 @@
         <v>1.65</v>
       </c>
       <c r="I247" t="n">
-        <v>1.326</v>
+        <v>1.3266</v>
       </c>
       <c r="J247" t="n">
-        <v>30.498</v>
+        <v>30.5118</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.25</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6636</v>
+        <v>0.664</v>
       </c>
       <c r="J248" t="n">
-        <v>15.2628</v>
+        <v>15.272</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.25</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6636</v>
+        <v>0.664</v>
       </c>
       <c r="J249" t="n">
-        <v>15.2628</v>
+        <v>15.272</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3674</v>
+        <v>-0.367</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.450200000000001</v>
+        <v>-8.441000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12386,13 +12386,13 @@
         <v>23</v>
       </c>
       <c r="H251" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0398</v>
+        <v>-1.0595</v>
       </c>
       <c r="J251" t="n">
-        <v>-23.9154</v>
+        <v>-24.3685</v>
       </c>
     </row>
     <row r="252">
@@ -13229,10 +13229,10 @@
         <v>1.51</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1302</v>
+        <v>1.1297</v>
       </c>
       <c r="J272" t="n">
-        <v>24.8644</v>
+        <v>24.8534</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6385</v>
+        <v>0.6381</v>
       </c>
       <c r="J273" t="n">
-        <v>14.047</v>
+        <v>14.0382</v>
       </c>
     </row>
     <row r="274">
@@ -13306,13 +13306,13 @@
         <v>22</v>
       </c>
       <c r="H274" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2922</v>
+        <v>0.3181</v>
       </c>
       <c r="J274" t="n">
-        <v>6.4284</v>
+        <v>6.9982</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0243</v>
+        <v>-0.0247</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.5346</v>
+        <v>-0.5434</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3708</v>
+        <v>-0.3711</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.1576</v>
+        <v>-8.164199999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13426,13 +13426,13 @@
         <v>22</v>
       </c>
       <c r="H277" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7587</v>
+        <v>0.7442</v>
       </c>
       <c r="J277" t="n">
-        <v>16.6914</v>
+        <v>16.3724</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4562</v>
+        <v>0.4567</v>
       </c>
       <c r="J278" t="n">
-        <v>10.0364</v>
+        <v>10.0474</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.16</v>
       </c>
       <c r="I279" t="n">
-        <v>0.369</v>
+        <v>0.3695</v>
       </c>
       <c r="J279" t="n">
-        <v>8.118</v>
+        <v>8.129</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4354</v>
+        <v>-0.4352</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.578799999999999</v>
+        <v>-9.574400000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5044</v>
+        <v>-0.5042</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.0968</v>
+        <v>-11.0924</v>
       </c>
     </row>
     <row r="282">

--- a/database/event/7905/event_7905_evp_summary.xlsx
+++ b/database/event/7905/event_7905_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8895</v>
+        <v>8.1624</v>
       </c>
       <c r="C2" t="n">
-        <v>3.208</v>
+        <v>3.3189</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9102</v>
+        <v>3.1126</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8895</v>
+        <v>8.1624</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4321</v>
+        <v>2.503</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2713</v>
+        <v>5.4733</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1302</v>
+        <v>2.9546</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6903</v>
+        <v>1.6589</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2713</v>
+        <v>5.4733</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9616</v>
+        <v>7.1322</v>
       </c>
       <c r="N2" t="n">
         <v>258</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4904</v>
+        <v>7.3016</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0457</v>
+        <v>2.9689</v>
       </c>
       <c r="D3" t="n">
-        <v>2.732</v>
+        <v>2.7204</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4904</v>
+        <v>7.3016</v>
       </c>
       <c r="F3" t="n">
-        <v>3.72</v>
+        <v>3.622</v>
       </c>
       <c r="G3" t="n">
-        <v>3.423</v>
+        <v>3.3323</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3794</v>
+        <v>7.1559</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9848</v>
+        <v>4.0178</v>
       </c>
       <c r="J3" t="n">
-        <v>3.423</v>
+        <v>3.3323</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>7.4078</v>
+        <v>7.3501</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.588</v>
+        <v>6.6461</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6788</v>
+        <v>2.7024</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3289</v>
+        <v>2.4218</v>
       </c>
       <c r="E4" t="n">
-        <v>6.588</v>
+        <v>6.6461</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2895</v>
+        <v>2.4055</v>
       </c>
       <c r="G4" t="n">
-        <v>4.265</v>
+        <v>4.2071</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6599</v>
+        <v>2.5887</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4363</v>
+        <v>1.4535</v>
       </c>
       <c r="J4" t="n">
-        <v>4.265</v>
+        <v>4.2071</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7013</v>
+        <v>5.6606</v>
       </c>
       <c r="N4" t="n">
         <v>258</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3683</v>
+        <v>6.3123</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5894</v>
+        <v>2.5667</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2308</v>
+        <v>2.2698</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3683</v>
+        <v>6.3123</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0638</v>
+        <v>3.0061</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8642</v>
+        <v>2.8659</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9807</v>
+        <v>3.939</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0833</v>
+        <v>4.0443</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8642</v>
+        <v>2.8659</v>
       </c>
       <c r="K5" t="n">
         <v>101</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>6.9475</v>
+        <v>6.9102</v>
       </c>
       <c r="N5" t="n">
         <v>179</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9239</v>
+        <v>5.8888</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4087</v>
+        <v>2.3945</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0323</v>
+        <v>2.0768</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9239</v>
+        <v>5.8888</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.383</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1619</v>
+        <v>3.1438</v>
       </c>
       <c r="H6" t="n">
-        <v>2.528</v>
+        <v>2.511</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5931</v>
+        <v>2.5781</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1619</v>
+        <v>3.1438</v>
       </c>
       <c r="K6" t="n">
         <v>101</v>
@@ -713,7 +713,7 @@
         <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>5.755000000000001</v>
+        <v>5.7219</v>
       </c>
       <c r="N6" t="n">
         <v>179</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5089</v>
+        <v>5.4911</v>
       </c>
       <c r="C7" t="n">
-        <v>2.24</v>
+        <v>2.2327</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8469</v>
+        <v>1.8957</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5089</v>
+        <v>5.4911</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4929</v>
+        <v>2.5209</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7555</v>
+        <v>2.7097</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7313</v>
+        <v>2.8271</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8017</v>
+        <v>2.9026</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7555</v>
+        <v>2.7097</v>
       </c>
       <c r="K7" t="n">
         <v>124</v>
@@ -759,7 +759,7 @@
         <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5572</v>
+        <v>5.6123</v>
       </c>
       <c r="N7" t="n">
         <v>212</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4539</v>
+        <v>4.3908</v>
       </c>
       <c r="C8" t="n">
-        <v>1.811</v>
+        <v>1.7853</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3756</v>
+        <v>1.3944</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4539</v>
+        <v>4.3908</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8989</v>
+        <v>1.9226</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5958</v>
+        <v>2.509</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8989</v>
+        <v>1.9226</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0254</v>
+        <v>1.0795</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5958</v>
+        <v>2.509</v>
       </c>
       <c r="K8" t="n">
         <v>104</v>
@@ -805,7 +805,7 @@
         <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6212</v>
+        <v>3.5885</v>
       </c>
       <c r="N8" t="n">
         <v>258</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3197</v>
+        <v>4.2868</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7564</v>
+        <v>1.7431</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3157</v>
+        <v>1.3471</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3197</v>
+        <v>4.2868</v>
       </c>
       <c r="F9" t="n">
-        <v>3.916</v>
+        <v>2.2669</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3125</v>
+        <v>1.9929</v>
       </c>
       <c r="H9" t="n">
-        <v>8.026</v>
+        <v>2.2669</v>
       </c>
       <c r="I9" t="n">
-        <v>4.334</v>
+        <v>1.2728</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3125</v>
+        <v>1.9929</v>
       </c>
       <c r="K9" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6465</v>
+        <v>3.2657</v>
       </c>
       <c r="N9" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1435</v>
+        <v>4.2239</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6848</v>
+        <v>1.7175</v>
       </c>
       <c r="D10" t="n">
-        <v>1.237</v>
+        <v>1.3184</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1435</v>
+        <v>4.2239</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2171</v>
+        <v>3.7955</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8994</v>
+        <v>0.3372</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4208</v>
+        <v>7.8072</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3072</v>
+        <v>4.3835</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8994</v>
+        <v>0.3372</v>
       </c>
       <c r="K10" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2066</v>
+        <v>4.7207</v>
       </c>
       <c r="N10" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.184</v>
+        <v>3.1743</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2947</v>
+        <v>1.2907</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8084</v>
+        <v>0.8403</v>
       </c>
       <c r="E11" t="n">
-        <v>3.184</v>
+        <v>3.1743</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3436</v>
+        <v>2.3351</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7973</v>
+        <v>0.7961</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4044</v>
+        <v>2.4012</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4664</v>
+        <v>2.4654</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7973</v>
+        <v>0.7961</v>
       </c>
       <c r="K11" t="n">
         <v>124</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2637</v>
+        <v>3.2615</v>
       </c>
       <c r="N11" t="n">
         <v>212</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0018</v>
+        <v>3.0586</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2206</v>
+        <v>1.2437</v>
       </c>
       <c r="D12" t="n">
-        <v>0.727</v>
+        <v>0.7876</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0018</v>
+        <v>3.0586</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4102</v>
+        <v>0.469</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6407</v>
+        <v>2.4939</v>
       </c>
       <c r="H12" t="n">
-        <v>3.058</v>
+        <v>0.469</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6513</v>
+        <v>0.4815</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6407</v>
+        <v>2.4939</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L12" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.292</v>
+        <v>2.9754</v>
       </c>
       <c r="N12" t="n">
-        <v>266</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8781</v>
+        <v>3.057</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1703</v>
+        <v>1.243</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6718</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8781</v>
+        <v>3.057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3803</v>
+        <v>2.4762</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4021</v>
+        <v>0.6299</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3803</v>
+        <v>2.8541</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3901</v>
+        <v>1.6025</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4021</v>
+        <v>0.6299</v>
       </c>
       <c r="K13" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7922</v>
+        <v>2.2324</v>
       </c>
       <c r="N13" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5447</v>
+        <v>2.5298</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0347</v>
+        <v>1.0286</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5228</v>
+        <v>0.5467</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5447</v>
+        <v>2.5298</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1988</v>
+        <v>3.1394</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.5104</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6599</v>
+        <v>5.344</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0563</v>
+        <v>3.0005</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.5104</v>
       </c>
       <c r="K14" t="n">
         <v>104</v>
@@ -1081,7 +1081,7 @@
         <v>154</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5014</v>
+        <v>2.4901</v>
       </c>
       <c r="N14" t="n">
         <v>258</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5242</v>
+        <v>2.4615</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0264</v>
+        <v>1.0009</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5137</v>
+        <v>0.5155</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5242</v>
+        <v>2.4615</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5317</v>
+        <v>2.5412</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3195</v>
+        <v>-0.3917</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8162</v>
+        <v>2.8736</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8162</v>
+        <v>2.8736</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3195</v>
+        <v>-0.3917</v>
       </c>
       <c r="K15" t="n">
         <v>80</v>
@@ -1127,7 +1127,7 @@
         <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4967</v>
+        <v>2.4819</v>
       </c>
       <c r="N15" t="n">
         <v>115</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2041</v>
+        <v>2.2214</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8962</v>
+        <v>0.9032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3707</v>
+        <v>0.4062</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2041</v>
+        <v>2.2214</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5922</v>
+        <v>1.0233</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3608</v>
+        <v>1.0124</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9486</v>
+        <v>1.0233</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0246</v>
+        <v>1.0233</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3608</v>
+        <v>1.0124</v>
       </c>
       <c r="K16" t="n">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="L16" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6638</v>
+        <v>2.0357</v>
       </c>
       <c r="N16" t="n">
-        <v>212</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1601</v>
+        <v>2.1489</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8783</v>
+        <v>0.8738</v>
       </c>
       <c r="D17" t="n">
-        <v>0.351</v>
+        <v>0.3731</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1601</v>
+        <v>2.1489</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9151</v>
+        <v>2.5211</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0593</v>
+        <v>-0.3449</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9151</v>
+        <v>2.8275</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9151</v>
+        <v>2.903</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0593</v>
+        <v>-0.3449</v>
       </c>
       <c r="K17" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9744</v>
+        <v>2.5581</v>
       </c>
       <c r="N17" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5117</v>
+        <v>1.4308</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6147</v>
+        <v>0.5818</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0614</v>
+        <v>0.046</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5117</v>
+        <v>1.4308</v>
       </c>
       <c r="F18" t="n">
-        <v>2.123</v>
+        <v>2.0745</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5279</v>
+        <v>-0.5603</v>
       </c>
       <c r="H18" t="n">
-        <v>2.123</v>
+        <v>2.0745</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1777</v>
+        <v>2.1299</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5279</v>
+        <v>-0.5603</v>
       </c>
       <c r="K18" t="n">
         <v>101</v>
@@ -1265,7 +1265,7 @@
         <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6498</v>
+        <v>1.5696</v>
       </c>
       <c r="N18" t="n">
         <v>179</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4808</v>
+        <v>1.3773</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6021</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0476</v>
+        <v>0.0216</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4808</v>
+        <v>1.3773</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8806</v>
+        <v>0.7658</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6653</v>
+        <v>0.6766</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8806</v>
+        <v>0.7658</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9033</v>
+        <v>0.7863</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6653</v>
+        <v>0.6766</v>
       </c>
       <c r="K19" t="n">
         <v>101</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5686</v>
+        <v>1.4629</v>
       </c>
       <c r="N19" t="n">
         <v>179</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2922</v>
+        <v>1.322</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5254</v>
+        <v>0.5375</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0366</v>
+        <v>-0.0036</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2922</v>
+        <v>1.322</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7434</v>
+        <v>1.7411</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5417</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7434</v>
+        <v>1.7411</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7434</v>
+        <v>1.7411</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5417</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>106</v>
@@ -1357,7 +1357,7 @@
         <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2017</v>
+        <v>1.2315</v>
       </c>
       <c r="N20" t="n">
         <v>145</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1662</v>
+        <v>1.0613</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4742</v>
+        <v>0.4315</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0929</v>
+        <v>-0.1223</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1662</v>
+        <v>1.0613</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9298</v>
+        <v>0.8869</v>
       </c>
       <c r="G21" t="n">
-        <v>0.129</v>
+        <v>0.067</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9298</v>
+        <v>0.8869</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9298</v>
+        <v>0.8869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.129</v>
+        <v>0.067</v>
       </c>
       <c r="K21" t="n">
         <v>106</v>
@@ -1403,7 +1403,7 @@
         <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0588</v>
+        <v>0.9539</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7741</v>
+        <v>0.7186</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3148</v>
+        <v>0.2922</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.268</v>
+        <v>-0.2784</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7741</v>
+        <v>0.7186</v>
       </c>
       <c r="F22" t="n">
-        <v>0.979</v>
+        <v>0.892</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1276</v>
+        <v>-0.0961</v>
       </c>
       <c r="H22" t="n">
-        <v>0.979</v>
+        <v>0.892</v>
       </c>
       <c r="I22" t="n">
-        <v>0.979</v>
+        <v>0.892</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1276</v>
+        <v>-0.0961</v>
       </c>
       <c r="K22" t="n">
         <v>106</v>
@@ -1449,7 +1449,7 @@
         <v>39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8513999999999999</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>145</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6835</v>
+        <v>0.6466</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2779</v>
+        <v>0.2629</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3085</v>
+        <v>-0.3112</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6835</v>
+        <v>0.6466</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6957</v>
+        <v>1.2344</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.6308</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6957</v>
+        <v>1.2344</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6957</v>
+        <v>1.2344</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.6308</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6957</v>
+        <v>0.6035999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6331</v>
+        <v>0.5363</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2574</v>
+        <v>0.2181</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.331</v>
+        <v>-0.3615</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6331</v>
+        <v>0.5363</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2502</v>
+        <v>0.5485</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6601</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2502</v>
+        <v>0.5485</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2502</v>
+        <v>0.5485</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6601</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5901</v>
+        <v>0.5485</v>
       </c>
       <c r="N24" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5978</v>
+        <v>0.5003</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2431</v>
+        <v>0.2034</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3468</v>
+        <v>-0.3779</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5978</v>
+        <v>0.5003</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.463</v>
+        <v>-0.4011</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1364</v>
+        <v>0.977</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.463</v>
+        <v>-0.4011</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.25</v>
+        <v>-0.2252</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1364</v>
+        <v>0.977</v>
       </c>
       <c r="K25" t="n">
         <v>106</v>
@@ -1587,7 +1587,7 @@
         <v>160</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8864000000000001</v>
+        <v>0.7518</v>
       </c>
       <c r="N25" t="n">
         <v>266</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4728</v>
+        <v>0.4586</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1922</v>
+        <v>0.1865</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4026</v>
+        <v>-0.3969</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4728</v>
+        <v>0.4586</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3058</v>
+        <v>1.2863</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7873</v>
+        <v>-0.782</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3058</v>
+        <v>1.2863</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3058</v>
+        <v>1.2863</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7873</v>
+        <v>-0.782</v>
       </c>
       <c r="K26" t="n">
         <v>80</v>
@@ -1633,7 +1633,7 @@
         <v>35</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5043</v>
       </c>
       <c r="N26" t="n">
         <v>115</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4219</v>
+        <v>0.4015</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1715</v>
+        <v>0.1633</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4254</v>
+        <v>-0.4229</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4219</v>
+        <v>0.4015</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1118</v>
+        <v>0.0914</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1118</v>
+        <v>0.0914</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1118</v>
+        <v>0.0914</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1118</v>
+        <v>0.0914</v>
       </c>
       <c r="N27" t="n">
         <v>101</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2453</v>
+        <v>0.147</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0997</v>
+        <v>0.0598</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5043</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2453</v>
+        <v>0.147</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1023</v>
+        <v>0.004</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1023</v>
+        <v>0.004</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1023</v>
+        <v>0.004</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1023</v>
+        <v>0.004</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1068</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0273</v>
+        <v>-0.0434</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6438</v>
+        <v>-0.6544</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1068</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1713</v>
+        <v>-0.211</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1713</v>
+        <v>-0.211</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1713</v>
+        <v>-0.211</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1713</v>
+        <v>-0.211</v>
       </c>
       <c r="N29" t="n">
         <v>101</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1495</v>
+        <v>-0.1942</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0608</v>
+        <v>-0.079</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6806</v>
+        <v>-0.6943</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1495</v>
+        <v>-0.1942</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1752</v>
+        <v>0.1305</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1752</v>
+        <v>0.1305</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1752</v>
+        <v>0.1305</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1752</v>
+        <v>0.1305</v>
       </c>
       <c r="N30" t="n">
         <v>101</v>
@@ -1826,124 +1826,124 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2523</v>
+        <v>-0.2689</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1026</v>
+        <v>-0.1093</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7265</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2523</v>
+        <v>-0.2689</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4891</v>
+        <v>-0.2245</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.606</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4891</v>
+        <v>-0.2245</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4891</v>
+        <v>-0.2245</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.606</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1169</v>
+        <v>-0.2245</v>
       </c>
       <c r="N31" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2683</v>
+        <v>-0.3107</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1091</v>
+        <v>-0.1263</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7337</v>
+        <v>-0.7473</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2683</v>
+        <v>-0.3107</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0525</v>
+        <v>0.4014</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.5767</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0525</v>
+        <v>0.4014</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0525</v>
+        <v>0.4014</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.5767</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0525</v>
+        <v>-0.1753</v>
       </c>
       <c r="N32" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2776</v>
+        <v>-0.3807</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1129</v>
+        <v>-0.1548</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7378</v>
+        <v>-0.7792</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2776</v>
+        <v>-0.3807</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2332</v>
+        <v>-0.1649</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2332</v>
+        <v>-0.1649</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2332</v>
+        <v>-0.1649</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2332</v>
+        <v>-0.1649</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6881</v>
+        <v>-0.7259</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2798</v>
+        <v>-0.2952</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9212</v>
+        <v>-0.9365</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6881</v>
+        <v>-0.7259</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3174</v>
+        <v>0.3125</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9324</v>
+        <v>-0.9653</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3174</v>
+        <v>0.3125</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3256</v>
+        <v>0.3209</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9324</v>
+        <v>-0.9653</v>
       </c>
       <c r="K34" t="n">
         <v>124</v>
@@ -2001,7 +2001,7 @@
         <v>88</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6444000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>212</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9922</v>
+        <v>-0.93</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4034</v>
+        <v>-0.3781</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.057</v>
+        <v>-1.0294</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9922</v>
+        <v>-0.93</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6948</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6948</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6948</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6948</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>101</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>regali</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2349</v>
+        <v>-1.2101</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5021</v>
+        <v>-0.492</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1654</v>
+        <v>-1.157</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2349</v>
+        <v>-1.2101</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9879</v>
+        <v>-1.037</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9879</v>
+        <v>-1.037</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9879</v>
+        <v>-1.037</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9879</v>
+        <v>-1.037</v>
       </c>
       <c r="N36" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>regali</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2733</v>
+        <v>-1.2577</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5177</v>
+        <v>-0.5114</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1826</v>
+        <v>-1.1787</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2733</v>
+        <v>-1.2577</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1002</v>
+        <v>-1.0107</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1002</v>
+        <v>-1.0107</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1002</v>
+        <v>-1.0107</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1002</v>
+        <v>-1.0107</v>
       </c>
       <c r="N37" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.1874</v>
+        <v>-2.0565</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8894</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5909</v>
+        <v>-1.5426</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.1874</v>
+        <v>-2.0565</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5564</v>
+        <v>-1.4578</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5105</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5564</v>
+        <v>-1.4578</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5564</v>
+        <v>-1.4578</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5105</v>
       </c>
       <c r="K38" t="n">
         <v>106</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.0992</v>
+        <v>-1.9683</v>
       </c>
       <c r="N38" t="n">
         <v>145</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.1756</v>
+        <v>-3.0951</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.2912</v>
+        <v>-1.2585</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.0323</v>
+        <v>-2.0158</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.1756</v>
+        <v>-3.0951</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.423</v>
+        <v>-2.3601</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.463</v>
+        <v>-0.4454</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.423</v>
+        <v>-2.3601</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.4854</v>
+        <v>-2.4232</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.463</v>
+        <v>-0.4454</v>
       </c>
       <c r="K39" t="n">
         <v>101</v>
@@ -2231,7 +2231,7 @@
         <v>78</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.9484</v>
+        <v>-2.8686</v>
       </c>
       <c r="N39" t="n">
         <v>179</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.7372</v>
+        <v>-3.6815</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.5196</v>
+        <v>-1.4969</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.2831</v>
+        <v>-2.2829</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.7372</v>
+        <v>-3.6815</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3624</v>
+        <v>-2.3199</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8815</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3624</v>
+        <v>-2.3199</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3624</v>
+        <v>-2.3199</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8815</v>
       </c>
       <c r="K40" t="n">
         <v>80</v>
@@ -2277,7 +2277,7 @@
         <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.2571</v>
+        <v>-3.2014</v>
       </c>
       <c r="N40" t="n">
         <v>115</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.4376</v>
+        <v>-4.2131</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.8044</v>
+        <v>-1.7131</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.596</v>
+        <v>-2.5251</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.4376</v>
+        <v>-4.2131</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.8578</v>
+        <v>-2.6782</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.3419</v>
+        <v>-1.297</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.8578</v>
+        <v>-2.6782</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5432</v>
+        <v>-1.5037</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.3419</v>
+        <v>-1.297</v>
       </c>
       <c r="K41" t="n">
         <v>106</v>
@@ -2323,7 +2323,7 @@
         <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8851</v>
+        <v>-2.8007</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8094</v>
+        <v>0.7412</v>
       </c>
       <c r="J2" t="n">
-        <v>17.8068</v>
+        <v>16.3064</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2799</v>
+        <v>0.2278</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1578</v>
+        <v>5.0116</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0525</v>
+        <v>-0.0404</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.155</v>
+        <v>-0.8888</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1096</v>
+        <v>-0.0917</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.4112</v>
+        <v>-2.0174</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1803</v>
+        <v>-0.1601</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.9666</v>
+        <v>-3.5222</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4157</v>
+        <v>0.4145</v>
       </c>
       <c r="J7" t="n">
-        <v>9.1454</v>
+        <v>9.119</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4157</v>
+        <v>0.4145</v>
       </c>
       <c r="J8" t="n">
-        <v>9.1454</v>
+        <v>9.119</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1651</v>
+        <v>0.1484</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6322</v>
+        <v>3.2648</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2533</v>
+        <v>-0.2335</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.5726</v>
+        <v>-5.137</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.665800000000001</v>
+        <v>-8.4282</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4111</v>
+        <v>0.3548</v>
       </c>
       <c r="J12" t="n">
-        <v>7.8109</v>
+        <v>6.7412</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1559</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9621</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1073</v>
+        <v>0.079</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0387</v>
+        <v>1.501</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1759</v>
+        <v>-0.1559</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.3421</v>
+        <v>-2.9621</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4066</v>
+        <v>-0.3966</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.7254</v>
+        <v>-7.5354</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5058</v>
+        <v>1.5388</v>
       </c>
       <c r="J17" t="n">
-        <v>28.6102</v>
+        <v>29.2372</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6634</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>12.6046</v>
+        <v>12.0764</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5592</v>
+        <v>0.5286</v>
       </c>
       <c r="J19" t="n">
-        <v>10.6248</v>
+        <v>10.0434</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3506</v>
+        <v>0.3182</v>
       </c>
       <c r="J20" t="n">
-        <v>6.6614</v>
+        <v>6.0458</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0564</v>
+        <v>0.04</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0716</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2021</v>
+        <v>0.1666</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8399</v>
+        <v>3.1654</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.84</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1935</v>
+        <v>-0.1771</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6765</v>
+        <v>-3.3649</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2984</v>
+        <v>-0.2816</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6696</v>
+        <v>-5.3504</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.326</v>
+        <v>-0.3101</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.194</v>
+        <v>-5.8919</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4074</v>
+        <v>-0.3965</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.7406</v>
+        <v>-7.5335</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.88</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7071</v>
+        <v>1.7416</v>
       </c>
       <c r="J27" t="n">
-        <v>32.4349</v>
+        <v>33.0904</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.47</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0561</v>
+        <v>1.0564</v>
       </c>
       <c r="J28" t="n">
-        <v>20.0659</v>
+        <v>20.0716</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7376</v>
+        <v>0.7155</v>
       </c>
       <c r="J29" t="n">
-        <v>14.0144</v>
+        <v>13.5945</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1544</v>
+        <v>-0.1289</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.9336</v>
+        <v>-2.4491</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2567</v>
+        <v>-0.2224</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.8773</v>
+        <v>-4.2256</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7341</v>
+        <v>0.6631</v>
       </c>
       <c r="J32" t="n">
-        <v>22.023</v>
+        <v>19.893</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.314</v>
+        <v>0.2588</v>
       </c>
       <c r="J33" t="n">
-        <v>9.42</v>
+        <v>7.764</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>2.913</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0703</v>
+        <v>-0.056</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.109</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.958</v>
+        <v>-2.448</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6541</v>
+        <v>0.6885</v>
       </c>
       <c r="J37" t="n">
-        <v>19.623</v>
+        <v>20.655</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4436</v>
+        <v>0.4453</v>
       </c>
       <c r="J38" t="n">
-        <v>13.308</v>
+        <v>13.359</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2899</v>
+        <v>0.2776</v>
       </c>
       <c r="J39" t="n">
-        <v>8.696999999999999</v>
+        <v>8.327999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.287</v>
+        <v>-0.2688</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4419</v>
+        <v>-0.4369</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.257</v>
+        <v>-13.107</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.17</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4058</v>
+        <v>0.3508</v>
       </c>
       <c r="J42" t="n">
-        <v>8.521800000000001</v>
+        <v>7.3668</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.116</v>
+        <v>0.0863</v>
       </c>
       <c r="J43" t="n">
-        <v>2.436</v>
+        <v>1.8123</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1932</v>
+        <v>-0.1735</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.0572</v>
+        <v>-3.6435</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2437</v>
+        <v>-0.224</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.1177</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3482</v>
+        <v>-0.3329</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.3122</v>
+        <v>-6.9909</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.87</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7027</v>
+        <v>1.7377</v>
       </c>
       <c r="J47" t="n">
-        <v>35.7567</v>
+        <v>36.4917</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.79</v>
       </c>
       <c r="I48" t="n">
-        <v>1.6011</v>
+        <v>1.6297</v>
       </c>
       <c r="J48" t="n">
-        <v>33.6231</v>
+        <v>34.2237</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0896</v>
+        <v>0.0688</v>
       </c>
       <c r="J49" t="n">
-        <v>1.8816</v>
+        <v>1.4448</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3676</v>
+        <v>-0.329</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.7196</v>
+        <v>-6.909</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5693</v>
+        <v>-0.5349</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9553</v>
+        <v>-11.2329</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>2.06</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6502</v>
+        <v>1.6902</v>
       </c>
       <c r="J52" t="n">
-        <v>34.6542</v>
+        <v>35.4942</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8881</v>
+        <v>0.8738</v>
       </c>
       <c r="J53" t="n">
-        <v>18.6501</v>
+        <v>18.3498</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3742</v>
+        <v>0.3417</v>
       </c>
       <c r="J54" t="n">
-        <v>7.8582</v>
+        <v>7.1757</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1842</v>
+        <v>-0.1539</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.8682</v>
+        <v>-3.2319</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7488</v>
+        <v>-0.7261</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.7248</v>
+        <v>-15.2481</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4566</v>
+        <v>0.4083</v>
       </c>
       <c r="J57" t="n">
-        <v>9.5886</v>
+        <v>8.574299999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1446</v>
+        <v>0.1106</v>
       </c>
       <c r="J58" t="n">
-        <v>3.0366</v>
+        <v>2.3226</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0165</v>
+        <v>-0.0119</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.3465</v>
+        <v>-0.2499</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3468</v>
+        <v>-0.3314</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.2828</v>
+        <v>-6.9594</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4715</v>
+        <v>-0.4681</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.9015</v>
+        <v>-9.8301</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8227</v>
+        <v>0.8068</v>
       </c>
       <c r="J62" t="n">
-        <v>18.0994</v>
+        <v>17.7496</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6756</v>
+        <v>0.6617</v>
       </c>
       <c r="J63" t="n">
-        <v>14.8632</v>
+        <v>14.5574</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.527</v>
       </c>
       <c r="J64" t="n">
-        <v>11.7876</v>
+        <v>11.594</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1746</v>
+        <v>0.148</v>
       </c>
       <c r="J65" t="n">
-        <v>3.8412</v>
+        <v>3.256</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4012</v>
+        <v>-0.3595</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.8264</v>
+        <v>-7.909</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4978</v>
+        <v>0.4596</v>
       </c>
       <c r="J67" t="n">
-        <v>10.9516</v>
+        <v>10.1112</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1488</v>
+        <v>0.1145</v>
       </c>
       <c r="J68" t="n">
-        <v>3.2736</v>
+        <v>2.519</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1464</v>
+        <v>-0.1269</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.2208</v>
+        <v>-2.7918</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2812</v>
+        <v>-0.2624</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.1864</v>
+        <v>-5.7728</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9415</v>
+        <v>0.9276</v>
       </c>
       <c r="J72" t="n">
-        <v>28.245</v>
+        <v>27.828</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.649</v>
+        <v>0.6355</v>
       </c>
       <c r="J73" t="n">
-        <v>19.47</v>
+        <v>19.065</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5708</v>
+        <v>0.5608</v>
       </c>
       <c r="J74" t="n">
-        <v>17.124</v>
+        <v>16.824</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1252</v>
+        <v>-0.0979</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.756</v>
+        <v>-2.937</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7063</v>
+        <v>-0.6765</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.189</v>
+        <v>-20.295</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3035</v>
+        <v>0.2527</v>
       </c>
       <c r="J77" t="n">
-        <v>9.105</v>
+        <v>7.581</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0819</v>
+        <v>0.0583</v>
       </c>
       <c r="J78" t="n">
-        <v>2.457</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1072</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.216</v>
+        <v>-2.724</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1421</v>
+        <v>-0.1235</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.263</v>
+        <v>-3.705</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.305</v>
+        <v>-0.2872</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.15</v>
+        <v>-8.616</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.15</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7427</v>
+        <v>1.7922</v>
       </c>
       <c r="J82" t="n">
-        <v>33.1113</v>
+        <v>34.0518</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.46</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8814</v>
+        <v>0.8681</v>
       </c>
       <c r="J83" t="n">
-        <v>16.7466</v>
+        <v>16.4939</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1498</v>
+        <v>0.1235</v>
       </c>
       <c r="J84" t="n">
-        <v>2.8462</v>
+        <v>2.3465</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1547</v>
+        <v>-0.1293</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.9393</v>
+        <v>-2.4567</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.257</v>
+        <v>-0.2228</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.883</v>
+        <v>-4.2332</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3726</v>
+        <v>0.3221</v>
       </c>
       <c r="J87" t="n">
-        <v>7.0794</v>
+        <v>6.1199</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1836</v>
+        <v>0.1464</v>
       </c>
       <c r="J88" t="n">
-        <v>3.4884</v>
+        <v>2.7816</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1781</v>
+        <v>-0.1606</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.3839</v>
+        <v>-3.0514</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3041</v>
+        <v>-0.2866</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.7779</v>
+        <v>-5.4454</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5777</v>
+        <v>-0.5889</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.9763</v>
+        <v>-11.1891</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.16</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3864</v>
+        <v>0.3319</v>
       </c>
       <c r="J92" t="n">
-        <v>7.728</v>
+        <v>6.638</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3304</v>
+        <v>0.2785</v>
       </c>
       <c r="J93" t="n">
-        <v>6.608</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1725</v>
+        <v>-0.1532</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.45</v>
+        <v>-3.064</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2441</v>
+        <v>-0.2243</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.882</v>
+        <v>-4.486</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4295</v>
+        <v>-0.4214</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.59</v>
+        <v>-8.428000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.93</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5083</v>
+        <v>1.534</v>
       </c>
       <c r="J97" t="n">
-        <v>30.166</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>13.356</v>
+        <v>13.114</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4832</v>
+        <v>0.4654</v>
       </c>
       <c r="J99" t="n">
-        <v>9.664</v>
+        <v>9.308</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.952</v>
+        <v>-1.536</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8061</v>
+        <v>-0.7871</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.122</v>
+        <v>-15.742</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.27</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6875</v>
       </c>
       <c r="J102" t="n">
-        <v>10.0935</v>
+        <v>10.3125</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.64</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3619</v>
+        <v>-0.3524</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.4285</v>
+        <v>-5.286</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.52</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4652</v>
+        <v>-0.4601</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.978</v>
+        <v>-6.9015</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.35</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6148</v>
+        <v>-0.6288</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.222</v>
+        <v>-9.432</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.31</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6499</v>
+        <v>-0.6702</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.7485</v>
+        <v>-10.053</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.46</v>
       </c>
       <c r="I107" t="n">
-        <v>2.0074</v>
+        <v>2.0808</v>
       </c>
       <c r="J107" t="n">
-        <v>30.111</v>
+        <v>31.212</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.28</v>
       </c>
       <c r="I108" t="n">
-        <v>1.8123</v>
+        <v>1.8607</v>
       </c>
       <c r="J108" t="n">
-        <v>27.1845</v>
+        <v>27.9105</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.43</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8142</v>
+        <v>0.8097</v>
       </c>
       <c r="J109" t="n">
-        <v>12.213</v>
+        <v>12.1455</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4907</v>
+        <v>0.4792</v>
       </c>
       <c r="J110" t="n">
-        <v>7.3605</v>
+        <v>7.188</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.8739</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.1175</v>
+        <v>-13.1085</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.72</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2677</v>
+        <v>1.2733</v>
       </c>
       <c r="J112" t="n">
-        <v>30.4248</v>
+        <v>30.5592</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7405</v>
+        <v>0.7248</v>
       </c>
       <c r="J113" t="n">
-        <v>17.772</v>
+        <v>17.3952</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.456</v>
+        <v>0.4253</v>
       </c>
       <c r="J114" t="n">
-        <v>10.944</v>
+        <v>10.2072</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.96</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1949</v>
+        <v>-0.1602</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.6776</v>
+        <v>-3.8448</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.18</v>
+        <v>-1.2058</v>
       </c>
       <c r="J116" t="n">
-        <v>-28.32</v>
+        <v>-28.9392</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.53</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8165</v>
+        <v>0.7834</v>
       </c>
       <c r="J117" t="n">
-        <v>19.596</v>
+        <v>18.8016</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0569</v>
+        <v>-0.0449</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.3656</v>
+        <v>-1.0776</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2306</v>
+        <v>-0.2102</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.5344</v>
+        <v>-5.0448</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2506</v>
+        <v>-0.2306</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.0144</v>
+        <v>-5.5344</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2702</v>
+        <v>-0.2509</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.4848</v>
+        <v>-6.0216</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.89</v>
       </c>
       <c r="I122" t="n">
-        <v>2.4491</v>
+        <v>2.5795</v>
       </c>
       <c r="J122" t="n">
-        <v>36.7365</v>
+        <v>38.6925</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.85</v>
       </c>
       <c r="I123" t="n">
-        <v>1.3233</v>
+        <v>1.3303</v>
       </c>
       <c r="J123" t="n">
-        <v>19.8495</v>
+        <v>19.9545</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9928</v>
+        <v>0.9902</v>
       </c>
       <c r="J124" t="n">
-        <v>14.892</v>
+        <v>14.853</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.103</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>1.545</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.91</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4164</v>
+        <v>-0.39</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.246</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.92</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0707</v>
+        <v>-0.0512</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.0605</v>
+        <v>-0.768</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.72</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2922</v>
+        <v>-0.2799</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.383</v>
+        <v>-4.1985</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3111</v>
+        <v>-0.2994</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.6665</v>
+        <v>-4.491</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3899</v>
+        <v>-0.3799</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.8485</v>
+        <v>-5.6985</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.27</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6875</v>
+        <v>-0.7159</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.3125</v>
+        <v>-10.7385</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9377</v>
+        <v>0.871</v>
       </c>
       <c r="J132" t="n">
-        <v>15.9409</v>
+        <v>14.807</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8095</v>
+        <v>0.7381</v>
       </c>
       <c r="J133" t="n">
-        <v>13.7615</v>
+        <v>12.5477</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.38</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4868</v>
+        <v>0.422</v>
       </c>
       <c r="J134" t="n">
-        <v>8.275600000000001</v>
+        <v>7.174</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1113</v>
+        <v>-0.0955</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.8921</v>
+        <v>-1.6235</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3158</v>
+        <v>-0.3024</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.3686</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.01</v>
       </c>
       <c r="I137" t="n">
-        <v>0.0737</v>
+        <v>0.0665</v>
       </c>
       <c r="J137" t="n">
-        <v>1.2529</v>
+        <v>1.1305</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.84</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1925</v>
+        <v>-0.1763</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.2725</v>
+        <v>-2.9971</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2423</v>
+        <v>-0.2255</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.1191</v>
+        <v>-3.8335</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.64</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3796</v>
+        <v>-0.3666</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.4532</v>
+        <v>-6.2322</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4065</v>
+        <v>-0.3955</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.9105</v>
+        <v>-6.7235</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5367</v>
+        <v>0.4855</v>
       </c>
       <c r="J142" t="n">
-        <v>10.1973</v>
+        <v>9.224500000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.93</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0984</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.8696</v>
+        <v>-1.6055</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2079</v>
+        <v>-0.1897</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.9501</v>
+        <v>-3.6043</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3866</v>
+        <v>-0.374</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.3454</v>
+        <v>-7.106</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4488</v>
+        <v>-0.4421</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.527200000000001</v>
+        <v>-8.399900000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.19</v>
       </c>
       <c r="I147" t="n">
-        <v>1.9161</v>
+        <v>1.9818</v>
       </c>
       <c r="J147" t="n">
-        <v>36.4059</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0996</v>
+        <v>1.1135</v>
       </c>
       <c r="J148" t="n">
-        <v>20.8924</v>
+        <v>21.1565</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6483</v>
+        <v>0.6248</v>
       </c>
       <c r="J149" t="n">
-        <v>12.3177</v>
+        <v>11.8712</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1697</v>
+        <v>0.1409</v>
       </c>
       <c r="J150" t="n">
-        <v>3.2243</v>
+        <v>2.6771</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4356</v>
+        <v>-0.4001</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.276400000000001</v>
+        <v>-7.6019</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7059</v>
+        <v>0.652</v>
       </c>
       <c r="J152" t="n">
-        <v>19.7652</v>
+        <v>18.256</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2211</v>
+        <v>0.1772</v>
       </c>
       <c r="J153" t="n">
-        <v>6.1908</v>
+        <v>4.9616</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0052</v>
+        <v>0.0029</v>
       </c>
       <c r="J154" t="n">
-        <v>0.1456</v>
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3062</v>
+        <v>-0.2884</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.573600000000001</v>
+        <v>-8.075200000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4421</v>
+        <v>-0.4358</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.3788</v>
+        <v>-12.2024</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2953</v>
+        <v>1.3157</v>
       </c>
       <c r="J157" t="n">
-        <v>36.2684</v>
+        <v>36.8396</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7141</v>
+        <v>0.6845</v>
       </c>
       <c r="J158" t="n">
-        <v>19.9948</v>
+        <v>19.166</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.17</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4808</v>
+        <v>0.4457</v>
       </c>
       <c r="J159" t="n">
-        <v>13.4624</v>
+        <v>12.4796</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.98</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1331</v>
+        <v>-0.1059</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.7268</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4306</v>
+        <v>-0.3895</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.0568</v>
+        <v>-10.906</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0207</v>
+        <v>0.0154</v>
       </c>
       <c r="J162" t="n">
-        <v>0.4968</v>
+        <v>0.3696</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.048</v>
+        <v>-0.0385</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.152</v>
+        <v>-0.924</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.92</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1145</v>
+        <v>-0.0992</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.748</v>
+        <v>-2.3808</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2206</v>
+        <v>-0.2013</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.2944</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3721</v>
+        <v>-0.3585</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.930400000000001</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.989</v>
+        <v>0.984</v>
       </c>
       <c r="J167" t="n">
-        <v>23.736</v>
+        <v>23.616</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6886</v>
+        <v>0.6551</v>
       </c>
       <c r="J168" t="n">
-        <v>16.5264</v>
+        <v>15.7224</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4437</v>
+        <v>0.4047</v>
       </c>
       <c r="J169" t="n">
-        <v>10.6488</v>
+        <v>9.7128</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.88</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4167</v>
+        <v>-0.374</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.0008</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4421</v>
+        <v>-0.3997</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.6104</v>
+        <v>-9.5928</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3975</v>
+        <v>0.3413</v>
       </c>
       <c r="J172" t="n">
-        <v>15.9</v>
+        <v>13.652</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.16</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3624</v>
+        <v>0.3079</v>
       </c>
       <c r="J173" t="n">
-        <v>14.496</v>
+        <v>12.316</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0427</v>
+        <v>0.0291</v>
       </c>
       <c r="J174" t="n">
-        <v>1.708</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0257</v>
+        <v>-0.0184</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.028</v>
+        <v>-0.736</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3484</v>
+        <v>-0.3337</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.936</v>
+        <v>-13.348</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2246</v>
+        <v>1.2418</v>
       </c>
       <c r="J177" t="n">
-        <v>48.984</v>
+        <v>49.672</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.16</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4617</v>
+        <v>0.4247</v>
       </c>
       <c r="J178" t="n">
-        <v>18.468</v>
+        <v>16.988</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.11</v>
       </c>
       <c r="I179" t="n">
-        <v>0.343</v>
+        <v>0.3079</v>
       </c>
       <c r="J179" t="n">
-        <v>13.72</v>
+        <v>12.316</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0852</v>
+        <v>-0.0643</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.408</v>
+        <v>-2.572</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2888</v>
+        <v>-0.2488</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.552</v>
+        <v>-9.952</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5454</v>
+        <v>0.4755</v>
       </c>
       <c r="J182" t="n">
-        <v>11.9988</v>
+        <v>10.461</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4352</v>
+        <v>0.3698</v>
       </c>
       <c r="J183" t="n">
-        <v>9.574400000000001</v>
+        <v>8.1356</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1483</v>
+        <v>0.1141</v>
       </c>
       <c r="J184" t="n">
-        <v>3.2626</v>
+        <v>2.5102</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0078</v>
+        <v>-0.0057</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.1716</v>
+        <v>-0.1254</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2914</v>
+        <v>-0.274</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.4108</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.513</v>
+        <v>0.5262</v>
       </c>
       <c r="J187" t="n">
-        <v>11.286</v>
+        <v>11.5764</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1201</v>
+        <v>0.1037</v>
       </c>
       <c r="J188" t="n">
-        <v>2.6422</v>
+        <v>2.2814</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0837</v>
+        <v>-0.0688</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.8414</v>
+        <v>-1.5136</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.4166</v>
+        <v>-2.9854</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4256</v>
+        <v>-0.4176</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.363200000000001</v>
+        <v>-9.187200000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6822</v>
+        <v>0.6262</v>
       </c>
       <c r="J192" t="n">
-        <v>15.0084</v>
+        <v>13.7764</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.99</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0243</v>
+        <v>-0.0177</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.5346</v>
+        <v>-0.3894</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0568</v>
+        <v>-0.0449</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.2496</v>
+        <v>-0.9878</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1674</v>
+        <v>-0.1473</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.6828</v>
+        <v>-3.2406</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3457</v>
+        <v>-0.3306</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.6054</v>
+        <v>-7.2732</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6774</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>14.9028</v>
+        <v>14.1372</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5441</v>
+        <v>0.5042</v>
       </c>
       <c r="J198" t="n">
-        <v>11.9702</v>
+        <v>11.0924</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0707</v>
+        <v>-0.0512</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.5554</v>
+        <v>-1.1264</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.98</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.112</v>
+        <v>-0.0858</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.464</v>
+        <v>-1.8876</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.96</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1822</v>
+        <v>-0.1481</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.0084</v>
+        <v>-3.2582</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3692</v>
+        <v>0.3154</v>
       </c>
       <c r="J202" t="n">
-        <v>7.7532</v>
+        <v>6.6234</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.04</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1413</v>
+        <v>0.1076</v>
       </c>
       <c r="J203" t="n">
-        <v>2.9673</v>
+        <v>2.2596</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.83</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2137</v>
+        <v>-0.1938</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.4877</v>
+        <v>-4.0698</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.5293</v>
+        <v>-5.1219</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3017</v>
+        <v>-0.2837</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.3357</v>
+        <v>-5.9577</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.54</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1575</v>
+        <v>1.1709</v>
       </c>
       <c r="J207" t="n">
-        <v>24.3075</v>
+        <v>24.5889</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0314</v>
+        <v>1.0339</v>
       </c>
       <c r="J208" t="n">
-        <v>21.6594</v>
+        <v>21.7119</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8119</v>
+        <v>0.7885</v>
       </c>
       <c r="J209" t="n">
-        <v>17.0499</v>
+        <v>16.5585</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5233</v>
+        <v>0.4892</v>
       </c>
       <c r="J210" t="n">
-        <v>10.9893</v>
+        <v>10.2732</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.52</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.2077</v>
+        <v>-1.2399</v>
       </c>
       <c r="J211" t="n">
-        <v>-25.3617</v>
+        <v>-26.0379</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6409</v>
+        <v>0.5825</v>
       </c>
       <c r="J212" t="n">
-        <v>14.7407</v>
+        <v>13.3975</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3437</v>
+        <v>0.2903</v>
       </c>
       <c r="J213" t="n">
-        <v>7.9051</v>
+        <v>6.6769</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1684</v>
+        <v>0.1317</v>
       </c>
       <c r="J214" t="n">
-        <v>3.8732</v>
+        <v>3.0291</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2535</v>
+        <v>-0.2337</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.8305</v>
+        <v>-5.3751</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3302</v>
+        <v>-0.3143</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.5946</v>
+        <v>-7.2289</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.9</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6405</v>
+        <v>1.6942</v>
       </c>
       <c r="J217" t="n">
-        <v>37.7315</v>
+        <v>38.9666</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.1</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3166</v>
+        <v>0.2825</v>
       </c>
       <c r="J218" t="n">
-        <v>7.2818</v>
+        <v>6.4975</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0265</v>
+        <v>-0.021</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.6095</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2899</v>
+        <v>-0.25</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.6677</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4506</v>
+        <v>-0.4091</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.3638</v>
+        <v>-9.4093</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6038</v>
+        <v>0.5506</v>
       </c>
       <c r="J222" t="n">
-        <v>10.8684</v>
+        <v>9.9108</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0184</v>
+        <v>0.0133</v>
       </c>
       <c r="J223" t="n">
-        <v>0.3312</v>
+        <v>0.2394</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1599</v>
+        <v>-0.1419</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.8782</v>
+        <v>-2.5542</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3086</v>
+        <v>-0.291</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.5548</v>
+        <v>-5.238</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.53</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4879</v>
+        <v>-0.4864</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.7822</v>
+        <v>-8.7552</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I227" t="n">
-        <v>1.6432</v>
+        <v>1.6879</v>
       </c>
       <c r="J227" t="n">
-        <v>29.5776</v>
+        <v>30.3822</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.68</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3108</v>
+        <v>1.3307</v>
       </c>
       <c r="J228" t="n">
-        <v>23.5944</v>
+        <v>23.9526</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0778</v>
+        <v>1.0892</v>
       </c>
       <c r="J229" t="n">
-        <v>19.4004</v>
+        <v>19.6056</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.01</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0014</v>
+        <v>-0.0102</v>
       </c>
       <c r="J230" t="n">
-        <v>0.0252</v>
+        <v>-0.1836</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.0491</v>
+        <v>-1.0621</v>
       </c>
       <c r="J231" t="n">
-        <v>-18.8838</v>
+        <v>-19.1178</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>0.914</v>
+        <v>0.874</v>
       </c>
       <c r="J232" t="n">
-        <v>17.366</v>
+        <v>16.606</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J233" t="n">
-        <v>3.363</v>
+        <v>2.6277</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.437</v>
+        <v>-0.323</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.63</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4074</v>
+        <v>-0.3975</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.7406</v>
+        <v>-7.5525</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4162</v>
+        <v>-0.4072</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.9078</v>
+        <v>-7.7368</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.66</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3055</v>
+        <v>1.3254</v>
       </c>
       <c r="J237" t="n">
-        <v>24.8045</v>
+        <v>25.1826</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.803</v>
+        <v>0.7811</v>
       </c>
       <c r="J238" t="n">
-        <v>15.257</v>
+        <v>14.8409</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.22</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5515</v>
       </c>
       <c r="J239" t="n">
-        <v>11.0618</v>
+        <v>10.4785</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.11</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3273</v>
+        <v>0.295</v>
       </c>
       <c r="J240" t="n">
-        <v>6.2187</v>
+        <v>5.605</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2466</v>
+        <v>-0.2109</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.6854</v>
+        <v>-4.0071</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9787</v>
+        <v>0.9478</v>
       </c>
       <c r="J242" t="n">
-        <v>22.5101</v>
+        <v>21.7994</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0469</v>
+        <v>0.0313</v>
       </c>
       <c r="J243" t="n">
-        <v>1.0787</v>
+        <v>0.7199</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.87</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1775</v>
+        <v>-0.1573</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.0825</v>
+        <v>-3.6179</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2296</v>
+        <v>-0.2093</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.2808</v>
+        <v>-4.8139</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4347</v>
+        <v>-0.4278</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.998100000000001</v>
+        <v>-9.839399999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.65</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3266</v>
+        <v>1.3512</v>
       </c>
       <c r="J247" t="n">
-        <v>30.5118</v>
+        <v>31.0776</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.25</v>
       </c>
       <c r="I248" t="n">
-        <v>0.664</v>
+        <v>0.6298</v>
       </c>
       <c r="J248" t="n">
-        <v>15.272</v>
+        <v>14.4854</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.25</v>
       </c>
       <c r="I249" t="n">
-        <v>0.664</v>
+        <v>0.6298</v>
       </c>
       <c r="J249" t="n">
-        <v>15.272</v>
+        <v>14.4854</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.367</v>
+        <v>-0.3248</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.441000000000001</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.59</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0595</v>
+        <v>-1.0672</v>
       </c>
       <c r="J251" t="n">
-        <v>-24.3685</v>
+        <v>-24.5456</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.8</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4899</v>
+        <v>1.5237</v>
       </c>
       <c r="J252" t="n">
-        <v>29.798</v>
+        <v>30.474</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.32</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.763</v>
       </c>
       <c r="J253" t="n">
-        <v>15.736</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.28</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7068</v>
+        <v>0.679</v>
       </c>
       <c r="J254" t="n">
-        <v>14.136</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.251</v>
+        <v>0.2205</v>
       </c>
       <c r="J255" t="n">
-        <v>5.02</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8711</v>
+        <v>-0.8589</v>
       </c>
       <c r="J256" t="n">
-        <v>-17.422</v>
+        <v>-17.178</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5566</v>
+        <v>0.5028</v>
       </c>
       <c r="J257" t="n">
-        <v>11.132</v>
+        <v>10.056</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.04</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1491</v>
+        <v>0.1149</v>
       </c>
       <c r="J258" t="n">
-        <v>2.982</v>
+        <v>2.298</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1025</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.05</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3814</v>
+        <v>-0.3685</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.628</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5044</v>
+        <v>-0.505</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.088</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3574</v>
+        <v>1.3798</v>
       </c>
       <c r="J262" t="n">
-        <v>25.7906</v>
+        <v>26.2162</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.65</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2808</v>
+        <v>1.2991</v>
       </c>
       <c r="J263" t="n">
-        <v>24.3352</v>
+        <v>24.6829</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5532</v>
+        <v>0.524</v>
       </c>
       <c r="J264" t="n">
-        <v>10.5108</v>
+        <v>9.956</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.12</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3439</v>
+        <v>0.3119</v>
       </c>
       <c r="J265" t="n">
-        <v>6.5341</v>
+        <v>5.9261</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.489</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.9693</v>
+        <v>-9.291</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.357</v>
+        <v>0.3076</v>
       </c>
       <c r="J267" t="n">
-        <v>6.783</v>
+        <v>5.8444</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.96</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0568</v>
+        <v>-0.0461</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.0792</v>
+        <v>-0.8759</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2842</v>
+        <v>-0.2662</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.3998</v>
+        <v>-5.0578</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.67</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3583</v>
+        <v>-0.3437</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.8077</v>
+        <v>-6.5303</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3855</v>
+        <v>-0.3728</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.3245</v>
+        <v>-7.0832</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.51</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1297</v>
+        <v>1.1426</v>
       </c>
       <c r="J272" t="n">
-        <v>24.8534</v>
+        <v>25.1372</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6381</v>
+        <v>0.6036</v>
       </c>
       <c r="J273" t="n">
-        <v>14.0382</v>
+        <v>13.2792</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3181</v>
+        <v>0.2836</v>
       </c>
       <c r="J274" t="n">
-        <v>6.9982</v>
+        <v>6.2392</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0247</v>
+        <v>-0.0193</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.5434</v>
+        <v>-0.4246</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.9</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3711</v>
+        <v>-0.3292</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.164199999999999</v>
+        <v>-7.2424</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.39</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7442</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>16.3724</v>
+        <v>15.202</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4567</v>
+        <v>0.3988</v>
       </c>
       <c r="J278" t="n">
-        <v>10.0474</v>
+        <v>8.7736</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.16</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3695</v>
+        <v>0.3146</v>
       </c>
       <c r="J279" t="n">
-        <v>8.129</v>
+        <v>6.9212</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4352</v>
+        <v>-0.4285</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.574400000000001</v>
+        <v>-9.427</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5042</v>
+        <v>-0.5062</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.0924</v>
+        <v>-11.1364</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.65</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8721</v>
+        <v>0.9588</v>
       </c>
       <c r="J282" t="n">
-        <v>20.9304</v>
+        <v>23.0112</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0578</v>
+        <v>-0.0454</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.3872</v>
+        <v>-1.0896</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.111</v>
+        <v>-0.0934</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.664</v>
+        <v>-2.2416</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.75</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3004</v>
+        <v>-0.2825</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.2096</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.67</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3745</v>
+        <v>-0.3618</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.988</v>
+        <v>-8.683199999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5901</v>
+        <v>0.5204</v>
       </c>
       <c r="J287" t="n">
-        <v>14.1624</v>
+        <v>12.4896</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4105</v>
+        <v>0.3465</v>
       </c>
       <c r="J288" t="n">
-        <v>9.852</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.96</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0765</v>
+        <v>-0.0613</v>
       </c>
       <c r="J289" t="n">
-        <v>-1.836</v>
+        <v>-1.4712</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1955</v>
+        <v>-0.1748</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.692</v>
+        <v>-4.1952</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3337</v>
+        <v>-0.3183</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.008800000000001</v>
+        <v>-7.6392</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.45</v>
       </c>
       <c r="I292" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J292" t="n">
-        <v>25.1836</v>
+        <v>25.7634</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>2.09</v>
       </c>
       <c r="I293" t="n">
-        <v>1.7218</v>
+        <v>1.7737</v>
       </c>
       <c r="J293" t="n">
-        <v>22.3834</v>
+        <v>23.0581</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.74</v>
       </c>
       <c r="I294" t="n">
-        <v>1.3329</v>
+        <v>1.3645</v>
       </c>
       <c r="J294" t="n">
-        <v>17.3277</v>
+        <v>17.7385</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9853</v>
       </c>
       <c r="J295" t="n">
-        <v>12.6659</v>
+        <v>12.8089</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.3</v>
       </c>
       <c r="I296" t="n">
-        <v>0.6742</v>
+        <v>0.6541</v>
       </c>
       <c r="J296" t="n">
-        <v>8.7646</v>
+        <v>8.503299999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.79</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1721</v>
+        <v>-0.1439</v>
       </c>
       <c r="J297" t="n">
-        <v>-2.2373</v>
+        <v>-1.8707</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.54</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.4309</v>
+        <v>-0.4289</v>
       </c>
       <c r="J298" t="n">
-        <v>-5.6017</v>
+        <v>-5.5757</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4731</v>
+        <v>-0.4725</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.1503</v>
+        <v>-6.1425</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4984</v>
+        <v>-0.4987</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.4792</v>
+        <v>-6.4831</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.2</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7339</v>
+        <v>-0.7696</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.540699999999999</v>
+        <v>-10.0048</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.4</v>
       </c>
       <c r="I302" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J302" t="n">
-        <v>29.058</v>
+        <v>29.727</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>2.28</v>
       </c>
       <c r="I303" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J303" t="n">
-        <v>29.058</v>
+        <v>29.727</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7059</v>
+        <v>0.6886</v>
       </c>
       <c r="J304" t="n">
-        <v>10.5885</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.15</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3806</v>
+        <v>0.347</v>
       </c>
       <c r="J305" t="n">
-        <v>5.709</v>
+        <v>5.205</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9908</v>
+        <v>-1.002</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.862</v>
+        <v>-15.03</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.9</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.124</v>
+        <v>-0.1091</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.86</v>
+        <v>-1.6365</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1472</v>
+        <v>-0.1318</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.208</v>
+        <v>-1.977</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1909</v>
+        <v>-0.175</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.8635</v>
+        <v>-2.625</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.66</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3602</v>
+        <v>-0.3461</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.403</v>
+        <v>-5.1915</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4582</v>
+        <v>-0.4521</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.873</v>
+        <v>-6.7815</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3664</v>
+        <v>1.3908</v>
       </c>
       <c r="J312" t="n">
-        <v>30.0608</v>
+        <v>30.5976</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.57</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1952</v>
+        <v>1.2099</v>
       </c>
       <c r="J313" t="n">
-        <v>26.2944</v>
+        <v>26.6178</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2537</v>
+        <v>0.223</v>
       </c>
       <c r="J314" t="n">
-        <v>5.5814</v>
+        <v>4.906</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2709</v>
+        <v>-0.233</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.9598</v>
+        <v>-5.126</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6283</v>
+        <v>-0.5952</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.8226</v>
+        <v>-13.0944</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6286</v>
+        <v>0.5722</v>
       </c>
       <c r="J317" t="n">
-        <v>13.8292</v>
+        <v>12.5884</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0554</v>
+        <v>-0.0443</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.2188</v>
+        <v>-0.9746</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.91</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1313</v>
+        <v>-0.1131</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.8886</v>
+        <v>-2.4882</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.79</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2576</v>
+        <v>-0.2379</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.6672</v>
+        <v>-5.2338</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.77</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2771</v>
+        <v>-0.258</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.0962</v>
+        <v>-5.676</v>
       </c>
     </row>
   </sheetData>
